--- a/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
+++ b/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R78cf11413bd94645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R874bdebffba6462c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="Rd45ea945a32f4c06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R6c954972241448e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R09e84eb89f67467a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R78a63e59565343d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R43c45543a68a4e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R711523ac9d67488e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="Rc49a277016d54c19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="Rb78d466b9b494181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R081149873d024e8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R8e3da8bd9a904a51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,7 +432,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8e8e7cd1d5744ab"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R751f1ccd780f4cd8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -532,7 +532,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Source ID"/>
     <x:tableColumn id="2" name="Publisher"/>
@@ -1049,7 +1049,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdce5731738224873"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a11b3d030c8410a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1229,7 +1229,7 @@
         <x:v>-0.07189690487427766</x:v>
       </x:c>
       <x:c r="O6" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
       </x:c>
       <x:c r="P6" s="16" t="str">
         <x:v>Year-long autonomous retail operation; balance is path dependent.</x:v>
@@ -1279,7 +1279,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="16" t="str">
-        <x:v>source-013</x:v>
+        <x:v>gate1-ceobench-com-ceo-bench-benchmark</x:v>
       </x:c>
       <x:c r="P7" s="16" t="str">
         <x:v>500-day startup simulation from $1M initial cash.</x:v>
@@ -1329,7 +1329,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="16" t="str">
-        <x:v>source-007</x:v>
+        <x:v>gate1-arxiv-org-yc-bench-benchmark</x:v>
       </x:c>
       <x:c r="P8" s="16" t="str">
         <x:v>The frontier exceeds the paper's 5×-capital threshold, so this score is saturated and needs a harder future anchor.</x:v>
@@ -1379,7 +1379,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="16" t="str">
-        <x:v>source-010</x:v>
+        <x:v>gate1-arxiv-org-business-arena-benchmark</x:v>
       </x:c>
       <x:c r="P9" s="16" t="str">
         <x:v>Ten-run model mean divided by the strongest published expert-designed strategy outcome.</x:v>
@@ -1429,7 +1429,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O10" s="16" t="str">
-        <x:v>source-011</x:v>
+        <x:v>gate1-arxiv-org-enterprisearena-benchmark</x:v>
       </x:c>
       <x:c r="P10" s="16" t="str">
         <x:v>132-month CFO simulator; only five seeds per system and the best published result is a tie.</x:v>
@@ -1479,7 +1479,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="16" t="str">
-        <x:v>source-006</x:v>
+        <x:v>gate1-arxiv-org-retailbench-benchmark</x:v>
       </x:c>
       <x:c r="P11" s="16" t="str">
         <x:v>Uses the v3 selected-run table; result is framework-selected and not a repeated-run mean.</x:v>
@@ -1529,7 +1529,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="16" t="str">
-        <x:v>source-009</x:v>
+        <x:v>gate1-arxiv-org-merchantbench-benchmark</x:v>
       </x:c>
       <x:c r="P12" s="16" t="str">
         <x:v>Three runs per model-framework pairing; human reference is three non-expert participants.</x:v>
@@ -1579,7 +1579,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="16" t="str">
-        <x:v>source-019</x:v>
+        <x:v>gate1-github-com-automationbench-benchmark</x:v>
       </x:c>
       <x:c r="P13" s="16" t="str">
         <x:v>Pinned to the current public 600-task table after the July 2026 stricter-classifier rescore; the private leaderboard is a different evaluation.</x:v>
@@ -1629,7 +1629,7 @@
         <x:v>-0.060528090139230106</x:v>
       </x:c>
       <x:c r="O14" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="P14" s="16" t="str">
         <x:v>Artificial Analysis implementation using the Stirrup harness, ServiceNow dataset, oracle tool mode, and three repeats per task.</x:v>
@@ -1679,7 +1679,7 @@
         <x:v>-0.004969950297574373</x:v>
       </x:c>
       <x:c r="O15" s="16" t="str">
-        <x:v>source-014</x:v>
+        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
       </x:c>
       <x:c r="P15" s="16" t="str">
         <x:v>Harness is held fixed so model release changes are more comparable.</x:v>
@@ -1729,7 +1729,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16" s="16" t="str">
-        <x:v>source-016</x:v>
+        <x:v>gate1-github-com-clawmark-benchmark</x:v>
       </x:c>
       <x:c r="P16" s="16" t="str">
         <x:v>Multi-day, multimodal coworker tasks across 13 domains.</x:v>
@@ -1779,7 +1779,7 @@
         <x:v>0.15016501951621222</x:v>
       </x:c>
       <x:c r="O17" s="16" t="str">
-        <x:v>source-005</x:v>
+        <x:v>gate1-arxiv-org-theagentcompany-benchmark</x:v>
       </x:c>
       <x:c r="P17" s="16" t="str">
         <x:v>Later points may include harness changes and should not be read as model-only uplift.</x:v>
@@ -1825,7 +1825,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O18" s="16" t="str">
-        <x:v>source-004</x:v>
+        <x:v>gate1-arxiv-org-workarena-benchmark</x:v>
       </x:c>
       <x:c r="P18" s="16" t="str">
         <x:v>Cataloged as an important browser/computer-use signal.</x:v>
@@ -1875,7 +1875,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O19" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-aclanthology-org-finch-finworkbench-benchmark</x:v>
       </x:c>
       <x:c r="P19" s="16" t="str">
         <x:v>Professional finance work with artifact and workflow requirements.</x:v>
@@ -1925,7 +1925,7 @@
         <x:v>0.17695542656782204</x:v>
       </x:c>
       <x:c r="O20" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="P20" s="16" t="str">
         <x:v>Customer-service policy and tool execution under realistic state.</x:v>
@@ -1975,7 +1975,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O21" s="16" t="str">
-        <x:v>source-023</x:v>
+        <x:v>gate1-mypcbench-com-mypcbench-benchmark</x:v>
       </x:c>
       <x:c r="P21" s="16" t="str">
         <x:v>Direct desktop computer use; current leaderboard may omit newer model generations.</x:v>
@@ -2025,7 +2025,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O22" s="16" t="str">
-        <x:v>source-012</x:v>
+        <x:v>gate1-arxiv-org-pi-bench-benchmark</x:v>
       </x:c>
       <x:c r="P22" s="16" t="str">
         <x:v>Personal-computing workflows scored for completion.</x:v>
@@ -2075,7 +2075,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O23" s="16" t="str">
-        <x:v>source-018</x:v>
+        <x:v>gate1-github-com-clawbench-benchmark</x:v>
       </x:c>
       <x:c r="P23" s="16" t="str">
         <x:v>Uses the repository's 33.3 headline/comparison score, not the separately reported 61.4% original-rubric pass rate.</x:v>
@@ -2125,7 +2125,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O24" s="16" t="str">
-        <x:v>source-020</x:v>
+        <x:v>gate1-hal-cs-princeton-edu-assistantbench-hal-benchmark</x:v>
       </x:c>
       <x:c r="P24" s="16" t="str">
         <x:v>Current HAL result covers 33 tasks and is treated as a one-point series, so it projects flat.</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O25" s="16" t="str">
-        <x:v>source-026</x:v>
+        <x:v>gate1-openai-com-gdpval-benchmark</x:v>
       </x:c>
       <x:c r="P25" s="16" t="str">
         <x:v>Keep the benchmark, but do not turn ‘just under half’ or Elo into a fake percentage.</x:v>
@@ -2221,7 +2221,7 @@
         <x:v>0.18034796332026065</x:v>
       </x:c>
       <x:c r="O26" s="16" t="str">
-        <x:v>source-037</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="P26" s="16" t="str">
         <x:v>Professional-worker benchmark used as a transfer signal, not a consumer denominator.</x:v>
@@ -2267,7 +2267,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O27" s="16" t="str">
-        <x:v>source-025</x:v>
+        <x:v>gate1-omegause-officeval-github-io-omegause-officeval-benchmark</x:v>
       </x:c>
       <x:c r="P27" s="16" t="str">
         <x:v>Economic value and computer-use signal.</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="O28" s="16" t="str">
-        <x:v>source-015</x:v>
+        <x:v>gate1-github-com-claw-eval-benchmark</x:v>
       </x:c>
       <x:c r="P28" s="16" t="str">
         <x:v>Governance/reliability emphasis; one current frontier point.</x:v>
@@ -2330,7 +2330,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re87897470fe54325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15c438678ec047a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2450,7 +2450,7 @@
         <x:v>Frontier balance / $63,000 strategy target</x:v>
       </x:c>
       <x:c r="I6" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
       </x:c>
       <x:c r="J6" s="16" t="str">
         <x:v>Observed release-quarter frontier.</x:v>
@@ -2482,7 +2482,7 @@
         <x:v>Frontier balance / $63,000 strategy target</x:v>
       </x:c>
       <x:c r="I7" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
       </x:c>
       <x:c r="J7" s="16" t="str">
         <x:v>Observed release-quarter frontier.</x:v>
@@ -2514,7 +2514,7 @@
         <x:v>Frontier balance / $63,000 strategy target</x:v>
       </x:c>
       <x:c r="I8" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
       </x:c>
       <x:c r="J8" s="16" t="str">
         <x:v>Observed release-quarter frontier.</x:v>
@@ -2546,7 +2546,7 @@
         <x:v>Best-run final cash / $2.2B upper bound</x:v>
       </x:c>
       <x:c r="I9" s="16" t="str">
-        <x:v>source-013</x:v>
+        <x:v>gate1-ceobench-com-ceo-bench-benchmark</x:v>
       </x:c>
       <x:c r="J9" s="16" t="str">
         <x:v>Three runs/model; best-run statistic is noisy.</x:v>
@@ -2578,7 +2578,7 @@
         <x:v>Best-run final cash / $2.2B upper bound</x:v>
       </x:c>
       <x:c r="I10" s="16" t="str">
-        <x:v>source-013</x:v>
+        <x:v>gate1-ceobench-com-ceo-bench-benchmark</x:v>
       </x:c>
       <x:c r="J10" s="16" t="str">
         <x:v>Three runs/model; best-run statistic is noisy.</x:v>
@@ -2610,7 +2610,7 @@
         <x:v>Mean final funds / $1M published substantial-profit threshold</x:v>
       </x:c>
       <x:c r="I11" s="16" t="str">
-        <x:v>source-007</x:v>
+        <x:v>gate1-arxiv-org-yc-bench-benchmark</x:v>
       </x:c>
       <x:c r="J11" s="16" t="str">
         <x:v>Provisional target-normalized score. Saturated at launch; no human or oracle ceiling is published.</x:v>
@@ -2642,7 +2642,7 @@
         <x:v>Best-model mean final worth / expert-strategy final worth</x:v>
       </x:c>
       <x:c r="I12" s="16" t="str">
-        <x:v>source-010</x:v>
+        <x:v>gate1-arxiv-org-business-arena-benchmark</x:v>
       </x:c>
       <x:c r="J12" s="16" t="str">
         <x:v>Ten matched runs per model; reference strategy uses only agent-visible information.</x:v>
@@ -2674,7 +2674,7 @@
         <x:v>Best-system full-horizon survival</x:v>
       </x:c>
       <x:c r="I13" s="16" t="str">
-        <x:v>source-011</x:v>
+        <x:v>gate1-arxiv-org-enterprisearena-benchmark</x:v>
       </x:c>
       <x:c r="J13" s="16" t="str">
         <x:v>Five seeds per system. The paper reports 60% full survival for both leaders and 20% for Qwen3.5-9B.</x:v>
@@ -2706,7 +2706,7 @@
         <x:v>Best LLM final net worth / oracle final net worth</x:v>
       </x:c>
       <x:c r="I14" s="16" t="str">
-        <x:v>source-006</x:v>
+        <x:v>gate1-arxiv-org-retailbench-benchmark</x:v>
       </x:c>
       <x:c r="J14" s="16" t="str">
         <x:v>Selected-run protocol; oracle has privileged simulator access and is a ceiling-like reference.</x:v>
@@ -2738,7 +2738,7 @@
         <x:v>Best LLM mean final net assets / human mean</x:v>
       </x:c>
       <x:c r="I15" s="16" t="str">
-        <x:v>source-009</x:v>
+        <x:v>gate1-arxiv-org-merchantbench-benchmark</x:v>
       </x:c>
       <x:c r="J15" s="16" t="str">
         <x:v>Authors' reported ratio; three LLM runs per configuration and three non-expert human participants.</x:v>
@@ -2770,7 +2770,7 @@
         <x:v>Public 600-task pass rate, max reasoning</x:v>
       </x:c>
       <x:c r="I16" s="16" t="str">
-        <x:v>source-019</x:v>
+        <x:v>gate1-github-com-automationbench-benchmark</x:v>
       </x:c>
       <x:c r="J16" s="16" t="str">
         <x:v>Current public frontier after the July 2026 stricter-classifier rescore; 182/600 tasks. Later private-leaderboard results are not comparable.</x:v>
@@ -2802,7 +2802,7 @@
         <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="I17" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="J17" s="16" t="str">
         <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
@@ -2834,7 +2834,7 @@
         <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="I18" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="J18" s="16" t="str">
         <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
@@ -2866,7 +2866,7 @@
         <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="I19" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="J19" s="16" t="str">
         <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
@@ -2898,7 +2898,7 @@
         <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="I20" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="J20" s="16" t="str">
         <x:v>Retrospective release-date point from the EnterpriseOps-Gym-AA table.</x:v>
@@ -2930,13 +2930,13 @@
         <x:v>Strict task success in oracle tool mode</x:v>
       </x:c>
       <x:c r="I21" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="J21" s="16" t="str">
         <x:v>Current 51.1% frontier; adaptive max-effort configuration includes an Opus 4.8 fallback.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="22" ht="54" hidden="0" customHeight="1">
       <x:c r="A22" s="16" t="str">
         <x:v>forecast-observation-017</x:v>
       </x:c>
@@ -2962,13 +2962,13 @@
         <x:v>Pi-harness full-suite pass rate</x:v>
       </x:c>
       <x:c r="I22" s="16" t="str">
-        <x:v>source-014</x:v>
+        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
       </x:c>
       <x:c r="J22" s="16" t="str">
         <x:v>107-task benchmark snapshot.</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="23" ht="54" hidden="0" customHeight="1">
       <x:c r="A23" s="16" t="str">
         <x:v>forecast-observation-018</x:v>
       </x:c>
@@ -2994,13 +2994,13 @@
         <x:v>Pi-harness full-suite pass rate</x:v>
       </x:c>
       <x:c r="I23" s="16" t="str">
-        <x:v>source-014</x:v>
+        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
       </x:c>
       <x:c r="J23" s="16" t="str">
         <x:v>Quarter frontier; fixed Pi harness.</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="24" ht="54" hidden="0" customHeight="1">
       <x:c r="A24" s="16" t="str">
         <x:v>forecast-observation-019</x:v>
       </x:c>
@@ -3026,7 +3026,7 @@
         <x:v>Pi-harness full-suite pass rate</x:v>
       </x:c>
       <x:c r="I24" s="16" t="str">
-        <x:v>source-014</x:v>
+        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
       </x:c>
       <x:c r="J24" s="16" t="str">
         <x:v>65/107 tasks; fixed Pi harness.</x:v>
@@ -3058,13 +3058,13 @@
         <x:v>Avg@3 weighted deterministic-checker score</x:v>
       </x:c>
       <x:c r="I25" s="16" t="str">
-        <x:v>source-016</x:v>
+        <x:v>gate1-github-com-clawmark-benchmark</x:v>
       </x:c>
       <x:c r="J25" s="16" t="str">
         <x:v>One pinned 100-task repo snapshot.</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="26" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A26" s="16" t="str">
         <x:v>forecast-observation-021</x:v>
       </x:c>
@@ -3090,7 +3090,7 @@
         <x:v>Fraction of tasks completed</x:v>
       </x:c>
       <x:c r="I26" s="16" t="str">
-        <x:v>source-005</x:v>
+        <x:v>gate1-arxiv-org-theagentcompany-benchmark</x:v>
       </x:c>
       <x:c r="J26" s="16" t="str">
         <x:v>Primary-paper baseline.</x:v>
@@ -3122,13 +3122,13 @@
         <x:v>Fraction of tasks completed</x:v>
       </x:c>
       <x:c r="I27" s="16" t="str">
-        <x:v>source-034</x:v>
+        <x:v>gate1-the-agent-company-com-theagentcompany-observation-source</x:v>
       </x:c>
       <x:c r="J27" s="16" t="str">
         <x:v>Later leaderboard configuration; comparability caveat.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="54" hidden="0" customHeight="1">
+    <x:row r="28" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A28" s="16" t="str">
         <x:v>forecast-observation-023</x:v>
       </x:c>
@@ -3154,7 +3154,7 @@
         <x:v>Fraction of tasks completed</x:v>
       </x:c>
       <x:c r="I28" s="16" t="str">
-        <x:v>source-034</x:v>
+        <x:v>gate1-the-agent-company-com-theagentcompany-observation-source</x:v>
       </x:c>
       <x:c r="J28" s="16" t="str">
         <x:v>Community/specialized harness; system-level frontier.</x:v>
@@ -3186,7 +3186,7 @@
         <x:v>Strict finance-work task pass rate</x:v>
       </x:c>
       <x:c r="I29" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-aclanthology-org-finch-finworkbench-benchmark</x:v>
       </x:c>
       <x:c r="J29" s="16" t="str">
         <x:v>Model release-quarter assignment; publication followed in 2026.</x:v>
@@ -3218,7 +3218,7 @@
         <x:v>tau3 Banking strict success</x:v>
       </x:c>
       <x:c r="I30" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="J30" s="16" t="str">
         <x:v>Release-quarter frontier.</x:v>
@@ -3250,7 +3250,7 @@
         <x:v>tau3 Banking strict success</x:v>
       </x:c>
       <x:c r="I31" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="J31" s="16" t="str">
         <x:v>Release-quarter frontier.</x:v>
@@ -3282,7 +3282,7 @@
         <x:v>tau3 Banking strict success</x:v>
       </x:c>
       <x:c r="I32" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="J32" s="16" t="str">
         <x:v>Release-quarter frontier.</x:v>
@@ -3314,7 +3314,7 @@
         <x:v>tau3 Banking strict success</x:v>
       </x:c>
       <x:c r="I33" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="J33" s="16" t="str">
         <x:v>Release-quarter frontier.</x:v>
@@ -3346,7 +3346,7 @@
         <x:v>tau3 Banking strict success</x:v>
       </x:c>
       <x:c r="I34" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="J34" s="16" t="str">
         <x:v>Current quarter frontier.</x:v>
@@ -3378,7 +3378,7 @@
         <x:v>Perfect task success rate</x:v>
       </x:c>
       <x:c r="I35" s="16" t="str">
-        <x:v>source-023</x:v>
+        <x:v>gate1-mypcbench-com-mypcbench-benchmark</x:v>
       </x:c>
       <x:c r="J35" s="16" t="str">
         <x:v>Current published frontier; newer models may be missing.</x:v>
@@ -3410,7 +3410,7 @@
         <x:v>Completeness checklist score</x:v>
       </x:c>
       <x:c r="I36" s="16" t="str">
-        <x:v>source-012</x:v>
+        <x:v>gate1-arxiv-org-pi-bench-benchmark</x:v>
       </x:c>
       <x:c r="J36" s="16" t="str">
         <x:v>One comparable frontier point.</x:v>
@@ -3442,7 +3442,7 @@
         <x:v>ClawBench V1 six-model comparison score</x:v>
       </x:c>
       <x:c r="I37" s="16" t="str">
-        <x:v>source-018</x:v>
+        <x:v>gate1-github-com-clawbench-benchmark</x:v>
       </x:c>
       <x:c r="J37" s="16" t="str">
         <x:v>Repository headline/comparison score. Do not mix with its separate original-rubric pass-rate table.</x:v>
@@ -3474,13 +3474,13 @@
         <x:v>Assistant task accuracy on current HAL 33-task configuration</x:v>
       </x:c>
       <x:c r="I38" s="16" t="str">
-        <x:v>source-020</x:v>
+        <x:v>gate1-hal-cs-princeton-edu-assistantbench-hal-benchmark</x:v>
       </x:c>
       <x:c r="J38" s="16" t="str">
         <x:v>Verified HAL leaderboard result. Kept separate from the 2024 full-benchmark configuration and projected flat.</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="39" ht="54" hidden="0" customHeight="1">
       <x:c r="A39" s="16" t="str">
         <x:v>forecast-observation-034</x:v>
       </x:c>
@@ -3506,13 +3506,13 @@
         <x:v>Strict end-to-end automation rate</x:v>
       </x:c>
       <x:c r="I39" s="16" t="str">
-        <x:v>source-037</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="J39" s="16" t="str">
         <x:v>Quarter frontier.</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="40" ht="54" hidden="0" customHeight="1">
       <x:c r="A40" s="16" t="str">
         <x:v>forecast-observation-035</x:v>
       </x:c>
@@ -3538,13 +3538,13 @@
         <x:v>Strict end-to-end automation rate</x:v>
       </x:c>
       <x:c r="I40" s="16" t="str">
-        <x:v>source-037</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="J40" s="16" t="str">
         <x:v>Quarter frontier.</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="41" ht="54" hidden="0" customHeight="1">
       <x:c r="A41" s="16" t="str">
         <x:v>forecast-observation-036</x:v>
       </x:c>
@@ -3570,7 +3570,7 @@
         <x:v>Strict end-to-end automation rate</x:v>
       </x:c>
       <x:c r="I41" s="16" t="str">
-        <x:v>source-037</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="J41" s="16" t="str">
         <x:v>Quarter frontier.</x:v>
@@ -3602,13 +3602,13 @@
         <x:v>Strict end-to-end automation rate</x:v>
       </x:c>
       <x:c r="I42" s="16" t="str">
-        <x:v>source-037</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="J42" s="16" t="str">
         <x:v>Current frontier; large quarter jump merits caution.</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="43" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A43" s="16" t="str">
         <x:v>forecast-observation-038</x:v>
       </x:c>
@@ -3634,7 +3634,7 @@
         <x:v>Pass^3 governed-agent score</x:v>
       </x:c>
       <x:c r="I43" s="16" t="str">
-        <x:v>source-015</x:v>
+        <x:v>gate1-github-com-claw-eval-benchmark</x:v>
       </x:c>
       <x:c r="J43" s="16" t="str">
         <x:v>One current frontier point.</x:v>
@@ -3647,7 +3647,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf38a3d5e40254dc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R789aa06094014b2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4146,9 +4146,9 @@
     <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ca08bb676a54a44"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17f988c1ac974d05"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R342dc7c9c1404501"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R347262acece241b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4258,7 +4258,7 @@
         <x:v>METR-selected Triframe scaffold</x:v>
       </x:c>
       <x:c r="H6" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I6" s="16" t="str">
         <x:v>Mostly software/ML/cyber tasks; horizon is human task duration rather than agent runtime</x:v>
@@ -4287,7 +4287,7 @@
         <x:v>METR-selected ReAct scaffold</x:v>
       </x:c>
       <x:c r="H7" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I7" s="16" t="str">
         <x:v>Scaffold differs by model family because METR elicits each model</x:v>
@@ -4316,7 +4316,7 @@
         <x:v>METR-selected Triframe scaffold</x:v>
       </x:c>
       <x:c r="H8" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I8" s="16" t="str">
         <x:v>Scaffold differs by model family because METR elicits each model</x:v>
@@ -4345,7 +4345,7 @@
         <x:v>METR-selected ReAct scaffold</x:v>
       </x:c>
       <x:c r="H9" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I9" s="16" t="str">
         <x:v>Point estimate has a wide confidence interval</x:v>
@@ -4374,7 +4374,7 @@
         <x:v>METR-selected ReAct scaffold</x:v>
       </x:c>
       <x:c r="H10" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I10" s="16" t="str">
         <x:v>METR warns that estimates above 16 hours are unreliable</x:v>
@@ -4403,7 +4403,7 @@
         <x:v>METR-selected Triframe scaffold</x:v>
       </x:c>
       <x:c r="H11" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I11" s="16" t="str">
         <x:v>Higher-reliability horizon on the same task suite</x:v>
@@ -4432,7 +4432,7 @@
         <x:v>METR-selected ReAct scaffold</x:v>
       </x:c>
       <x:c r="H12" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I12" s="16" t="str">
         <x:v>Higher-reliability horizon on the same task suite</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>METR-selected Triframe scaffold</x:v>
       </x:c>
       <x:c r="H13" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I13" s="16" t="str">
         <x:v>Higher-reliability horizon on the same task suite</x:v>
@@ -4490,7 +4490,7 @@
         <x:v>METR-selected ReAct scaffold</x:v>
       </x:c>
       <x:c r="H14" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I14" s="16" t="str">
         <x:v>Higher-reliability horizon on the same task suite</x:v>
@@ -4519,7 +4519,7 @@
         <x:v>METR-selected ReAct scaffold</x:v>
       </x:c>
       <x:c r="H15" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="I15" s="16" t="str">
         <x:v>Higher-reliability horizon on the same task suite</x:v>
@@ -4548,7 +4548,7 @@
         <x:v>days; METR all-time stitched log-linear fit excluding central H50 estimates above 16 hours</x:v>
       </x:c>
       <x:c r="H16" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
       </x:c>
       <x:c r="I16" s="16" t="str">
         <x:v>Official point estimate</x:v>
@@ -4577,7 +4577,7 @@
         <x:v>days; METR post-2023 log-linear fit excluding central H50 estimates above 16 hours</x:v>
       </x:c>
       <x:c r="H17" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
       </x:c>
       <x:c r="I17" s="16" t="str">
         <x:v>Official point estimate and reported interval</x:v>
@@ -4606,7 +4606,7 @@
         <x:v>days; Two-endpoint log growth from GPT-5 203.012577 minutes to Claude Mythos Preview 1044.780145 minutes</x:v>
       </x:c>
       <x:c r="H18" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
       </x:c>
       <x:c r="I18" s="16" t="str">
         <x:v>Not an independent acceleration fit; final estimate exceeds METR 16-hour reliable range</x:v>
@@ -4635,7 +4635,7 @@
         <x:v>days; Two-endpoint log growth from H80 38.312431 to 185.911829 minutes</x:v>
       </x:c>
       <x:c r="H19" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
       </x:c>
       <x:c r="I19" s="16" t="str">
         <x:v>H80 comes from same two-parameter fit and is not independent</x:v>
@@ -4648,7 +4648,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4cf174731ef409b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda73b4c901c345de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4721,9 +4721,9 @@
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="6" ht="54" hidden="0" customHeight="1">
       <x:c r="A6" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-aclanthology-org-finch-finworkbench-benchmark</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
         <x:v>aclanthology.org</x:v>
@@ -4742,9 +4742,9 @@
       </x:c>
       <x:c r="G6" s="16" t="str"/>
     </x:row>
-    <x:row r="7" ht="97.19999694824219" hidden="0" customHeight="1">
+    <x:row r="7" ht="108" hidden="0" customHeight="1">
       <x:c r="A7" s="16" t="str">
-        <x:v>source-002</x:v>
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
         <x:v>andonlabs.com</x:v>
@@ -4756,64 +4756,64 @@
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E7" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation, supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>Business, forecast benchmark, forecast observation, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F7" s="16" t="str">
         <x:v>https://andonlabs.com/evals/vending-bench-2</x:v>
       </x:c>
       <x:c r="G7" s="16" t="str"/>
     </x:row>
-    <x:row r="8" ht="54" hidden="0" customHeight="1">
+    <x:row r="8" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A8" s="16" t="str">
-        <x:v>source-003</x:v>
+        <x:v>gate1-anthropic-com-osworld-observation-source</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>artificialanalysis.ai</x:v>
+        <x:v>anthropic.com</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>EnterpriseOps-Gym-AA benchmark</x:v>
+        <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E8" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>Capability velocity, release metadata, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F8" s="16" t="str">
-        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
+        <x:v>https://www.anthropic.com/news/claude-sonnet-4-5</x:v>
       </x:c>
       <x:c r="G8" s="16" t="str"/>
     </x:row>
-    <x:row r="9" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="9" ht="54" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
-        <x:v>source-004</x:v>
+        <x:v>gate1-artificialanalysis-ai-enterpriseops-gym-aa-benchmark</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
-        <x:v>arxiv.org</x:v>
+        <x:v>artificialanalysis.ai</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str">
-        <x:v>WorkArena++ benchmark</x:v>
+        <x:v>EnterpriseOps-Gym-AA benchmark</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E9" s="16" t="str">
-        <x:v>forecast benchmark</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F9" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2407.05291</x:v>
+        <x:v>https://artificialanalysis.ai/evaluations/enterprise-ops-gym-aa</x:v>
       </x:c>
       <x:c r="G9" s="16" t="str"/>
     </x:row>
     <x:row r="10" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A10" s="16" t="str">
-        <x:v>source-005</x:v>
+        <x:v>gate1-arxiv-org-business-arena-benchmark</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C10" s="16" t="str">
-        <x:v>TheAgentCompany benchmark</x:v>
+        <x:v>Business Arena benchmark</x:v>
       </x:c>
       <x:c r="D10" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4822,19 +4822,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F10" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2412.14161</x:v>
+        <x:v>https://arxiv.org/abs/2608.08621</x:v>
       </x:c>
       <x:c r="G10" s="16" t="str"/>
     </x:row>
     <x:row r="11" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
-        <x:v>source-006</x:v>
+        <x:v>gate1-arxiv-org-enterprisearena-benchmark</x:v>
       </x:c>
       <x:c r="B11" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str">
-        <x:v>RetailBench benchmark</x:v>
+        <x:v>EnterpriseArena benchmark</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4843,19 +4843,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F11" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2603.16453</x:v>
+        <x:v>https://arxiv.org/html/2603.23638v2</x:v>
       </x:c>
       <x:c r="G11" s="16" t="str"/>
     </x:row>
     <x:row r="12" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A12" s="16" t="str">
-        <x:v>source-007</x:v>
+        <x:v>gate1-arxiv-org-merchantbench-benchmark</x:v>
       </x:c>
       <x:c r="B12" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C12" s="16" t="str">
-        <x:v>YC-Bench benchmark</x:v>
+        <x:v>MerchantBench benchmark</x:v>
       </x:c>
       <x:c r="D12" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4864,13 +4864,13 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F12" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2604.01212</x:v>
+        <x:v>https://arxiv.org/abs/2607.28956</x:v>
       </x:c>
       <x:c r="G12" s="16" t="str"/>
     </x:row>
-    <x:row r="13" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="13" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>source-008</x:v>
+        <x:v>gate1-arxiv-org-osworld-observation-source</x:v>
       </x:c>
       <x:c r="B13" s="16" t="str">
         <x:v>arxiv.org</x:v>
@@ -4891,13 +4891,13 @@
     </x:row>
     <x:row r="14" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A14" s="16" t="str">
-        <x:v>source-009</x:v>
+        <x:v>gate1-arxiv-org-pi-bench-benchmark</x:v>
       </x:c>
       <x:c r="B14" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C14" s="16" t="str">
-        <x:v>MerchantBench benchmark</x:v>
+        <x:v>pi-Bench benchmark</x:v>
       </x:c>
       <x:c r="D14" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4906,19 +4906,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F14" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2607.28956</x:v>
+        <x:v>https://arxiv.org/html/2605.14678v3</x:v>
       </x:c>
       <x:c r="G14" s="16" t="str"/>
     </x:row>
     <x:row r="15" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A15" s="16" t="str">
-        <x:v>source-010</x:v>
+        <x:v>gate1-arxiv-org-retailbench-benchmark</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C15" s="16" t="str">
-        <x:v>Business Arena benchmark</x:v>
+        <x:v>RetailBench benchmark</x:v>
       </x:c>
       <x:c r="D15" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4927,19 +4927,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F15" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2608.08621</x:v>
+        <x:v>https://arxiv.org/abs/2603.16453</x:v>
       </x:c>
       <x:c r="G15" s="16" t="str"/>
     </x:row>
     <x:row r="16" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A16" s="16" t="str">
-        <x:v>source-011</x:v>
+        <x:v>gate1-arxiv-org-theagentcompany-benchmark</x:v>
       </x:c>
       <x:c r="B16" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C16" s="16" t="str">
-        <x:v>EnterpriseArena benchmark</x:v>
+        <x:v>TheAgentCompany benchmark</x:v>
       </x:c>
       <x:c r="D16" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4948,40 +4948,40 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F16" s="16" t="str">
-        <x:v>https://arxiv.org/html/2603.23638v2</x:v>
+        <x:v>https://arxiv.org/abs/2412.14161</x:v>
       </x:c>
       <x:c r="G16" s="16" t="str"/>
     </x:row>
     <x:row r="17" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A17" s="16" t="str">
-        <x:v>source-012</x:v>
+        <x:v>gate1-arxiv-org-workarena-benchmark</x:v>
       </x:c>
       <x:c r="B17" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C17" s="16" t="str">
-        <x:v>pi-Bench benchmark</x:v>
+        <x:v>WorkArena++ benchmark</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>forecast benchmark</x:v>
       </x:c>
       <x:c r="F17" s="16" t="str">
-        <x:v>https://arxiv.org/html/2605.14678v3</x:v>
+        <x:v>https://arxiv.org/abs/2407.05291</x:v>
       </x:c>
       <x:c r="G17" s="16" t="str"/>
     </x:row>
     <x:row r="18" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A18" s="16" t="str">
-        <x:v>source-013</x:v>
+        <x:v>gate1-arxiv-org-yc-bench-benchmark</x:v>
       </x:c>
       <x:c r="B18" s="16" t="str">
-        <x:v>ceobench.com</x:v>
+        <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C18" s="16" t="str">
-        <x:v>CEO-Bench benchmark</x:v>
+        <x:v>YC-Bench benchmark</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -4990,19 +4990,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F18" s="16" t="str">
-        <x:v>https://ceobench.com/</x:v>
+        <x:v>https://arxiv.org/abs/2604.01212</x:v>
       </x:c>
       <x:c r="G18" s="16" t="str"/>
     </x:row>
-    <x:row r="19" ht="54" hidden="0" customHeight="1">
+    <x:row r="19" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A19" s="16" t="str">
-        <x:v>source-014</x:v>
+        <x:v>gate1-ceobench-com-ceo-bench-benchmark</x:v>
       </x:c>
       <x:c r="B19" s="16" t="str">
-        <x:v>github.com</x:v>
+        <x:v>ceobench.com</x:v>
       </x:c>
       <x:c r="C19" s="16" t="str">
-        <x:v>Commerce Agent Bench benchmark</x:v>
+        <x:v>CEO-Bench benchmark</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5011,40 +5011,42 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F19" s="16" t="str">
-        <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
+        <x:v>https://ceobench.com/</x:v>
       </x:c>
       <x:c r="G19" s="16" t="str"/>
     </x:row>
-    <x:row r="20" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="20" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A20" s="16" t="str">
-        <x:v>source-015</x:v>
+        <x:v>gate1-diffuse-personal-ai-gate-1-model-harness-capability-calculation-contract</x:v>
       </x:c>
       <x:c r="B20" s="16" t="str">
-        <x:v>github.com</x:v>
+        <x:v>Diffuse Personal AI</x:v>
       </x:c>
       <x:c r="C20" s="16" t="str">
-        <x:v>Claw-Eval benchmark</x:v>
+        <x:v>Gate 1 · Model–harness capability calculation contract</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>methodology, normalization, model configuration</x:v>
       </x:c>
       <x:c r="F20" s="16" t="str">
-        <x:v>https://github.com/claw-eval/claw-eval</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="str"/>
+        <x:v>https://github.com/buwilliams/diffuse-personal-ai/blob/main/intent/02-model/06-report-card-calculations.md</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="str">
+        <x:v>Holds definitions and assumptions that are authored by the forecast rather than fetched as observations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="21" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A21" s="16" t="str">
-        <x:v>source-016</x:v>
+        <x:v>gate1-github-com-automationbench-benchmark</x:v>
       </x:c>
       <x:c r="B21" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C21" s="16" t="str">
-        <x:v>ClawMark benchmark</x:v>
+        <x:v>AutomationBench benchmark</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5053,34 +5055,34 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F21" s="16" t="str">
-        <x:v>https://github.com/evolvent-ai/ClawMark</x:v>
+        <x:v>https://github.com/zapier/AutomationBench</x:v>
       </x:c>
       <x:c r="G21" s="16" t="str"/>
     </x:row>
-    <x:row r="22" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="22" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A22" s="16" t="str">
-        <x:v>source-017</x:v>
+        <x:v>gate1-github-com-claw-eval-benchmark</x:v>
       </x:c>
       <x:c r="B22" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C22" s="16" t="str">
-        <x:v>MyPCBench source</x:v>
+        <x:v>Claw-Eval benchmark</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E22" s="16" t="str">
-        <x:v>supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F22" s="16" t="str">
-        <x:v>https://github.com/ljang0/MyPCBench/blob/main/README.md</x:v>
+        <x:v>https://github.com/claw-eval/claw-eval</x:v>
       </x:c>
       <x:c r="G22" s="16" t="str"/>
     </x:row>
     <x:row r="23" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A23" s="16" t="str">
-        <x:v>source-018</x:v>
+        <x:v>gate1-github-com-clawbench-benchmark</x:v>
       </x:c>
       <x:c r="B23" s="16" t="str">
         <x:v>github.com</x:v>
@@ -5101,13 +5103,13 @@
     </x:row>
     <x:row r="24" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A24" s="16" t="str">
-        <x:v>source-019</x:v>
+        <x:v>gate1-github-com-clawmark-benchmark</x:v>
       </x:c>
       <x:c r="B24" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C24" s="16" t="str">
-        <x:v>AutomationBench benchmark</x:v>
+        <x:v>ClawMark benchmark</x:v>
       </x:c>
       <x:c r="D24" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5116,19 +5118,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F24" s="16" t="str">
-        <x:v>https://github.com/zapier/AutomationBench</x:v>
+        <x:v>https://github.com/evolvent-ai/ClawMark</x:v>
       </x:c>
       <x:c r="G24" s="16" t="str"/>
     </x:row>
-    <x:row r="25" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="25" ht="54" hidden="0" customHeight="1">
       <x:c r="A25" s="16" t="str">
-        <x:v>source-020</x:v>
+        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
       </x:c>
       <x:c r="B25" s="16" t="str">
-        <x:v>hal.cs.princeton.edu</x:v>
+        <x:v>github.com</x:v>
       </x:c>
       <x:c r="C25" s="16" t="str">
-        <x:v>AssistantBench (HAL) benchmark</x:v>
+        <x:v>Commerce Agent Bench benchmark</x:v>
       </x:c>
       <x:c r="D25" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5137,387 +5139,408 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F25" s="16" t="str">
-        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
+        <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
       </x:c>
       <x:c r="G25" s="16" t="str"/>
     </x:row>
-    <x:row r="26" ht="54" hidden="0" customHeight="1">
+    <x:row r="26" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A26" s="16" t="str">
-        <x:v>source-021</x:v>
+        <x:v>gate1-github-com-mypcbench-source</x:v>
       </x:c>
       <x:c r="B26" s="16" t="str">
-        <x:v>labs.scale.com</x:v>
+        <x:v>github.com</x:v>
       </x:c>
       <x:c r="C26" s="16" t="str">
-        <x:v>Remote Labor Index source</x:v>
+        <x:v>MyPCBench source</x:v>
       </x:c>
       <x:c r="D26" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E26" s="16" t="str">
-        <x:v>supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F26" s="16" t="str">
-        <x:v>https://labs.scale.com/leaderboard/rli</x:v>
+        <x:v>https://github.com/ljang0/MyPCBench/blob/main/README.md</x:v>
       </x:c>
       <x:c r="G26" s="16" t="str"/>
     </x:row>
     <x:row r="27" ht="54" hidden="0" customHeight="1">
       <x:c r="A27" s="16" t="str">
-        <x:v>source-022</x:v>
+        <x:v>gate1-hal-cs-princeton-edu-assistantbench-hal-benchmark</x:v>
       </x:c>
       <x:c r="B27" s="16" t="str">
-        <x:v>metr.org</x:v>
+        <x:v>hal.cs.princeton.edu</x:v>
       </x:c>
       <x:c r="C27" s="16" t="str">
-        <x:v>METR Time Horizon source</x:v>
+        <x:v>AssistantBench (HAL) benchmark</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E27" s="16" t="str">
-        <x:v>supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F27" s="16" t="str">
-        <x:v>https://metr.org/time-horizons/</x:v>
+        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
       </x:c>
       <x:c r="G27" s="16" t="str"/>
     </x:row>
-    <x:row r="28" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="28" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A28" s="16" t="str">
-        <x:v>source-023</x:v>
+        <x:v>gate1-labs-scale-com-remote-labor-index-source</x:v>
       </x:c>
       <x:c r="B28" s="16" t="str">
-        <x:v>mypcbench.com</x:v>
+        <x:v>labs.scale.com</x:v>
       </x:c>
       <x:c r="C28" s="16" t="str">
-        <x:v>MyPCBench benchmark</x:v>
+        <x:v>Remote Labor Index source</x:v>
       </x:c>
       <x:c r="D28" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E28" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>Professional capability, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F28" s="16" t="str">
-        <x:v>https://mypcbench.com/</x:v>
+        <x:v>https://labs.scale.com/leaderboard/rli</x:v>
       </x:c>
       <x:c r="G28" s="16" t="str"/>
     </x:row>
-    <x:row r="29" ht="54" hidden="0" customHeight="1">
+    <x:row r="29" ht="129.60000610351562" hidden="0" customHeight="1">
       <x:c r="A29" s="16" t="str">
-        <x:v>source-024</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="B29" s="16" t="str">
-        <x:v>mypcbench.pages.dev</x:v>
+        <x:v>metr.org</x:v>
       </x:c>
       <x:c r="C29" s="16" t="str">
-        <x:v>MyPCBench source</x:v>
+        <x:v>METR Time Horizon source</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E29" s="16" t="str">
-        <x:v>supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>Capability, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation, task-horizon observations</x:v>
       </x:c>
       <x:c r="F29" s="16" t="str">
-        <x:v>https://mypcbench.pages.dev/leaderboard.html</x:v>
+        <x:v>https://metr.org/time-horizons/</x:v>
       </x:c>
       <x:c r="G29" s="16" t="str"/>
     </x:row>
-    <x:row r="30" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="30" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A30" s="16" t="str">
-        <x:v>source-025</x:v>
+        <x:v>gate1-mypcbench-com-mypcbench-benchmark</x:v>
       </x:c>
       <x:c r="B30" s="16" t="str">
-        <x:v>omegause-officeval.github.io</x:v>
+        <x:v>mypcbench.com</x:v>
       </x:c>
       <x:c r="C30" s="16" t="str">
-        <x:v>OmegaUse-OfficeVal benchmark</x:v>
+        <x:v>MyPCBench benchmark</x:v>
       </x:c>
       <x:c r="D30" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E30" s="16" t="str">
-        <x:v>forecast benchmark</x:v>
+        <x:v>capability evidence, forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F30" s="16" t="str">
-        <x:v>https://omegause-officeval.github.io/</x:v>
+        <x:v>https://mypcbench.com/</x:v>
       </x:c>
       <x:c r="G30" s="16" t="str"/>
     </x:row>
-    <x:row r="31" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="31" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A31" s="16" t="str">
-        <x:v>source-026</x:v>
+        <x:v>gate1-mypcbench-pages-dev-mypcbench-source</x:v>
       </x:c>
       <x:c r="B31" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>mypcbench.pages.dev</x:v>
       </x:c>
       <x:c r="C31" s="16" t="str">
-        <x:v>GDPval benchmark</x:v>
+        <x:v>MyPCBench source</x:v>
       </x:c>
       <x:c r="D31" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E31" s="16" t="str">
-        <x:v>forecast benchmark</x:v>
+        <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F31" s="16" t="str">
-        <x:v>https://openai.com/index/gdpval/</x:v>
+        <x:v>https://mypcbench.pages.dev/leaderboard.html</x:v>
       </x:c>
       <x:c r="G31" s="16" t="str"/>
     </x:row>
-    <x:row r="32" ht="54" hidden="0" customHeight="1">
+    <x:row r="32" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A32" s="16" t="str">
-        <x:v>source-027</x:v>
+        <x:v>gate1-omegause-officeval-github-io-omegause-officeval-benchmark</x:v>
       </x:c>
       <x:c r="B32" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>omegause-officeval.github.io</x:v>
       </x:c>
       <x:c r="C32" s="16" t="str">
-        <x:v>Agents Last Exam source</x:v>
+        <x:v>OmegaUse-OfficeVal benchmark</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E32" s="16" t="str">
-        <x:v>supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark</x:v>
       </x:c>
       <x:c r="F32" s="16" t="str">
-        <x:v>https://openai.com/index/gpt-5-6/</x:v>
+        <x:v>https://omegause-officeval.github.io/</x:v>
       </x:c>
       <x:c r="G32" s="16" t="str"/>
     </x:row>
-    <x:row r="33" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="33" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A33" s="16" t="str">
-        <x:v>source-028</x:v>
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
       </x:c>
       <x:c r="B33" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C33" s="16" t="str">
-        <x:v>OSWorld observation source</x:v>
+        <x:v>Agents Last Exam source</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E33" s="16" t="str">
-        <x:v>supporting evaluation observation</x:v>
+        <x:v>AI R&amp;D, Capability velocity, Computer use, release metadata, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F33" s="16" t="str">
-        <x:v>https://openai.com/index/introducing-gpt-5-4/</x:v>
+        <x:v>https://openai.com/index/gpt-5-6/</x:v>
       </x:c>
       <x:c r="G33" s="16" t="str"/>
     </x:row>
-    <x:row r="34" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="34" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A34" s="16" t="str">
-        <x:v>source-029</x:v>
+        <x:v>gate1-openai-com-gdpval-benchmark</x:v>
       </x:c>
       <x:c r="B34" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C34" s="16" t="str">
-        <x:v>OSWorld observation source</x:v>
+        <x:v>GDPval benchmark</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
-        <x:v>supporting evaluation observation</x:v>
+        <x:v>forecast benchmark</x:v>
       </x:c>
       <x:c r="F34" s="16" t="str">
-        <x:v>https://openai.com/index/introducing-gpt-5-5/</x:v>
+        <x:v>https://openai.com/index/gdpval/</x:v>
       </x:c>
       <x:c r="G34" s="16" t="str"/>
     </x:row>
-    <x:row r="35" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="35" ht="54" hidden="0" customHeight="1">
       <x:c r="A35" s="16" t="str">
-        <x:v>source-030</x:v>
+        <x:v>gate1-openai-com-osworld-observation-source</x:v>
       </x:c>
       <x:c r="B35" s="16" t="str">
-        <x:v>os-world.github.io</x:v>
+        <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C35" s="16" t="str">
-        <x:v>OSWorld source</x:v>
+        <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E35" s="16" t="str">
-        <x:v>supporting evaluation</x:v>
+        <x:v>release metadata, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F35" s="16" t="str">
-        <x:v>https://os-world.github.io/</x:v>
+        <x:v>https://openai.com/index/introducing-gpt-5-4/</x:v>
       </x:c>
       <x:c r="G35" s="16" t="str"/>
     </x:row>
-    <x:row r="36" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="36" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A36" s="16" t="str">
-        <x:v>source-031</x:v>
+        <x:v>gate1-openai-com-osworld-observation-source-2</x:v>
       </x:c>
       <x:c r="B36" s="16" t="str">
-        <x:v>osworld-v2.xlang.ai</x:v>
+        <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C36" s="16" t="str">
-        <x:v>OSWorld source</x:v>
+        <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D36" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
-        <x:v>supporting evaluation</x:v>
+        <x:v>Capability velocity, release metadata, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F36" s="16" t="str">
-        <x:v>https://osworld-v2.xlang.ai/</x:v>
+        <x:v>https://openai.com/index/introducing-gpt-5-5/</x:v>
       </x:c>
       <x:c r="G36" s="16" t="str"/>
     </x:row>
     <x:row r="37" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A37" s="16" t="str">
-        <x:v>source-032</x:v>
+        <x:v>gate1-os-world-github-io-osworld-source</x:v>
       </x:c>
       <x:c r="B37" s="16" t="str">
-        <x:v>taubench.com</x:v>
+        <x:v>os-world.github.io</x:v>
       </x:c>
       <x:c r="C37" s="16" t="str">
-        <x:v>tau3 Banking benchmark</x:v>
+        <x:v>OSWorld source</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>supporting evaluation</x:v>
       </x:c>
       <x:c r="F37" s="16" t="str">
-        <x:v>https://taubench.com/leaderboard/</x:v>
+        <x:v>https://os-world.github.io/</x:v>
       </x:c>
       <x:c r="G37" s="16" t="str"/>
     </x:row>
-    <x:row r="38" ht="54" hidden="0" customHeight="1">
+    <x:row r="38" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A38" s="16" t="str">
-        <x:v>source-033</x:v>
+        <x:v>gate1-osworld-v2-xlang-ai-osworld-source</x:v>
       </x:c>
       <x:c r="B38" s="16" t="str">
-        <x:v>taubench.com</x:v>
+        <x:v>osworld-v2.xlang.ai</x:v>
       </x:c>
       <x:c r="C38" s="16" t="str">
-        <x:v>tau3 Banking source</x:v>
+        <x:v>OSWorld source</x:v>
       </x:c>
       <x:c r="D38" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
-        <x:v>supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>Computer use, capability evidence, supporting evaluation</x:v>
       </x:c>
       <x:c r="F38" s="16" t="str">
-        <x:v>https://taubench.com/leaderboard/?benchmark=knowledge</x:v>
+        <x:v>https://osworld-v2.xlang.ai/</x:v>
       </x:c>
       <x:c r="G38" s="16" t="str"/>
     </x:row>
-    <x:row r="39" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="39" ht="54" hidden="0" customHeight="1">
       <x:c r="A39" s="16" t="str">
-        <x:v>source-034</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="B39" s="16" t="str">
-        <x:v>the-agent-company.com</x:v>
+        <x:v>remotelabor.ai</x:v>
       </x:c>
       <x:c r="C39" s="16" t="str">
-        <x:v>TheAgentCompany observation source</x:v>
+        <x:v>Remote Labor Index benchmark</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
-        <x:v>forecast observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F39" s="16" t="str">
-        <x:v>https://the-agent-company.com/</x:v>
+        <x:v>https://www.remotelabor.ai/</x:v>
       </x:c>
       <x:c r="G39" s="16" t="str"/>
     </x:row>
-    <x:row r="40" ht="75.5999984741211" hidden="0" customHeight="1">
+    <x:row r="40" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A40" s="16" t="str">
-        <x:v>source-035</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="B40" s="16" t="str">
-        <x:v>www-cdn.anthropic.com</x:v>
+        <x:v>taubench.com</x:v>
       </x:c>
       <x:c r="C40" s="16" t="str">
-        <x:v>OSWorld observation source</x:v>
+        <x:v>tau3 Banking benchmark</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E40" s="16" t="str">
-        <x:v>supporting evaluation observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F40" s="16" t="str">
-        <x:v>https://www-cdn.anthropic.com/6a5fa276ac68b9aeb0c8b6af5fa36326e0e166dd.pdf</x:v>
+        <x:v>https://taubench.com/leaderboard/</x:v>
       </x:c>
       <x:c r="G40" s="16" t="str"/>
     </x:row>
-    <x:row r="41" ht="54" hidden="0" customHeight="1">
+    <x:row r="41" ht="108" hidden="0" customHeight="1">
       <x:c r="A41" s="16" t="str">
-        <x:v>source-036</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
       </x:c>
       <x:c r="B41" s="16" t="str">
-        <x:v>anthropic.com</x:v>
+        <x:v>taubench.com</x:v>
       </x:c>
       <x:c r="C41" s="16" t="str">
-        <x:v>OSWorld observation source</x:v>
+        <x:v>tau3 Banking source</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
-        <x:v>supporting evaluation observation</x:v>
+        <x:v>Business, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F41" s="16" t="str">
-        <x:v>https://www.anthropic.com/news/claude-sonnet-4-5</x:v>
+        <x:v>https://taubench.com/leaderboard/?benchmark=knowledge</x:v>
       </x:c>
       <x:c r="G41" s="16" t="str"/>
     </x:row>
-    <x:row r="42" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="42" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A42" s="16" t="str">
-        <x:v>source-037</x:v>
+        <x:v>gate1-the-agent-company-com-theagentcompany-observation-source</x:v>
       </x:c>
       <x:c r="B42" s="16" t="str">
-        <x:v>remotelabor.ai</x:v>
+        <x:v>the-agent-company.com</x:v>
       </x:c>
       <x:c r="C42" s="16" t="str">
-        <x:v>Remote Labor Index benchmark</x:v>
+        <x:v>TheAgentCompany observation source</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>forecast observation</x:v>
       </x:c>
       <x:c r="F42" s="16" t="str">
-        <x:v>https://www.remotelabor.ai/</x:v>
+        <x:v>https://the-agent-company.com/</x:v>
       </x:c>
       <x:c r="G42" s="16" t="str"/>
     </x:row>
-    <x:row r="43" ht="54" hidden="0" customHeight="1">
+    <x:row r="43" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A43" s="16" t="str">
-        <x:v>source-001</x:v>
+        <x:v>gate1-www-cdn-anthropic-com-osworld-observation-source</x:v>
       </x:c>
       <x:c r="B43" s="16" t="str">
-        <x:v>METR</x:v>
+        <x:v>www-cdn.anthropic.com</x:v>
       </x:c>
       <x:c r="C43" s="16" t="str">
-        <x:v>Task-horizon benchmark results</x:v>
+        <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E43" s="16" t="str">
+        <x:v>supporting evaluation observation</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="str">
+        <x:v>https://www-cdn.anthropic.com/6a5fa276ac68b9aeb0c8b6af5fa36326e0e166dd.pdf</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="str"/>
+    </x:row>
+    <x:row r="44" ht="54" hidden="0" customHeight="1">
+      <x:c r="A44" s="16" t="str">
+        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
+      </x:c>
+      <x:c r="B44" s="16" t="str">
+        <x:v>METR</x:v>
+      </x:c>
+      <x:c r="C44" s="16" t="str">
+        <x:v>Task-horizon benchmark results</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="str">
         <x:v>published trend estimate</x:v>
       </x:c>
-      <x:c r="F43" s="16" t="str">
+      <x:c r="F44" s="16" t="str">
         <x:v>https://metr.org/assets/benchmark_results_1_1.yaml</x:v>
       </x:c>
-      <x:c r="G43" s="16" t="str"/>
+      <x:c r="G44" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5526,7 +5549,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f845f8d0a7f4fda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c1e17ff33894986"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
+++ b/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R43c45543a68a4e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R711523ac9d67488e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="Rc49a277016d54c19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="Rb78d466b9b494181"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R081149873d024e8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R8e3da8bd9a904a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R92ca18988d4349b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R9b953f0147934030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="Rdbf41fc1baa4406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R0050d58b9b5c437e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R18f7bf643a6644ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R199cddbd754944f9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,7 +432,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R751f1ccd780f4cd8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd07637d622bc49a0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -458,7 +458,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CapabilityBenchmarksTable" displayName="CapabilityBenchmarksTable" ref="A5:P28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CapabilityBenchmarksTable" displayName="CapabilityBenchmarksTable" ref="A5:P29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Category"/>
     <x:tableColumn id="2" name="ID"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CapabilityObservationsTable" displayName="CapabilityObservationsTable" ref="A5:J43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CapabilityObservationsTable" displayName="CapabilityObservationsTable" ref="A5:J44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Observation ID"/>
     <x:tableColumn id="2" name="Benchmark ID"/>
@@ -532,7 +532,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Source ID"/>
     <x:tableColumn id="2" name="Publisher"/>
@@ -833,7 +833,7 @@
         <x:v>Current capability</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
-        <x:v>0.45660533834944794</x:v>
+        <x:v>0.45165059809758934</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
         <x:v>Confidence-weighted score</x:v>
@@ -860,12 +860,12 @@
       <x:c r="G8" s="16"/>
       <x:c r="H8" s="16"/>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+    <x:row r="9" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
         <x:v>GPA</x:v>
       </x:c>
       <x:c r="B9" s="18" t="n">
-        <x:v>0.5796055796055796</x:v>
+        <x:v>0.5641332752613242</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str">
         <x:v>0–4</x:v>
@@ -884,7 +884,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="C10" s="16" t="n">
-        <x:v>0.4782608695652174</x:v>
+        <x:v>0.47222222222222227</x:v>
       </x:c>
       <x:c r="D10" s="16"/>
       <x:c r="E10" s="16"/>
@@ -897,7 +897,7 @@
         <x:v>Economic gap velocity</x:v>
       </x:c>
       <x:c r="B11" s="18" t="n">
-        <x:v>0.1206064198155199</x:v>
+        <x:v>0.11844032433366539</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str">
         <x:v>failure-gap halvings / quarter</x:v>
@@ -971,22 +971,22 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="B15" s="22" t="n">
-        <x:v>0.5063285714285714</x:v>
+        <x:v>0.49453749999999996</x:v>
       </x:c>
       <x:c r="C15" s="21" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D15" s="23" t="n">
-        <x:v>0.625</x:v>
+        <x:v>0.5925925925925926</x:v>
       </x:c>
       <x:c r="E15" s="21" t="n">
-        <x:v>0.42857142857142855</x:v>
+        <x:v>0.375</x:v>
       </x:c>
       <x:c r="F15" s="21" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G15" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="H15" s="24" t="n">
         <x:v>0.23660304317034014</x:v>
@@ -1049,7 +1049,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a11b3d030c8410a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3381f692a524ed5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2323,6 +2323,56 @@
         <x:v>Governance/reliability emphasis; one current frontier point.</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="140.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A29" s="16" t="str">
+        <x:v>Operational execution</x:v>
+      </x:c>
+      <x:c r="B29" s="16" t="str">
+        <x:v>OPS-09</x:v>
+      </x:c>
+      <x:c r="C29" s="16" t="str">
+        <x:v>WeaveBench</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="str">
+        <x:v>Trajectory-audited pass rate on long-horizon hybrid-interface tasks</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="str">
+        <x:v>The source reports PassRate as a percentage; divide by 100 to obtain the bounded 0–1 score</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="str">
+        <x:v>Graded</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="H29" s="17" t="n">
+        <x:v>0.412</x:v>
+      </x:c>
+      <x:c r="I29" s="16" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J29" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L29" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M29" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N29" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="16" t="str">
+        <x:v>gate1-arxiv-org-weavebench</x:v>
+      </x:c>
+      <x:c r="P29" s="16" t="str">
+        <x:v>114 tasks across eight real-world work domains; the selected frontier result is the best published model–runtime pairing in Table 3.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:P2"/>
@@ -2330,7 +2380,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15c438678ec047a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ab0459da4345cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3640,6 +3690,38 @@
         <x:v>One current frontier point.</x:v>
       </x:c>
     </x:row>
+    <x:row r="44" ht="183.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A44" s="16" t="str">
+        <x:v>forecast-observation-039</x:v>
+      </x:c>
+      <x:c r="B44" s="16" t="str">
+        <x:v>OPS-09</x:v>
+      </x:c>
+      <x:c r="C44" s="25" t="str">
+        <x:v>2026-04-16</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="n">
+        <x:v>0.412</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="str">
+        <x:v>Claude Opus 4.7 + Claude Code</x:v>
+      </x:c>
+      <x:c r="H44" s="16" t="str">
+        <x:v>WeaveBench trajectory-audited PassRate; 41.2% reported in Table 3</x:v>
+      </x:c>
+      <x:c r="I44" s="16" t="str">
+        <x:v>gate1-arxiv-org-weavebench</x:v>
+      </x:c>
+      <x:c r="J44" s="16" t="str">
+        <x:v>Claude Opus 4.7's release date assigns the frontier point to 2026-Q2; the paper's 6 July revision is the observation date. The paired harness is part of the measured system.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J2"/>
@@ -3647,7 +3729,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R789aa06094014b2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f2e14c32b7446f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3777,7 +3859,7 @@
         <x:v>2024-12-31</x:v>
       </x:c>
       <x:c r="C9" s="17" t="n">
-        <x:v>0.24</x:v>
+        <x:v>0.24000000000000002</x:v>
       </x:c>
       <x:c r="D9" s="17"/>
       <x:c r="E9" s="17" t="n">
@@ -3794,7 +3876,7 @@
         <x:v>2025-03-31</x:v>
       </x:c>
       <x:c r="C10" s="17" t="n">
-        <x:v>0.24</x:v>
+        <x:v>0.24000000000000002</x:v>
       </x:c>
       <x:c r="D10" s="17"/>
       <x:c r="E10" s="17" t="n">
@@ -3803,7 +3885,7 @@
       <x:c r="F10" s="17"/>
       <x:c r="G10" s="17"/>
     </x:row>
-    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>2025-Q2</x:v>
       </x:c>
@@ -3811,7 +3893,7 @@
         <x:v>2025-06-30</x:v>
       </x:c>
       <x:c r="C11" s="17" t="n">
-        <x:v>0.2990130434782609</x:v>
+        <x:v>0.30067600000000005</x:v>
       </x:c>
       <x:c r="D11" s="17"/>
       <x:c r="E11" s="17" t="n">
@@ -3830,7 +3912,7 @@
         <x:v>2025-09-30</x:v>
       </x:c>
       <x:c r="C12" s="17" t="n">
-        <x:v>0.2705225806451613</x:v>
+        <x:v>0.2687088235294118</x:v>
       </x:c>
       <x:c r="D12" s="17"/>
       <x:c r="E12" s="17" t="n">
@@ -3851,7 +3933,7 @@
         <x:v>2025-12-31</x:v>
       </x:c>
       <x:c r="C13" s="17" t="n">
-        <x:v>0.28586451612903224</x:v>
+        <x:v>0.28385882352941183</x:v>
       </x:c>
       <x:c r="D13" s="17"/>
       <x:c r="E13" s="17" t="n">
@@ -3872,7 +3954,7 @@
         <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="C14" s="17" t="n">
-        <x:v>0.43162401795735134</x:v>
+        <x:v>0.43123729674796746</x:v>
       </x:c>
       <x:c r="D14" s="17" t="n">
         <x:v>0.3636316666666667</x:v>
@@ -3895,13 +3977,13 @@
         <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="C15" s="17" t="n">
-        <x:v>0.46116062691076226</x:v>
+        <x:v>0.4584121401419464</x:v>
       </x:c>
       <x:c r="D15" s="17" t="n">
         <x:v>0.44483507740620487</x:v>
       </x:c>
       <x:c r="E15" s="17" t="n">
-        <x:v>0.4717571428571428</x:v>
+        <x:v>0.46428749999999996</x:v>
       </x:c>
       <x:c r="F15" s="17" t="n">
         <x:v>0.49477499999999996</x:v>
@@ -3918,13 +4000,13 @@
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="C16" s="17" t="n">
-        <x:v>0.45660533834944794</x:v>
+        <x:v>0.45165059809758934</x:v>
       </x:c>
       <x:c r="D16" s="17" t="n">
         <x:v>0.38254856862232545</x:v>
       </x:c>
       <x:c r="E16" s="17" t="n">
-        <x:v>0.5063285714285714</x:v>
+        <x:v>0.49453749999999996</x:v>
       </x:c>
       <x:c r="F16" s="17" t="n">
         <x:v>0.49477499999999996</x:v>
@@ -3941,19 +4023,19 @@
         <x:v>2026-12-31</x:v>
       </x:c>
       <x:c r="C17" s="17" t="n">
-        <x:v>0.5069516309988237</x:v>
+        <x:v>0.5015863697066921</x:v>
       </x:c>
       <x:c r="D17" s="17" t="n">
-        <x:v>0.4397563268306439</x:v>
+        <x:v>0.43877715846704063</x:v>
       </x:c>
       <x:c r="E17" s="17" t="n">
-        <x:v>0.5520679354408162</x:v>
+        <x:v>0.5405677498483082</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
-        <x:v>0.5415848189315059</x:v>
+        <x:v>0.540783621766425</x:v>
       </x:c>
       <x:c r="G17" s="17" t="n">
-        <x:v>0.4837186639062336</x:v>
+        <x:v>0.4828163309121596</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -3964,19 +4046,19 @@
         <x:v>2027-03-31</x:v>
       </x:c>
       <x:c r="C18" s="17" t="n">
-        <x:v>0.5673035430993775</x:v>
+        <x:v>0.5615680771328883</x:v>
       </x:c>
       <x:c r="D18" s="17" t="n">
-        <x:v>0.5083333246341348</x:v>
+        <x:v>0.5063176554272025</x:v>
       </x:c>
       <x:c r="E18" s="17" t="n">
-        <x:v>0.6068973564204667</x:v>
+        <x:v>0.5958582337673388</x:v>
       </x:c>
       <x:c r="F18" s="17" t="n">
-        <x:v>0.5976974327293203</x:v>
+        <x:v>0.5960481265278903</x:v>
       </x:c>
       <x:c r="G18" s="17" t="n">
-        <x:v>0.5469144227284541</x:v>
+        <x:v>0.5450569231419062</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -3987,19 +4069,19 @@
         <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="C19" s="17" t="n">
-        <x:v>0.6368959313305393</x:v>
+        <x:v>0.6309224397345665</x:v>
       </x:c>
       <x:c r="D19" s="17" t="n">
-        <x:v>0.5874101407409149</x:v>
+        <x:v>0.5844119331240532</x:v>
       </x:c>
       <x:c r="E19" s="17" t="n">
-        <x:v>0.6701217053847245</x:v>
+        <x:v>0.6597883290361504</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
-        <x:v>0.6624014440550342</x:v>
+        <x:v>0.6599481831734086</x:v>
       </x:c>
       <x:c r="G19" s="17" t="n">
-        <x:v>0.6197860788110534</x:v>
+        <x:v>0.6170231406317374</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4010,19 +4092,19 @@
         <x:v>2027-09-30</x:v>
       </x:c>
       <x:c r="C20" s="17" t="n">
-        <x:v>0.7130777020429602</x:v>
+        <x:v>0.7071214661713452</x:v>
       </x:c>
       <x:c r="D20" s="17" t="n">
-        <x:v>0.6739743760895377</x:v>
+        <x:v>0.6702134271837716</x:v>
       </x:c>
       <x:c r="E20" s="17" t="n">
-        <x:v>0.7393324765431778</x:v>
+        <x:v>0.7300277608001164</x:v>
       </x:c>
       <x:c r="F20" s="17" t="n">
-        <x:v>0.7332319799839943</x:v>
+        <x:v>0.7301546117669241</x:v>
       </x:c>
       <x:c r="G20" s="17" t="n">
-        <x:v>0.6995576161331936</x:v>
+        <x:v>0.696091788995754</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4033,19 +4115,19 @@
         <x:v>2027-12-31</x:v>
       </x:c>
       <x:c r="C21" s="17" t="n">
-        <x:v>0.7908646163430303</x:v>
+        <x:v>0.785307273130474</x:v>
       </x:c>
       <x:c r="D21" s="17" t="n">
-        <x:v>0.7623625126941985</x:v>
+        <x:v>0.7582520723615275</x:v>
       </x:c>
       <x:c r="E21" s="17" t="n">
-        <x:v>0.810001512907104</x:v>
+        <x:v>0.8020985851875222</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:v>0.8055549094277401</x:v>
+        <x:v>0.8021915724734591</x:v>
       </x:c>
       <x:c r="G21" s="17" t="n">
-        <x:v>0.781009933127585</x:v>
+        <x:v>0.7772220391655169</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4056,19 +4138,19 @@
         <x:v>2028-03-31</x:v>
       </x:c>
       <x:c r="C22" s="17" t="n">
-        <x:v>0.8632288948971791</x:v>
+        <x:v>0.8585194965024904</x:v>
       </x:c>
       <x:c r="D22" s="17" t="n">
-        <x:v>0.8445889873614943</x:v>
+        <x:v>0.8406903716745077</x:v>
       </x:c>
       <x:c r="E22" s="17" t="n">
-        <x:v>0.875744110856999</x:v>
+        <x:v>0.869584814451797</x:v>
       </x:c>
       <x:c r="F22" s="17" t="n">
-        <x:v>0.8728361052331195</x:v>
+        <x:v>0.8696460922054736</x:v>
       </x:c>
       <x:c r="G22" s="17" t="n">
-        <x:v>0.8567840939732693</x:v>
+        <x:v>0.8531914027708731</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4079,19 +4161,19 @@
         <x:v>2028-06-30</x:v>
       </x:c>
       <x:c r="C23" s="17" t="n">
-        <x:v>0.9226760137122777</x:v>
+        <x:v>0.9191900534722246</x:v>
       </x:c>
       <x:c r="D23" s="17" t="n">
-        <x:v>0.912137881746391</x:v>
+        <x:v>0.909006525789121</x:v>
       </x:c>
       <x:c r="E23" s="17" t="n">
-        <x:v>0.929751531501927</x:v>
+        <x:v>0.9255102723694668</x:v>
       </x:c>
       <x:c r="F23" s="17" t="n">
-        <x:v>0.9281074811243533</x:v>
+        <x:v>0.9255452726124369</x:v>
       </x:c>
       <x:c r="G23" s="17" t="n">
-        <x:v>0.9190324246815913</x:v>
+        <x:v>0.9161467863159515</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4102,19 +4184,19 @@
         <x:v>2028-09-30</x:v>
       </x:c>
       <x:c r="C24" s="17" t="n">
-        <x:v>0.964050064411599</x:v>
+        <x:v>0.9619089891630892</x:v>
       </x:c>
       <x:c r="D24" s="17" t="n">
-        <x:v>0.9591506123323175</x:v>
+        <x:v>0.957108826806816</x:v>
       </x:c>
       <x:c r="E24" s="17" t="n">
-        <x:v>0.9673396569559614</x:v>
+        <x:v>0.9648881215205617</x:v>
       </x:c>
       <x:c r="F24" s="17" t="n">
-        <x:v>0.9665752951063544</x:v>
+        <x:v>0.9649046194232525</x:v>
       </x:c>
       <x:c r="G24" s="17" t="n">
-        <x:v>0.96235606495228</x:v>
+        <x:v>0.960474498395429</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4125,19 +4207,19 @@
         <x:v>2028-12-31</x:v>
       </x:c>
       <x:c r="C25" s="17" t="n">
-        <x:v>0.98714656448233</x:v>
+        <x:v>0.9861271409811129</x:v>
       </x:c>
       <x:c r="D25" s="17" t="n">
-        <x:v>0.9853948286212713</x:v>
+        <x:v>0.9843789076270163</x:v>
       </x:c>
       <x:c r="E25" s="17" t="n">
-        <x:v>0.9883227158427239</x:v>
+        <x:v>0.987212149813532</x:v>
       </x:c>
       <x:c r="F25" s="17" t="n">
-        <x:v>0.9880494281278703</x:v>
+        <x:v>0.987218158398579</x:v>
       </x:c>
       <x:c r="G25" s="17" t="n">
-        <x:v>0.9865408968375637</x:v>
+        <x:v>0.9856046951928179</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4146,9 +4228,9 @@
     <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17f988c1ac974d05"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0378b56330fd4218"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R347262acece241b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R361a0ce7a1414cee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4648,7 +4730,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda73b4c901c345de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9b7ff8a0cdf4bd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4952,57 +5034,57 @@
       </x:c>
       <x:c r="G16" s="16" t="str"/>
     </x:row>
-    <x:row r="17" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="17" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A17" s="16" t="str">
-        <x:v>gate1-arxiv-org-workarena-benchmark</x:v>
+        <x:v>gate1-arxiv-org-weavebench</x:v>
       </x:c>
       <x:c r="B17" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C17" s="16" t="str">
-        <x:v>WorkArena++ benchmark</x:v>
+        <x:v>WeaveBench</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
-        <x:v>forecast benchmark</x:v>
+        <x:v>capability evidence</x:v>
       </x:c>
       <x:c r="F17" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2407.05291</x:v>
+        <x:v>https://arxiv.org/abs/2606.09426</x:v>
       </x:c>
       <x:c r="G17" s="16" t="str"/>
     </x:row>
     <x:row r="18" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A18" s="16" t="str">
-        <x:v>gate1-arxiv-org-yc-bench-benchmark</x:v>
+        <x:v>gate1-arxiv-org-workarena-benchmark</x:v>
       </x:c>
       <x:c r="B18" s="16" t="str">
         <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C18" s="16" t="str">
-        <x:v>YC-Bench benchmark</x:v>
+        <x:v>WorkArena++ benchmark</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E18" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>forecast benchmark</x:v>
       </x:c>
       <x:c r="F18" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2604.01212</x:v>
+        <x:v>https://arxiv.org/abs/2407.05291</x:v>
       </x:c>
       <x:c r="G18" s="16" t="str"/>
     </x:row>
     <x:row r="19" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A19" s="16" t="str">
-        <x:v>gate1-ceobench-com-ceo-bench-benchmark</x:v>
+        <x:v>gate1-arxiv-org-yc-bench-benchmark</x:v>
       </x:c>
       <x:c r="B19" s="16" t="str">
-        <x:v>ceobench.com</x:v>
+        <x:v>arxiv.org</x:v>
       </x:c>
       <x:c r="C19" s="16" t="str">
-        <x:v>CEO-Bench benchmark</x:v>
+        <x:v>YC-Bench benchmark</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5011,63 +5093,63 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F19" s="16" t="str">
-        <x:v>https://ceobench.com/</x:v>
+        <x:v>https://arxiv.org/abs/2604.01212</x:v>
       </x:c>
       <x:c r="G19" s="16" t="str"/>
     </x:row>
-    <x:row r="20" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="20" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A20" s="16" t="str">
-        <x:v>gate1-diffuse-personal-ai-gate-1-model-harness-capability-calculation-contract</x:v>
+        <x:v>gate1-ceobench-com-ceo-bench-benchmark</x:v>
       </x:c>
       <x:c r="B20" s="16" t="str">
-        <x:v>Diffuse Personal AI</x:v>
+        <x:v>ceobench.com</x:v>
       </x:c>
       <x:c r="C20" s="16" t="str">
-        <x:v>Gate 1 · Model–harness capability calculation contract</x:v>
+        <x:v>CEO-Bench benchmark</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
-        <x:v>methodology, normalization, model configuration</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F20" s="16" t="str">
-        <x:v>https://github.com/buwilliams/diffuse-personal-ai/blob/main/intent/02-model/06-report-card-calculations.md</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="str">
-        <x:v>Holds definitions and assumptions that are authored by the forecast rather than fetched as observations.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="43.20000076293945" hidden="0" customHeight="1">
+        <x:v>https://ceobench.com/</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A21" s="16" t="str">
-        <x:v>gate1-github-com-automationbench-benchmark</x:v>
+        <x:v>gate1-diffuse-personal-ai-gate-1-model-harness-capability-calculation-contract</x:v>
       </x:c>
       <x:c r="B21" s="16" t="str">
-        <x:v>github.com</x:v>
+        <x:v>Diffuse Personal AI</x:v>
       </x:c>
       <x:c r="C21" s="16" t="str">
-        <x:v>AutomationBench benchmark</x:v>
+        <x:v>Gate 1 · Model–harness capability calculation contract</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E21" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>methodology, normalization, model configuration</x:v>
       </x:c>
       <x:c r="F21" s="16" t="str">
-        <x:v>https://github.com/zapier/AutomationBench</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="str"/>
+        <x:v>https://github.com/buwilliams/diffuse-personal-ai/blob/main/intent/02-model/06-report-card-calculations.md</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="str">
+        <x:v>Holds definitions and assumptions that are authored by the forecast rather than fetched as observations.</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A22" s="16" t="str">
-        <x:v>gate1-github-com-claw-eval-benchmark</x:v>
+        <x:v>gate1-github-com-automationbench-benchmark</x:v>
       </x:c>
       <x:c r="B22" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C22" s="16" t="str">
-        <x:v>Claw-Eval benchmark</x:v>
+        <x:v>AutomationBench benchmark</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5076,19 +5158,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F22" s="16" t="str">
-        <x:v>https://github.com/claw-eval/claw-eval</x:v>
+        <x:v>https://github.com/zapier/AutomationBench</x:v>
       </x:c>
       <x:c r="G22" s="16" t="str"/>
     </x:row>
     <x:row r="23" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A23" s="16" t="str">
-        <x:v>gate1-github-com-clawbench-benchmark</x:v>
+        <x:v>gate1-github-com-claw-eval-benchmark</x:v>
       </x:c>
       <x:c r="B23" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C23" s="16" t="str">
-        <x:v>ClawBench benchmark</x:v>
+        <x:v>Claw-Eval benchmark</x:v>
       </x:c>
       <x:c r="D23" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5097,19 +5179,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F23" s="16" t="str">
-        <x:v>https://github.com/TIGER-AI-Lab/ClawBench</x:v>
+        <x:v>https://github.com/claw-eval/claw-eval</x:v>
       </x:c>
       <x:c r="G23" s="16" t="str"/>
     </x:row>
     <x:row r="24" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A24" s="16" t="str">
-        <x:v>gate1-github-com-clawmark-benchmark</x:v>
+        <x:v>gate1-github-com-clawbench-benchmark</x:v>
       </x:c>
       <x:c r="B24" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C24" s="16" t="str">
-        <x:v>ClawMark benchmark</x:v>
+        <x:v>ClawBench benchmark</x:v>
       </x:c>
       <x:c r="D24" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5118,19 +5200,19 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F24" s="16" t="str">
-        <x:v>https://github.com/evolvent-ai/ClawMark</x:v>
+        <x:v>https://github.com/TIGER-AI-Lab/ClawBench</x:v>
       </x:c>
       <x:c r="G24" s="16" t="str"/>
     </x:row>
-    <x:row r="25" ht="54" hidden="0" customHeight="1">
+    <x:row r="25" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A25" s="16" t="str">
-        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
+        <x:v>gate1-github-com-clawmark-benchmark</x:v>
       </x:c>
       <x:c r="B25" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C25" s="16" t="str">
-        <x:v>Commerce Agent Bench benchmark</x:v>
+        <x:v>ClawMark benchmark</x:v>
       </x:c>
       <x:c r="D25" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5139,223 +5221,223 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F25" s="16" t="str">
-        <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
+        <x:v>https://github.com/evolvent-ai/ClawMark</x:v>
       </x:c>
       <x:c r="G25" s="16" t="str"/>
     </x:row>
-    <x:row r="26" ht="75.5999984741211" hidden="0" customHeight="1">
+    <x:row r="26" ht="54" hidden="0" customHeight="1">
       <x:c r="A26" s="16" t="str">
-        <x:v>gate1-github-com-mypcbench-source</x:v>
+        <x:v>gate1-github-com-commerce-agent-bench-benchmark</x:v>
       </x:c>
       <x:c r="B26" s="16" t="str">
         <x:v>github.com</x:v>
       </x:c>
       <x:c r="C26" s="16" t="str">
-        <x:v>MyPCBench source</x:v>
+        <x:v>Commerce Agent Bench benchmark</x:v>
       </x:c>
       <x:c r="D26" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E26" s="16" t="str">
-        <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F26" s="16" t="str">
-        <x:v>https://github.com/ljang0/MyPCBench/blob/main/README.md</x:v>
+        <x:v>https://github.com/Accio-org/CommerceAgentBench</x:v>
       </x:c>
       <x:c r="G26" s="16" t="str"/>
     </x:row>
-    <x:row r="27" ht="54" hidden="0" customHeight="1">
+    <x:row r="27" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A27" s="16" t="str">
-        <x:v>gate1-hal-cs-princeton-edu-assistantbench-hal-benchmark</x:v>
+        <x:v>gate1-github-com-mypcbench-source</x:v>
       </x:c>
       <x:c r="B27" s="16" t="str">
-        <x:v>hal.cs.princeton.edu</x:v>
+        <x:v>github.com</x:v>
       </x:c>
       <x:c r="C27" s="16" t="str">
-        <x:v>AssistantBench (HAL) benchmark</x:v>
+        <x:v>MyPCBench source</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E27" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F27" s="16" t="str">
-        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
+        <x:v>https://github.com/ljang0/MyPCBench/blob/main/README.md</x:v>
       </x:c>
       <x:c r="G27" s="16" t="str"/>
     </x:row>
-    <x:row r="28" ht="75.5999984741211" hidden="0" customHeight="1">
+    <x:row r="28" ht="54" hidden="0" customHeight="1">
       <x:c r="A28" s="16" t="str">
-        <x:v>gate1-labs-scale-com-remote-labor-index-source</x:v>
+        <x:v>gate1-hal-cs-princeton-edu-assistantbench-hal-benchmark</x:v>
       </x:c>
       <x:c r="B28" s="16" t="str">
-        <x:v>labs.scale.com</x:v>
+        <x:v>hal.cs.princeton.edu</x:v>
       </x:c>
       <x:c r="C28" s="16" t="str">
-        <x:v>Remote Labor Index source</x:v>
+        <x:v>AssistantBench (HAL) benchmark</x:v>
       </x:c>
       <x:c r="D28" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E28" s="16" t="str">
-        <x:v>Professional capability, supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F28" s="16" t="str">
-        <x:v>https://labs.scale.com/leaderboard/rli</x:v>
+        <x:v>https://hal.cs.princeton.edu/assistantbench</x:v>
       </x:c>
       <x:c r="G28" s="16" t="str"/>
     </x:row>
-    <x:row r="29" ht="129.60000610351562" hidden="0" customHeight="1">
+    <x:row r="29" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A29" s="16" t="str">
-        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+        <x:v>gate1-labs-scale-com-remote-labor-index-source</x:v>
       </x:c>
       <x:c r="B29" s="16" t="str">
-        <x:v>metr.org</x:v>
+        <x:v>labs.scale.com</x:v>
       </x:c>
       <x:c r="C29" s="16" t="str">
-        <x:v>METR Time Horizon source</x:v>
+        <x:v>Remote Labor Index source</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E29" s="16" t="str">
-        <x:v>Capability, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation, task-horizon observations</x:v>
+        <x:v>Professional capability, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F29" s="16" t="str">
-        <x:v>https://metr.org/time-horizons/</x:v>
+        <x:v>https://labs.scale.com/leaderboard/rli</x:v>
       </x:c>
       <x:c r="G29" s="16" t="str"/>
     </x:row>
-    <x:row r="30" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="30" ht="129.60000610351562" hidden="0" customHeight="1">
       <x:c r="A30" s="16" t="str">
-        <x:v>gate1-mypcbench-com-mypcbench-benchmark</x:v>
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
       </x:c>
       <x:c r="B30" s="16" t="str">
-        <x:v>mypcbench.com</x:v>
+        <x:v>metr.org</x:v>
       </x:c>
       <x:c r="C30" s="16" t="str">
-        <x:v>MyPCBench benchmark</x:v>
+        <x:v>METR Time Horizon source</x:v>
       </x:c>
       <x:c r="D30" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E30" s="16" t="str">
-        <x:v>capability evidence, forecast benchmark, forecast observation</x:v>
+        <x:v>Capability, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation, task-horizon observations</x:v>
       </x:c>
       <x:c r="F30" s="16" t="str">
-        <x:v>https://mypcbench.com/</x:v>
+        <x:v>https://metr.org/time-horizons/</x:v>
       </x:c>
       <x:c r="G30" s="16" t="str"/>
     </x:row>
-    <x:row r="31" ht="75.5999984741211" hidden="0" customHeight="1">
+    <x:row r="31" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A31" s="16" t="str">
-        <x:v>gate1-mypcbench-pages-dev-mypcbench-source</x:v>
+        <x:v>gate1-mypcbench-com-mypcbench-benchmark</x:v>
       </x:c>
       <x:c r="B31" s="16" t="str">
-        <x:v>mypcbench.pages.dev</x:v>
+        <x:v>mypcbench.com</x:v>
       </x:c>
       <x:c r="C31" s="16" t="str">
-        <x:v>MyPCBench source</x:v>
+        <x:v>MyPCBench benchmark</x:v>
       </x:c>
       <x:c r="D31" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E31" s="16" t="str">
-        <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>capability evidence, forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F31" s="16" t="str">
-        <x:v>https://mypcbench.pages.dev/leaderboard.html</x:v>
+        <x:v>https://mypcbench.com/</x:v>
       </x:c>
       <x:c r="G31" s="16" t="str"/>
     </x:row>
-    <x:row r="32" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="32" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A32" s="16" t="str">
-        <x:v>gate1-omegause-officeval-github-io-omegause-officeval-benchmark</x:v>
+        <x:v>gate1-mypcbench-pages-dev-mypcbench-source</x:v>
       </x:c>
       <x:c r="B32" s="16" t="str">
-        <x:v>omegause-officeval.github.io</x:v>
+        <x:v>mypcbench.pages.dev</x:v>
       </x:c>
       <x:c r="C32" s="16" t="str">
-        <x:v>OmegaUse-OfficeVal benchmark</x:v>
+        <x:v>MyPCBench source</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E32" s="16" t="str">
-        <x:v>forecast benchmark</x:v>
+        <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F32" s="16" t="str">
-        <x:v>https://omegause-officeval.github.io/</x:v>
+        <x:v>https://mypcbench.pages.dev/leaderboard.html</x:v>
       </x:c>
       <x:c r="G32" s="16" t="str"/>
     </x:row>
-    <x:row r="33" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="33" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A33" s="16" t="str">
-        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+        <x:v>gate1-omegause-officeval-github-io-omegause-officeval-benchmark</x:v>
       </x:c>
       <x:c r="B33" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>omegause-officeval.github.io</x:v>
       </x:c>
       <x:c r="C33" s="16" t="str">
-        <x:v>Agents Last Exam source</x:v>
+        <x:v>OmegaUse-OfficeVal benchmark</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E33" s="16" t="str">
-        <x:v>AI R&amp;D, Capability velocity, Computer use, release metadata, supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark</x:v>
       </x:c>
       <x:c r="F33" s="16" t="str">
-        <x:v>https://openai.com/index/gpt-5-6/</x:v>
+        <x:v>https://omegause-officeval.github.io/</x:v>
       </x:c>
       <x:c r="G33" s="16" t="str"/>
     </x:row>
-    <x:row r="34" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="34" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A34" s="16" t="str">
-        <x:v>gate1-openai-com-gdpval-benchmark</x:v>
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
       </x:c>
       <x:c r="B34" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C34" s="16" t="str">
-        <x:v>GDPval benchmark</x:v>
+        <x:v>Agents Last Exam source</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
-        <x:v>forecast benchmark</x:v>
+        <x:v>AI R&amp;D, Capability velocity, Computer use, release metadata, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F34" s="16" t="str">
-        <x:v>https://openai.com/index/gdpval/</x:v>
+        <x:v>https://openai.com/index/gpt-5-6/</x:v>
       </x:c>
       <x:c r="G34" s="16" t="str"/>
     </x:row>
-    <x:row r="35" ht="54" hidden="0" customHeight="1">
+    <x:row r="35" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A35" s="16" t="str">
-        <x:v>gate1-openai-com-osworld-observation-source</x:v>
+        <x:v>gate1-openai-com-gdpval-benchmark</x:v>
       </x:c>
       <x:c r="B35" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C35" s="16" t="str">
-        <x:v>OSWorld observation source</x:v>
+        <x:v>GDPval benchmark</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E35" s="16" t="str">
-        <x:v>release metadata, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark</x:v>
       </x:c>
       <x:c r="F35" s="16" t="str">
-        <x:v>https://openai.com/index/introducing-gpt-5-4/</x:v>
+        <x:v>https://openai.com/index/gdpval/</x:v>
       </x:c>
       <x:c r="G35" s="16" t="str"/>
     </x:row>
-    <x:row r="36" ht="75.5999984741211" hidden="0" customHeight="1">
+    <x:row r="36" ht="54" hidden="0" customHeight="1">
       <x:c r="A36" s="16" t="str">
-        <x:v>gate1-openai-com-osworld-observation-source-2</x:v>
+        <x:v>gate1-openai-com-osworld-observation-source</x:v>
       </x:c>
       <x:c r="B36" s="16" t="str">
         <x:v>openai.com</x:v>
@@ -5367,40 +5449,40 @@
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
-        <x:v>Capability velocity, release metadata, supporting evaluation observation</x:v>
+        <x:v>release metadata, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F36" s="16" t="str">
-        <x:v>https://openai.com/index/introducing-gpt-5-5/</x:v>
+        <x:v>https://openai.com/index/introducing-gpt-5-4/</x:v>
       </x:c>
       <x:c r="G36" s="16" t="str"/>
     </x:row>
-    <x:row r="37" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="37" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A37" s="16" t="str">
-        <x:v>gate1-os-world-github-io-osworld-source</x:v>
+        <x:v>gate1-openai-com-osworld-observation-source-2</x:v>
       </x:c>
       <x:c r="B37" s="16" t="str">
-        <x:v>os-world.github.io</x:v>
+        <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C37" s="16" t="str">
-        <x:v>OSWorld source</x:v>
+        <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
-        <x:v>supporting evaluation</x:v>
+        <x:v>Capability velocity, release metadata, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F37" s="16" t="str">
-        <x:v>https://os-world.github.io/</x:v>
+        <x:v>https://openai.com/index/introducing-gpt-5-5/</x:v>
       </x:c>
       <x:c r="G37" s="16" t="str"/>
     </x:row>
-    <x:row r="38" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="38" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A38" s="16" t="str">
-        <x:v>gate1-osworld-v2-xlang-ai-osworld-source</x:v>
+        <x:v>gate1-os-world-github-io-osworld-source</x:v>
       </x:c>
       <x:c r="B38" s="16" t="str">
-        <x:v>osworld-v2.xlang.ai</x:v>
+        <x:v>os-world.github.io</x:v>
       </x:c>
       <x:c r="C38" s="16" t="str">
         <x:v>OSWorld source</x:v>
@@ -5409,43 +5491,43 @@
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
-        <x:v>Computer use, capability evidence, supporting evaluation</x:v>
+        <x:v>supporting evaluation</x:v>
       </x:c>
       <x:c r="F38" s="16" t="str">
-        <x:v>https://osworld-v2.xlang.ai/</x:v>
+        <x:v>https://os-world.github.io/</x:v>
       </x:c>
       <x:c r="G38" s="16" t="str"/>
     </x:row>
-    <x:row r="39" ht="54" hidden="0" customHeight="1">
+    <x:row r="39" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A39" s="16" t="str">
-        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
+        <x:v>gate1-osworld-v2-xlang-ai-osworld-source</x:v>
       </x:c>
       <x:c r="B39" s="16" t="str">
-        <x:v>remotelabor.ai</x:v>
+        <x:v>osworld-v2.xlang.ai</x:v>
       </x:c>
       <x:c r="C39" s="16" t="str">
-        <x:v>Remote Labor Index benchmark</x:v>
+        <x:v>OSWorld source</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
-        <x:v>forecast benchmark, forecast observation</x:v>
+        <x:v>Computer use, capability evidence, supporting evaluation</x:v>
       </x:c>
       <x:c r="F39" s="16" t="str">
-        <x:v>https://www.remotelabor.ai/</x:v>
+        <x:v>https://osworld-v2.xlang.ai/</x:v>
       </x:c>
       <x:c r="G39" s="16" t="str"/>
     </x:row>
-    <x:row r="40" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="40" ht="54" hidden="0" customHeight="1">
       <x:c r="A40" s="16" t="str">
-        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
+        <x:v>gate1-remotelabor-ai-remote-labor-index-benchmark</x:v>
       </x:c>
       <x:c r="B40" s="16" t="str">
-        <x:v>taubench.com</x:v>
+        <x:v>remotelabor.ai</x:v>
       </x:c>
       <x:c r="C40" s="16" t="str">
-        <x:v>tau3 Banking benchmark</x:v>
+        <x:v>Remote Labor Index benchmark</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
         <x:v>2026-08-26</x:v>
@@ -5454,93 +5536,114 @@
         <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F40" s="16" t="str">
-        <x:v>https://taubench.com/leaderboard/</x:v>
+        <x:v>https://www.remotelabor.ai/</x:v>
       </x:c>
       <x:c r="G40" s="16" t="str"/>
     </x:row>
-    <x:row r="41" ht="108" hidden="0" customHeight="1">
+    <x:row r="41" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A41" s="16" t="str">
-        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-benchmark</x:v>
       </x:c>
       <x:c r="B41" s="16" t="str">
         <x:v>taubench.com</x:v>
       </x:c>
       <x:c r="C41" s="16" t="str">
-        <x:v>tau3 Banking source</x:v>
+        <x:v>tau3 Banking benchmark</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
-        <x:v>Business, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation</x:v>
+        <x:v>forecast benchmark, forecast observation</x:v>
       </x:c>
       <x:c r="F41" s="16" t="str">
-        <x:v>https://taubench.com/leaderboard/?benchmark=knowledge</x:v>
+        <x:v>https://taubench.com/leaderboard/</x:v>
       </x:c>
       <x:c r="G41" s="16" t="str"/>
     </x:row>
-    <x:row r="42" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="42" ht="108" hidden="0" customHeight="1">
       <x:c r="A42" s="16" t="str">
-        <x:v>gate1-the-agent-company-com-theagentcompany-observation-source</x:v>
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
       </x:c>
       <x:c r="B42" s="16" t="str">
-        <x:v>the-agent-company.com</x:v>
+        <x:v>taubench.com</x:v>
       </x:c>
       <x:c r="C42" s="16" t="str">
-        <x:v>TheAgentCompany observation source</x:v>
+        <x:v>tau3 Banking source</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
-        <x:v>forecast observation</x:v>
+        <x:v>Business, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation</x:v>
       </x:c>
       <x:c r="F42" s="16" t="str">
-        <x:v>https://the-agent-company.com/</x:v>
+        <x:v>https://taubench.com/leaderboard/?benchmark=knowledge</x:v>
       </x:c>
       <x:c r="G42" s="16" t="str"/>
     </x:row>
-    <x:row r="43" ht="75.5999984741211" hidden="0" customHeight="1">
+    <x:row r="43" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A43" s="16" t="str">
-        <x:v>gate1-www-cdn-anthropic-com-osworld-observation-source</x:v>
+        <x:v>gate1-the-agent-company-com-theagentcompany-observation-source</x:v>
       </x:c>
       <x:c r="B43" s="16" t="str">
-        <x:v>www-cdn.anthropic.com</x:v>
+        <x:v>the-agent-company.com</x:v>
       </x:c>
       <x:c r="C43" s="16" t="str">
-        <x:v>OSWorld observation source</x:v>
+        <x:v>TheAgentCompany observation source</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E43" s="16" t="str">
-        <x:v>supporting evaluation observation</x:v>
+        <x:v>forecast observation</x:v>
       </x:c>
       <x:c r="F43" s="16" t="str">
-        <x:v>https://www-cdn.anthropic.com/6a5fa276ac68b9aeb0c8b6af5fa36326e0e166dd.pdf</x:v>
+        <x:v>https://the-agent-company.com/</x:v>
       </x:c>
       <x:c r="G43" s="16" t="str"/>
     </x:row>
-    <x:row r="44" ht="54" hidden="0" customHeight="1">
+    <x:row r="44" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A44" s="16" t="str">
-        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
+        <x:v>gate1-www-cdn-anthropic-com-osworld-observation-source</x:v>
       </x:c>
       <x:c r="B44" s="16" t="str">
-        <x:v>METR</x:v>
+        <x:v>www-cdn.anthropic.com</x:v>
       </x:c>
       <x:c r="C44" s="16" t="str">
-        <x:v>Task-horizon benchmark results</x:v>
+        <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D44" s="16" t="str">
         <x:v>2026-08-26</x:v>
       </x:c>
       <x:c r="E44" s="16" t="str">
+        <x:v>supporting evaluation observation</x:v>
+      </x:c>
+      <x:c r="F44" s="16" t="str">
+        <x:v>https://www-cdn.anthropic.com/6a5fa276ac68b9aeb0c8b6af5fa36326e0e166dd.pdf</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="str"/>
+    </x:row>
+    <x:row r="45" ht="54" hidden="0" customHeight="1">
+      <x:c r="A45" s="16" t="str">
+        <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
+      </x:c>
+      <x:c r="B45" s="16" t="str">
+        <x:v>METR</x:v>
+      </x:c>
+      <x:c r="C45" s="16" t="str">
+        <x:v>Task-horizon benchmark results</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="str">
+        <x:v>2026-08-26</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="str">
         <x:v>published trend estimate</x:v>
       </x:c>
-      <x:c r="F44" s="16" t="str">
+      <x:c r="F45" s="16" t="str">
         <x:v>https://metr.org/assets/benchmark_results_1_1.yaml</x:v>
       </x:c>
-      <x:c r="G44" s="16" t="str"/>
+      <x:c r="G45" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5549,7 +5652,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c1e17ff33894986"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88bdf65d4ba14310"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
+++ b/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R92ca18988d4349b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R9b953f0147934030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="Rdbf41fc1baa4406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R0050d58b9b5c437e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R18f7bf643a6644ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="R199cddbd754944f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfc9d8234a25941dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R0f924df657c84667"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R9f047a4302974902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R7bdfa4be3f8b43ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="Rb45043662ed04ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="Rcdcc147019f8479b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,7 +432,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd07637d622bc49a0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3310f7fb916247ac"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -442,16 +442,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CapabilitySummaryTable" displayName="CapabilitySummaryTable" ref="A5:H17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="8">
-    <x:tableColumn id="1" name="Metric / category"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CapabilitySummaryTable" displayName="CapabilitySummaryTable" ref="A5:K19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="Metric / benchmark family"/>
     <x:tableColumn id="2" name="Score / value"/>
     <x:tableColumn id="3" name="Interpretation / confidence"/>
     <x:tableColumn id="4" name="Confidence weight"/>
     <x:tableColumn id="5" name="GPA"/>
     <x:tableColumn id="6" name="Graded"/>
     <x:tableColumn id="7" name="Total"/>
-    <x:tableColumn id="8" name="Gap velocity"/>
+    <x:tableColumn id="8" name="Raw gap velocity"/>
+    <x:tableColumn id="9" name="History credits"/>
+    <x:tableColumn id="10" name="Pooling weight"/>
+    <x:tableColumn id="11" name="Pooled gap velocity"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -749,6 +752,9 @@
     <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
@@ -762,6 +768,9 @@
       <x:c r="F1" s="3"/>
       <x:c r="G1" s="3"/>
       <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+      <x:c r="K1" s="3"/>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3"/>
@@ -772,6 +781,9 @@
       <x:c r="F2" s="3"/>
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
+      <x:c r="I2" s="3"/>
+      <x:c r="J2" s="3"/>
+      <x:c r="K2" s="3"/>
     </x:row>
     <x:row r="3" ht="24" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -784,11 +796,14 @@
       <x:c r="F3" s="6"/>
       <x:c r="G3" s="6"/>
       <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+      <x:c r="J3" s="6"/>
+      <x:c r="K3" s="6"/>
     </x:row>
     <x:row r="4"/>
     <x:row r="5" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A5" s="12" t="str">
-        <x:v>Metric / category</x:v>
+        <x:v>Metric / benchmark family</x:v>
       </x:c>
       <x:c r="B5" s="12" t="str">
         <x:v>Score / value</x:v>
@@ -809,7 +824,16 @@
         <x:v>Total</x:v>
       </x:c>
       <x:c r="H5" s="12" t="str">
-        <x:v>Gap velocity</x:v>
+        <x:v>Raw gap velocity</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>History credits</x:v>
+      </x:c>
+      <x:c r="J5" s="12" t="str">
+        <x:v>Pooling weight</x:v>
+      </x:c>
+      <x:c r="K5" s="12" t="str">
+        <x:v>Pooled gap velocity</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="64.80000305175781" hidden="0" customHeight="1">
@@ -827,6 +851,9 @@
       <x:c r="F6" s="16"/>
       <x:c r="G6" s="16"/>
       <x:c r="H6" s="16"/>
+      <x:c r="I6" s="16"/>
+      <x:c r="J6" s="16"/>
+      <x:c r="K6" s="16"/>
     </x:row>
     <x:row r="7" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A7" s="16" t="str">
@@ -843,6 +870,9 @@
       <x:c r="F7" s="16"/>
       <x:c r="G7" s="16"/>
       <x:c r="H7" s="16"/>
+      <x:c r="I7" s="16"/>
+      <x:c r="J7" s="16"/>
+      <x:c r="K7" s="16"/>
     </x:row>
     <x:row r="8" ht="54" hidden="0" customHeight="1">
       <x:c r="A8" s="16" t="str">
@@ -859,6 +889,9 @@
       <x:c r="F8" s="16"/>
       <x:c r="G8" s="16"/>
       <x:c r="H8" s="16"/>
+      <x:c r="I8" s="16"/>
+      <x:c r="J8" s="16"/>
+      <x:c r="K8" s="16"/>
     </x:row>
     <x:row r="9" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
@@ -875,6 +908,9 @@
       <x:c r="F9" s="16"/>
       <x:c r="G9" s="16"/>
       <x:c r="H9" s="16"/>
+      <x:c r="I9" s="16"/>
+      <x:c r="J9" s="16"/>
+      <x:c r="K9" s="16"/>
     </x:row>
     <x:row r="10" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A10" s="16" t="str">
@@ -891,165 +927,251 @@
       <x:c r="F10" s="16"/>
       <x:c r="G10" s="16"/>
       <x:c r="H10" s="16"/>
-    </x:row>
-    <x:row r="11" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="I10" s="16"/>
+      <x:c r="J10" s="16"/>
+      <x:c r="K10" s="16"/>
+    </x:row>
+    <x:row r="11" ht="54" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
-        <x:v>Economic gap velocity</x:v>
+        <x:v>Pooled economic gap velocity</x:v>
       </x:c>
       <x:c r="B11" s="18" t="n">
-        <x:v>0.11844032433366539</x:v>
+        <x:v>0.15281328681186693</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str">
-        <x:v>failure-gap halvings / quarter</x:v>
+        <x:v>confidence-weighted family gap halvings / quarter</x:v>
       </x:c>
       <x:c r="D11" s="16"/>
       <x:c r="E11" s="16"/>
       <x:c r="F11" s="16"/>
       <x:c r="G11" s="16"/>
       <x:c r="H11" s="16"/>
-    </x:row>
-    <x:row r="12" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="I11" s="16"/>
+      <x:c r="J11" s="16"/>
+      <x:c r="K11" s="16"/>
+    </x:row>
+    <x:row r="12" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A12" s="16" t="str">
-        <x:v>METR H50 acceleration</x:v>
+        <x:v>Cross-family velocity prior</x:v>
       </x:c>
       <x:c r="B12" s="18" t="n">
-        <x:v>0.2091206151346937</x:v>
+        <x:v>0.14659783540166885</x:v>
       </x:c>
       <x:c r="C12" s="16" t="str">
-        <x:v>task-horizon doublings / quarter²</x:v>
+        <x:v>evidence-weighted prior for sparse families</x:v>
       </x:c>
       <x:c r="D12" s="16"/>
       <x:c r="E12" s="16"/>
       <x:c r="F12" s="16"/>
       <x:c r="G12" s="16"/>
       <x:c r="H12" s="16"/>
+      <x:c r="I12" s="16"/>
+      <x:c r="J12" s="16"/>
+      <x:c r="K12" s="16"/>
     </x:row>
     <x:row r="13" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>METR H80 guardrail</x:v>
+        <x:v>Partial-pooling prior strength</x:v>
       </x:c>
       <x:c r="B13" s="18" t="n">
-        <x:v>0.3429173634620015</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C13" s="16" t="str">
-        <x:v>task-horizon doublings / quarter²</x:v>
+        <x:v>history credits</x:v>
       </x:c>
       <x:c r="D13" s="16"/>
       <x:c r="E13" s="16"/>
       <x:c r="F13" s="16"/>
       <x:c r="G13" s="16"/>
       <x:c r="H13" s="16"/>
+      <x:c r="I13" s="16"/>
+      <x:c r="J13" s="16"/>
+      <x:c r="K13" s="16"/>
     </x:row>
     <x:row r="14" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A14" s="21" t="str">
-        <x:v>Direct economic stewardship</x:v>
-      </x:c>
-      <x:c r="B14" s="22" t="n">
-        <x:v>0.38254856862232545</x:v>
-      </x:c>
-      <x:c r="C14" s="21" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="D14" s="23" t="n">
-        <x:v>0.47619047619047616</x:v>
-      </x:c>
-      <x:c r="E14" s="21" t="n">
-        <x:v>0.7142857142857143</x:v>
-      </x:c>
-      <x:c r="F14" s="21" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G14" s="21" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H14" s="24" t="n">
-        <x:v>0.006549844650824387</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="21.600000381469727" hidden="0" customHeight="1">
-      <x:c r="A15" s="21" t="str">
-        <x:v>Operational execution</x:v>
-      </x:c>
-      <x:c r="B15" s="22" t="n">
-        <x:v>0.49453749999999996</x:v>
-      </x:c>
-      <x:c r="C15" s="21" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="D15" s="23" t="n">
-        <x:v>0.5925925925925926</x:v>
-      </x:c>
-      <x:c r="E15" s="21" t="n">
-        <x:v>0.375</x:v>
-      </x:c>
-      <x:c r="F15" s="21" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G15" s="21" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="H15" s="24" t="n">
-        <x:v>0.23660304317034014</x:v>
-      </x:c>
+      <x:c r="A14" s="16" t="str">
+        <x:v>METR H50 acceleration</x:v>
+      </x:c>
+      <x:c r="B14" s="18" t="n">
+        <x:v>0.2091206151346937</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="str">
+        <x:v>task-horizon doublings / quarter²</x:v>
+      </x:c>
+      <x:c r="D14" s="16"/>
+      <x:c r="E14" s="16"/>
+      <x:c r="F14" s="16"/>
+      <x:c r="G14" s="16"/>
+      <x:c r="H14" s="16"/>
+      <x:c r="I14" s="16"/>
+      <x:c r="J14" s="16"/>
+      <x:c r="K14" s="16"/>
+    </x:row>
+    <x:row r="15" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A15" s="16" t="str">
+        <x:v>METR H80 guardrail</x:v>
+      </x:c>
+      <x:c r="B15" s="18" t="n">
+        <x:v>0.3429173634620015</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>task-horizon doublings / quarter²</x:v>
+      </x:c>
+      <x:c r="D15" s="16"/>
+      <x:c r="E15" s="16"/>
+      <x:c r="F15" s="16"/>
+      <x:c r="G15" s="16"/>
+      <x:c r="H15" s="16"/>
+      <x:c r="I15" s="16"/>
+      <x:c r="J15" s="16"/>
+      <x:c r="K15" s="16"/>
     </x:row>
     <x:row r="16" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A16" s="21" t="str">
-        <x:v>Personal stewardship transfer</x:v>
+        <x:v>Direct economic stewardship</x:v>
       </x:c>
       <x:c r="B16" s="22" t="n">
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.38254856862232545</x:v>
       </x:c>
       <x:c r="C16" s="21" t="str">
         <x:v>Low</x:v>
       </x:c>
       <x:c r="D16" s="23" t="n">
+        <x:v>0.47619047619047616</x:v>
+      </x:c>
+      <x:c r="E16" s="21" t="n">
+        <x:v>0.7142857142857143</x:v>
+      </x:c>
+      <x:c r="F16" s="21" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G16" s="21" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H16" s="24" t="n">
+        <x:v>0.006549844650824387</x:v>
+      </x:c>
+      <x:c r="I16" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J16" s="23" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K16" s="24" t="n">
+        <x:v>0.07657384002624662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A17" s="21" t="str">
+        <x:v>Operational execution</x:v>
+      </x:c>
+      <x:c r="B17" s="22" t="n">
+        <x:v>0.49453749999999996</x:v>
+      </x:c>
+      <x:c r="C17" s="21" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="n">
+        <x:v>0.5925925925925926</x:v>
+      </x:c>
+      <x:c r="E17" s="21" t="n">
+        <x:v>0.375</x:v>
+      </x:c>
+      <x:c r="F17" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G17" s="21" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H17" s="24" t="n">
+        <x:v>0.23660304317034014</x:v>
+      </x:c>
+      <x:c r="I17" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J17" s="23" t="n">
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="K17" s="24" t="n">
+        <x:v>0.21205616832433888</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A18" s="21" t="str">
+        <x:v>Personal stewardship transfer</x:v>
+      </x:c>
+      <x:c r="B18" s="22" t="n">
+        <x:v>0.49477499999999996</x:v>
+      </x:c>
+      <x:c r="C18" s="21" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="D18" s="23" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E16" s="21" t="n">
+      <x:c r="E18" s="21" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="F16" s="21" t="n">
+      <x:c r="F18" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G16" s="21" t="n">
+      <x:c r="G18" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H16" s="24"/>
-    </x:row>
-    <x:row r="17" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A17" s="21" t="str">
+      <x:c r="H18" s="24"/>
+      <x:c r="I18" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="24" t="n">
+        <x:v>0.14659783540166885</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A19" s="21" t="str">
         <x:v>Economic value &amp; governance</x:v>
       </x:c>
-      <x:c r="B17" s="22" t="n">
+      <x:c r="B19" s="22" t="n">
         <x:v>0.431</x:v>
       </x:c>
-      <x:c r="C17" s="21" t="str">
+      <x:c r="C19" s="21" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D17" s="23" t="n">
+      <x:c r="D19" s="23" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E17" s="21" t="n">
+      <x:c r="E19" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F17" s="21" t="n">
+      <x:c r="F19" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G17" s="21" t="n">
+      <x:c r="G19" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H17" s="24" t="n">
+      <x:c r="H19" s="24" t="n">
         <x:v>0.18665713536174536</x:v>
+      </x:c>
+      <x:c r="I19" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J19" s="23" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="K19" s="24" t="n">
+        <x:v>0.16262155538569945</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A1:K2"/>
+    <x:mergeCell ref="A3:K3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3381f692a524ed5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refaf931c089b4164"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2380,7 +2502,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ab0459da4345cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2fa919507894072"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3729,7 +3851,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f2e14c32b7446f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re03305a66d8c4077"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4023,19 +4145,19 @@
         <x:v>2026-12-31</x:v>
       </x:c>
       <x:c r="C17" s="17" t="n">
-        <x:v>0.5015863697066921</x:v>
+        <x:v>0.5131595499494372</x:v>
       </x:c>
       <x:c r="D17" s="17" t="n">
-        <x:v>0.43877715846704063</x:v>
+        <x:v>0.41951189241520126</x:v>
       </x:c>
       <x:c r="E17" s="17" t="n">
-        <x:v>0.5405677498483082</x:v>
+        <x:v>0.573964900822655</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
-        <x:v>0.540783621766425</x:v>
+        <x:v>0.5510902207212565</x:v>
       </x:c>
       <x:c r="G17" s="17" t="n">
-        <x:v>0.4828163309121596</x:v>
+        <x:v>0.5009128455312821</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4046,19 +4168,19 @@
         <x:v>2027-03-31</x:v>
       </x:c>
       <x:c r="C18" s="17" t="n">
-        <x:v>0.5615680771328883</x:v>
+        <x:v>0.5838014161122994</x:v>
       </x:c>
       <x:c r="D18" s="17" t="n">
-        <x:v>0.5063176554272025</x:v>
+        <x:v>0.4656938403212752</x:v>
       </x:c>
       <x:c r="E18" s="17" t="n">
-        <x:v>0.5958582337673388</x:v>
+        <x:v>0.6613572683659491</x:v>
       </x:c>
       <x:c r="F18" s="17" t="n">
-        <x:v>0.5960481265278903</x:v>
+        <x:v>0.616970387335722</x:v>
       </x:c>
       <x:c r="G18" s="17" t="n">
-        <x:v>0.5450569231419062</x:v>
+        <x:v>0.5814804824886135</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4069,19 +4191,19 @@
         <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="C19" s="17" t="n">
-        <x:v>0.6309224397345665</x:v>
+        <x:v>0.6609741939528238</x:v>
       </x:c>
       <x:c r="D19" s="17" t="n">
-        <x:v>0.5844119331240532</x:v>
+        <x:v>0.5219860028628462</x:v>
       </x:c>
       <x:c r="E19" s="17" t="n">
-        <x:v>0.6597883290361504</x:v>
+        <x:v>0.7512018452006073</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
-        <x:v>0.6599481831734086</x:v>
+        <x:v>0.6904941506847201</x:v>
       </x:c>
       <x:c r="G19" s="17" t="n">
-        <x:v>0.6170231406317374</x:v>
+        <x:v>0.669604082591502</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4092,19 +4214,19 @@
         <x:v>2027-09-30</x:v>
       </x:c>
       <x:c r="C20" s="17" t="n">
-        <x:v>0.7071214661713452</x:v>
+        <x:v>0.7400505147370063</x:v>
       </x:c>
       <x:c r="D20" s="17" t="n">
-        <x:v>0.6702134271837716</x:v>
+        <x:v>0.5883664976708365</x:v>
       </x:c>
       <x:c r="E20" s="17" t="n">
-        <x:v>0.7300277608001164</x:v>
+        <x:v>0.8355489742820248</x:v>
       </x:c>
       <x:c r="F20" s="17" t="n">
-        <x:v>0.7301546117669241</x:v>
+        <x:v>0.767532135108189</x:v>
       </x:c>
       <x:c r="G20" s="17" t="n">
-        <x:v>0.696091788995754</x:v>
+        <x:v>0.7594853081263506</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4115,19 +4237,19 @@
         <x:v>2027-12-31</x:v>
       </x:c>
       <x:c r="C21" s="17" t="n">
-        <x:v>0.785307273130474</x:v>
+        <x:v>0.814832346574145</x:v>
       </x:c>
       <x:c r="D21" s="17" t="n">
-        <x:v>0.7582520723615275</x:v>
+        <x:v>0.6632445350745001</x:v>
       </x:c>
       <x:c r="E21" s="17" t="n">
-        <x:v>0.8020985851875222</x:v>
+        <x:v>0.9056885837078396</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:v>0.8021915724734591</x:v>
+        <x:v>0.8417188367356241</x:v>
       </x:c>
       <x:c r="G21" s="17" t="n">
-        <x:v>0.7772220391655169</x:v>
+        <x:v>0.8429776734919401</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4138,19 +4260,19 @@
         <x:v>2028-03-31</x:v>
       </x:c>
       <x:c r="C22" s="17" t="n">
-        <x:v>0.8585194965024904</x:v>
+        <x:v>0.8790181332273004</x:v>
       </x:c>
       <x:c r="D22" s="17" t="n">
-        <x:v>0.8406903716745077</x:v>
+        <x:v>0.7428320885130025</x:v>
       </x:c>
       <x:c r="E22" s="17" t="n">
-        <x:v>0.869584814451797</x:v>
+        <x:v>0.9553023421503699</x:v>
       </x:c>
       <x:c r="F22" s="17" t="n">
-        <x:v>0.8696460922054736</x:v>
+        <x:v>0.9055396378770173</x:v>
       </x:c>
       <x:c r="G22" s="17" t="n">
-        <x:v>0.8531914027708731</x:v>
+        <x:v>0.9114317496077905</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4161,19 +4283,19 @@
         <x:v>2028-06-30</x:v>
       </x:c>
       <x:c r="C23" s="17" t="n">
-        <x:v>0.9191900534722246</x:v>
+        <x:v>0.9283165342168052</x:v>
       </x:c>
       <x:c r="D23" s="17" t="n">
-        <x:v>0.909006525789121</x:v>
+        <x:v>0.820954678700308</x:v>
       </x:c>
       <x:c r="E23" s="17" t="n">
-        <x:v>0.9255102723694668</x:v>
+        <x:v>0.9836016052557366</x:v>
       </x:c>
       <x:c r="F23" s="17" t="n">
-        <x:v>0.9255452726124369</x:v>
+        <x:v>0.952772721942952</x:v>
       </x:c>
       <x:c r="G23" s="17" t="n">
-        <x:v>0.9161467863159515</x:v>
+        <x:v>0.9589498550640618</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4184,19 +4306,19 @@
         <x:v>2028-09-30</x:v>
       </x:c>
       <x:c r="C24" s="17" t="n">
-        <x:v>0.9619089891630892</x:v>
+        <x:v>0.9619503679317483</x:v>
       </x:c>
       <x:c r="D24" s="17" t="n">
-        <x:v>0.957108826806816</x:v>
+        <x:v>0.8899011632631341</x:v>
       </x:c>
       <x:c r="E24" s="17" t="n">
-        <x:v>0.9648881215205617</x:v>
+        <x:v>0.9957344087455272</x:v>
       </x:c>
       <x:c r="F24" s="17" t="n">
-        <x:v>0.9649046194232525</x:v>
+        <x:v>0.9813835870220199</x:v>
       </x:c>
       <x:c r="G24" s="17" t="n">
-        <x:v>0.960474498395429</x:v>
+        <x:v>0.9853840670800804</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4207,19 +4329,19 @@
         <x:v>2028-12-31</x:v>
       </x:c>
       <x:c r="C25" s="17" t="n">
-        <x:v>0.9861271409811129</x:v>
+        <x:v>0.982311895144309</x:v>
       </x:c>
       <x:c r="D25" s="17" t="n">
-        <x:v>0.9843789076270163</x:v>
+        <x:v>0.9426962228960611</x:v>
       </x:c>
       <x:c r="E25" s="17" t="n">
-        <x:v>0.987212149813532</x:v>
+        <x:v>0.9993007920949821</x:v>
       </x:c>
       <x:c r="F25" s="17" t="n">
-        <x:v>0.987218158398579</x:v>
+        <x:v>0.9946672024336355</x:v>
       </x:c>
       <x:c r="G25" s="17" t="n">
-        <x:v>0.9856046951928179</x:v>
+        <x:v>0.996347921884617</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4228,9 +4350,9 @@
     <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0378b56330fd4218"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a6bc9c47cb14cc2"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R361a0ce7a1414cee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0147c4dff9cc498e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4730,7 +4852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9b7ff8a0cdf4bd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56a29f38ff9e4c24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5652,7 +5774,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88bdf65d4ba14310"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re239c13ea45b4223"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
+++ b/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfc9d8234a25941dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R0f924df657c84667"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R9f047a4302974902"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R7bdfa4be3f8b43ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="Rb45043662ed04ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="6" r:id="Rcdcc147019f8479b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9a0940a3125d4bb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R8da8e13224474d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R1ef87d98bcbd4838"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R697aab421d234433"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R5aab6667b7644f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Evidence" sheetId="6" r:id="R43b117debd5e4831"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Releases" sheetId="7" r:id="R75d07812935a4169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb8ccdc4d4c1d4fca"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -432,7 +434,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3310f7fb916247ac"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf692cba597744bfa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -485,7 +487,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CapabilityObservationsTable" displayName="CapabilityObservationsTable" ref="A5:J44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="CapabilityObservationsTable" displayName="CapabilityObservationsTable" ref="A5:J45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Observation ID"/>
     <x:tableColumn id="2" name="Benchmark ID"/>
@@ -535,7 +537,41 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilityResearchEvidenceTable" displayName="CapabilityResearchEvidenceTable" ref="A5:I55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="Evidence ID"/>
+    <x:tableColumn id="2" name="Category"/>
+    <x:tableColumn id="3" name="Metric date"/>
+    <x:tableColumn id="4" name="Entity"/>
+    <x:tableColumn id="5" name="Metric"/>
+    <x:tableColumn id="6" name="Value"/>
+    <x:tableColumn id="7" name="Unit"/>
+    <x:tableColumn id="8" name="Source ID"/>
+    <x:tableColumn id="9" name="Caveat / comparability note"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="CapabilityModelReleasesTable" displayName="CapabilityModelReleasesTable" ref="A5:I23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
+    <x:tableColumn id="1" name="Release ID"/>
+    <x:tableColumn id="2" name="Provider"/>
+    <x:tableColumn id="3" name="Model"/>
+    <x:tableColumn id="4" name="Release date"/>
+    <x:tableColumn id="5" name="Availability stage"/>
+    <x:tableColumn id="6" name="Availability scope"/>
+    <x:tableColumn id="7" name="Parent release"/>
+    <x:tableColumn id="8" name="Source ID"/>
+    <x:tableColumn id="9" name="Notes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Source ID"/>
     <x:tableColumn id="2" name="Publisher"/>
@@ -787,7 +823,7 @@
     </x:row>
     <x:row r="3" ht="24" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
-        <x:v>Snapshot 2026-08-26. Every value is calculated from the latest dated JSON snapshot through the same shared model used by the website.</x:v>
+        <x:v>Snapshot 2026-09-03. Every value is calculated from the latest dated JSON snapshot through the same shared model used by the website.</x:v>
       </x:c>
       <x:c r="B3" s="6"/>
       <x:c r="C3" s="6"/>
@@ -841,7 +877,7 @@
         <x:v>Snapshot</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="C6" s="16" t="str">
         <x:v>Latest immutable snapshot selected automatically</x:v>
@@ -860,7 +896,7 @@
         <x:v>Current capability</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
-        <x:v>0.45165059809758934</x:v>
+        <x:v>0.46141401843584867</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
         <x:v>Confidence-weighted score</x:v>
@@ -898,7 +934,7 @@
         <x:v>GPA</x:v>
       </x:c>
       <x:c r="B9" s="18" t="n">
-        <x:v>0.5641332752613242</x:v>
+        <x:v>0.5601812366737741</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str">
         <x:v>0–4</x:v>
@@ -920,7 +956,7 @@
         <x:v>Low</x:v>
       </x:c>
       <x:c r="C10" s="16" t="n">
-        <x:v>0.47222222222222227</x:v>
+        <x:v>0.48611111111111116</x:v>
       </x:c>
       <x:c r="D10" s="16"/>
       <x:c r="E10" s="16"/>
@@ -936,7 +972,7 @@
         <x:v>Pooled economic gap velocity</x:v>
       </x:c>
       <x:c r="B11" s="18" t="n">
-        <x:v>0.15281328681186693</x:v>
+        <x:v>0.15706886974084042</x:v>
       </x:c>
       <x:c r="C11" s="16" t="str">
         <x:v>confidence-weighted family gap halvings / quarter</x:v>
@@ -955,7 +991,7 @@
         <x:v>Cross-family velocity prior</x:v>
       </x:c>
       <x:c r="B12" s="18" t="n">
-        <x:v>0.14659783540166885</x:v>
+        <x:v>0.14986492610341606</x:v>
       </x:c>
       <x:c r="C12" s="16" t="str">
         <x:v>evidence-weighted prior for sparse families</x:v>
@@ -1058,7 +1094,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="K16" s="24" t="n">
-        <x:v>0.07657384002624662</x:v>
+        <x:v>0.07820738537712023</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -1066,13 +1102,13 @@
         <x:v>Operational execution</x:v>
       </x:c>
       <x:c r="B17" s="22" t="n">
-        <x:v>0.49453749999999996</x:v>
+        <x:v>0.5195</x:v>
       </x:c>
       <x:c r="C17" s="21" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="D17" s="23" t="n">
-        <x:v>0.5925925925925926</x:v>
+        <x:v>0.6296296296296297</x:v>
       </x:c>
       <x:c r="E17" s="21" t="n">
         <x:v>0.375</x:v>
@@ -1084,16 +1120,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H17" s="24" t="n">
-        <x:v>0.23660304317034014</x:v>
+        <x:v>0.23877625507365563</x:v>
       </x:c>
       <x:c r="I17" s="21" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J17" s="23" t="n">
-        <x:v>0.7272727272727273</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="K17" s="24" t="n">
-        <x:v>0.21205616832433888</x:v>
+        <x:v>0.21654842283109574</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32.400001525878906" hidden="0" customHeight="1">
@@ -1126,7 +1162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K18" s="24" t="n">
-        <x:v>0.14659783540166885</x:v>
+        <x:v>0.14986492610341606</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="32.400001525878906" hidden="0" customHeight="1">
@@ -1161,7 +1197,7 @@
         <x:v>0.4</x:v>
       </x:c>
       <x:c r="K19" s="24" t="n">
-        <x:v>0.16262155538569945</x:v>
+        <x:v>0.16458180980674778</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1171,7 +1207,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refaf931c089b4164"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1109f040a14438b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1680,7 +1716,7 @@
         <x:v>2026-Q2</x:v>
       </x:c>
       <x:c r="H13" s="17" t="n">
-        <x:v>0.3033</x:v>
+        <x:v>0.503</x:v>
       </x:c>
       <x:c r="I13" s="16" t="str">
         <x:v>F</x:v>
@@ -1689,13 +1725,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L13" s="16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M13" s="20" t="n">
-        <x:v>0</x:v>
+        <x:v>0.24746910268691757</x:v>
       </x:c>
       <x:c r="N13" s="20" t="n">
         <x:v>0</x:v>
@@ -2502,7 +2538,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2fa919507894072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67a02012d48a4e8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2916,7 +2952,7 @@
         <x:v>Authors' reported ratio; three LLM runs per configuration and three non-expert human participants.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="151.1999969482422" hidden="0" customHeight="1">
+    <x:row r="16" ht="291.6000061035156" hidden="0" customHeight="1">
       <x:c r="A16" s="16" t="str">
         <x:v>forecast-observation-011</x:v>
       </x:c>
@@ -2933,7 +2969,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="17" t="n">
-        <x:v>0.3033</x:v>
+        <x:v>0.41</x:v>
       </x:c>
       <x:c r="G16" s="16" t="str">
         <x:v>Claude Opus 4.8</x:v>
@@ -2945,7 +2981,7 @@
         <x:v>gate1-github-com-automationbench-benchmark</x:v>
       </x:c>
       <x:c r="J16" s="16" t="str">
-        <x:v>Current public frontier after the July 2026 stricter-classifier rescore; 182/600 tasks. Later private-leaderboard results are not comparable.</x:v>
+        <x:v>The benchmark repository's current public table reports 41.0% for Claude Opus 4.8. This is an upstream historical rescore relative to the 30.33% value preserved in snapshot-20260826; the immutable prior snapshot remains the audit record for that earlier published state.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="86.4000015258789" hidden="0" customHeight="1">
@@ -3842,6 +3878,38 @@
       </x:c>
       <x:c r="J44" s="16" t="str">
         <x:v>Claude Opus 4.7's release date assigns the frontier point to 2026-Q2; the paper's 6 July revision is the observation date. The paired harness is part of the measured system.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="280.79998779296875" hidden="0" customHeight="1">
+      <x:c r="A45" s="16" t="str">
+        <x:v>forecast-observation-040</x:v>
+      </x:c>
+      <x:c r="B45" s="16" t="str">
+        <x:v>OPS-01</x:v>
+      </x:c>
+      <x:c r="C45" s="25" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="str">
+        <x:v>2026-Q3</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="n">
+        <x:v>0.503</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="str">
+        <x:v>Claude Opus 5 · public AutomationBench harness · max reasoning</x:v>
+      </x:c>
+      <x:c r="H45" s="16" t="str">
+        <x:v>Public 600-task pass rate, max reasoning</x:v>
+      </x:c>
+      <x:c r="I45" s="16" t="str">
+        <x:v>gate1-github-com-automationbench-benchmark</x:v>
+      </x:c>
+      <x:c r="J45" s="16" t="str">
+        <x:v>Current public-table frontier observed on 2026-09-03: 50.3%. The repository warns that public and held-out private scores are not interchangeable and that task fixes can trigger rescoring; preserve the 2026-Q2 observation as the prior published snapshot point.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3851,7 +3919,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re03305a66d8c4077"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12261a76a63a4b8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3981,7 +4049,7 @@
         <x:v>2024-12-31</x:v>
       </x:c>
       <x:c r="C9" s="17" t="n">
-        <x:v>0.24000000000000002</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D9" s="17"/>
       <x:c r="E9" s="17" t="n">
@@ -3998,7 +4066,7 @@
         <x:v>2025-03-31</x:v>
       </x:c>
       <x:c r="C10" s="17" t="n">
-        <x:v>0.24000000000000002</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="D10" s="17"/>
       <x:c r="E10" s="17" t="n">
@@ -4007,7 +4075,7 @@
       <x:c r="F10" s="17"/>
       <x:c r="G10" s="17"/>
     </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>2025-Q2</x:v>
       </x:c>
@@ -4015,7 +4083,7 @@
         <x:v>2025-06-30</x:v>
       </x:c>
       <x:c r="C11" s="17" t="n">
-        <x:v>0.30067600000000005</x:v>
+        <x:v>0.2987846153846153</x:v>
       </x:c>
       <x:c r="D11" s="17"/>
       <x:c r="E11" s="17" t="n">
@@ -4034,7 +4102,7 @@
         <x:v>2025-09-30</x:v>
       </x:c>
       <x:c r="C12" s="17" t="n">
-        <x:v>0.2687088235294118</x:v>
+        <x:v>0.27077428571428575</x:v>
       </x:c>
       <x:c r="D12" s="17"/>
       <x:c r="E12" s="17" t="n">
@@ -4055,7 +4123,7 @@
         <x:v>2025-12-31</x:v>
       </x:c>
       <x:c r="C13" s="17" t="n">
-        <x:v>0.28385882352941183</x:v>
+        <x:v>0.28614285714285714</x:v>
       </x:c>
       <x:c r="D13" s="17"/>
       <x:c r="E13" s="17" t="n">
@@ -4076,7 +4144,7 @@
         <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="C14" s="17" t="n">
-        <x:v>0.43123729674796746</x:v>
+        <x:v>0.4316781094527364</x:v>
       </x:c>
       <x:c r="D14" s="17" t="n">
         <x:v>0.3636316666666667</x:v>
@@ -4099,13 +4167,13 @@
         <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="C15" s="17" t="n">
-        <x:v>0.4584121401419464</x:v>
+        <x:v>0.46327270736286097</x:v>
       </x:c>
       <x:c r="D15" s="17" t="n">
         <x:v>0.44483507740620487</x:v>
       </x:c>
       <x:c r="E15" s="17" t="n">
-        <x:v>0.46428749999999996</x:v>
+        <x:v>0.47762499999999997</x:v>
       </x:c>
       <x:c r="F15" s="17" t="n">
         <x:v>0.49477499999999996</x:v>
@@ -4119,16 +4187,16 @@
         <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="B16" s="25" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="C16" s="17" t="n">
-        <x:v>0.45165059809758934</x:v>
+        <x:v>0.46141401843584867</x:v>
       </x:c>
       <x:c r="D16" s="17" t="n">
         <x:v>0.38254856862232545</x:v>
       </x:c>
       <x:c r="E16" s="17" t="n">
-        <x:v>0.49453749999999996</x:v>
+        <x:v>0.5195</x:v>
       </x:c>
       <x:c r="F16" s="17" t="n">
         <x:v>0.49477499999999996</x:v>
@@ -4145,19 +4213,19 @@
         <x:v>2026-12-31</x:v>
       </x:c>
       <x:c r="C17" s="17" t="n">
-        <x:v>0.5131595499494372</x:v>
+        <x:v>0.5229995627802766</x:v>
       </x:c>
       <x:c r="D17" s="17" t="n">
-        <x:v>0.41951189241520126</x:v>
+        <x:v>0.4202758375398714</x:v>
       </x:c>
       <x:c r="E17" s="17" t="n">
-        <x:v>0.573964900822655</x:v>
+        <x:v>0.5964688772542405</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
-        <x:v>0.5510902207212565</x:v>
+        <x:v>0.552271008992256</x:v>
       </x:c>
       <x:c r="G17" s="17" t="n">
-        <x:v>0.5009128455312821</x:v>
+        <x:v>0.5017009236990078</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4168,19 +4236,19 @@
         <x:v>2027-03-31</x:v>
       </x:c>
       <x:c r="C18" s="17" t="n">
-        <x:v>0.5838014161122994</x:v>
+        <x:v>0.5935051470655859</x:v>
       </x:c>
       <x:c r="D18" s="17" t="n">
-        <x:v>0.4656938403212752</x:v>
+        <x:v>0.4673398551270709</x:v>
       </x:c>
       <x:c r="E18" s="17" t="n">
-        <x:v>0.6613572683659491</x:v>
+        <x:v>0.6808011881770635</x:v>
       </x:c>
       <x:c r="F18" s="17" t="n">
-        <x:v>0.616970387335722</x:v>
+        <x:v>0.6193267190642807</x:v>
       </x:c>
       <x:c r="G18" s="17" t="n">
-        <x:v>0.5814804824886135</x:v>
+        <x:v>0.5830271843081689</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4191,19 +4259,19 @@
         <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="C19" s="17" t="n">
-        <x:v>0.6609741939528238</x:v>
+        <x:v>0.6702136448373787</x:v>
       </x:c>
       <x:c r="D19" s="17" t="n">
-        <x:v>0.5219860028628462</x:v>
+        <x:v>0.5245890317621351</x:v>
       </x:c>
       <x:c r="E19" s="17" t="n">
-        <x:v>0.7512018452006073</x:v>
+        <x:v>0.7670137971277526</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
-        <x:v>0.6904941506847201</x:v>
+        <x:v>0.6938558057039086</x:v>
       </x:c>
       <x:c r="G19" s="17" t="n">
-        <x:v>0.669604082591502</x:v>
+        <x:v>0.6717619134028711</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4214,19 +4282,19 @@
         <x:v>2027-09-30</x:v>
       </x:c>
       <x:c r="C20" s="17" t="n">
-        <x:v>0.7400505147370063</x:v>
+        <x:v>0.7484056019235392</x:v>
       </x:c>
       <x:c r="D20" s="17" t="n">
-        <x:v>0.5883664976708365</x:v>
+        <x:v>0.5919116923360023</x:v>
       </x:c>
       <x:c r="E20" s="17" t="n">
-        <x:v>0.8355489742820248</x:v>
+        <x:v>0.847345194629627</x:v>
       </x:c>
       <x:c r="F20" s="17" t="n">
-        <x:v>0.767532135108189</x:v>
+        <x:v>0.771519152001999</x:v>
       </x:c>
       <x:c r="G20" s="17" t="n">
-        <x:v>0.7594853081263506</x:v>
+        <x:v>0.7619688824935531</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4237,19 +4305,19 @@
         <x:v>2027-12-31</x:v>
       </x:c>
       <x:c r="C21" s="17" t="n">
-        <x:v>0.814832346574145</x:v>
+        <x:v>0.8218754308129803</x:v>
       </x:c>
       <x:c r="D21" s="17" t="n">
-        <x:v>0.6632445350745001</x:v>
+        <x:v>0.6675717363225923</x:v>
       </x:c>
       <x:c r="E21" s="17" t="n">
-        <x:v>0.9056885837078396</x:v>
+        <x:v>0.9134787578279036</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:v>0.8417188367356241</x:v>
+        <x:v>0.8457604280448145</x:v>
       </x:c>
       <x:c r="G21" s="17" t="n">
-        <x:v>0.8429776734919401</x:v>
+        <x:v>0.845395776269385</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4260,19 +4328,19 @@
         <x:v>2028-03-31</x:v>
       </x:c>
       <x:c r="C22" s="17" t="n">
-        <x:v>0.8790181332273004</x:v>
+        <x:v>0.8844520818471866</x:v>
       </x:c>
       <x:c r="D22" s="17" t="n">
-        <x:v>0.7428320885130025</x:v>
+        <x:v>0.7475926341041975</x:v>
       </x:c>
       <x:c r="E22" s="17" t="n">
-        <x:v>0.9553023421503699</x:v>
+        <x:v>0.9596379122408556</x:v>
       </x:c>
       <x:c r="F22" s="17" t="n">
-        <x:v>0.9055396378770173</x:v>
+        <x:v>0.909004461475341</x:v>
       </x:c>
       <x:c r="G22" s="17" t="n">
-        <x:v>0.9114317496077905</x:v>
+        <x:v>0.9133955193622444</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4283,19 +4351,19 @@
         <x:v>2028-06-30</x:v>
       </x:c>
       <x:c r="C23" s="17" t="n">
-        <x:v>0.9283165342168052</x:v>
+        <x:v>0.9320987866474012</x:v>
       </x:c>
       <x:c r="D23" s="17" t="n">
-        <x:v>0.820954678700308</x:v>
+        <x:v>0.8256212592531782</x:v>
       </x:c>
       <x:c r="E23" s="17" t="n">
-        <x:v>0.9836016052557366</x:v>
+        <x:v>0.9855034454242547</x:v>
       </x:c>
       <x:c r="F23" s="17" t="n">
-        <x:v>0.952772721942952</x:v>
+        <x:v>0.9552024733547424</x:v>
       </x:c>
       <x:c r="G23" s="17" t="n">
-        <x:v>0.9589498550640618</x:v>
+        <x:v>0.9602303867818771</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4306,19 +4374,19 @@
         <x:v>2028-09-30</x:v>
       </x:c>
       <x:c r="C24" s="17" t="n">
-        <x:v>0.9619503679317483</x:v>
+        <x:v>0.9643049231635812</x:v>
       </x:c>
       <x:c r="D24" s="17" t="n">
-        <x:v>0.8899011632631341</x:v>
+        <x:v>0.8938773235175859</x:v>
       </x:c>
       <x:c r="E24" s="17" t="n">
-        <x:v>0.9957344087455272</x:v>
+        <x:v>0.9963351713992433</x:v>
       </x:c>
       <x:c r="F24" s="17" t="n">
-        <x:v>0.9813835870220199</x:v>
+        <x:v>0.9827039499618946</x:v>
       </x:c>
       <x:c r="G24" s="17" t="n">
-        <x:v>0.9853840670800804</x:v>
+        <x:v>0.986015173001708</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
@@ -4329,19 +4397,19 @@
         <x:v>2028-12-31</x:v>
       </x:c>
       <x:c r="C25" s="17" t="n">
-        <x:v>0.982311895144309</x:v>
+        <x:v>0.9836084379542608</x:v>
       </x:c>
       <x:c r="D25" s="17" t="n">
-        <x:v>0.9426962228960611</x:v>
+        <x:v>0.9455298336524652</x:v>
       </x:c>
       <x:c r="E25" s="17" t="n">
-        <x:v>0.9993007920949821</x:v>
+        <x:v>0.9994218464309694</x:v>
       </x:c>
       <x:c r="F25" s="17" t="n">
-        <x:v>0.9946672024336355</x:v>
+        <x:v>0.9951815650138214</x:v>
       </x:c>
       <x:c r="G25" s="17" t="n">
-        <x:v>0.996347921884617</x:v>
+        <x:v>0.996563545473006</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4350,9 +4418,9 @@
     <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a6bc9c47cb14cc2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R965847d0cb314e76"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0147c4dff9cc498e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b24a39c91640a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4852,12 +4920,2140 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56a29f38ff9e4c24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34da4859e8644913"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="72" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Supporting Capability Evidence</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="3"/>
+      <x:c r="B2" s="3"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+      <x:c r="E2" s="3"/>
+      <x:c r="F2" s="3"/>
+      <x:c r="G2" s="3"/>
+      <x:c r="H2" s="3"/>
+      <x:c r="I2" s="3"/>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>Release-day, vendor, and independent signals that inform interpretation but do not enter the direct economic-delegation basket unless the calculation contract explicitly promotes them.</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+    </x:row>
+    <x:row r="4"/>
+    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Evidence ID</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>Metric date</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str">
+        <x:v>Entity</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Unit</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>Caveat / comparability note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>evidence-001</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C6" s="25" t="str">
+        <x:v>2026-02-27</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>consumer subscribers</x:v>
+      </x:c>
+      <x:c r="F6" s="16"/>
+      <x:c r="G6" s="16" t="str">
+        <x:v>subscriptions</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>gate1-apnews-com-chatgpt-paid-consumers-observation</x:v>
+      </x:c>
+      <x:c r="I6" s="16" t="str">
+        <x:v>Direct executive statement reported by AP; latest disclosed, not a current estimate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>evidence-002</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="str">
+        <x:v>2026-06-02</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="str">
+        <x:v>OpenAI Codex</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="str">
+        <x:v>weekly active users</x:v>
+      </x:c>
+      <x:c r="F7" s="16"/>
+      <x:c r="G7" s="16" t="str">
+        <x:v>people</x:v>
+      </x:c>
+      <x:c r="H7" s="16" t="str">
+        <x:v>gate1-openai-com-codex-reach-observation-3</x:v>
+      </x:c>
+      <x:c r="I7" s="16" t="str">
+        <x:v>Selected agent/coding population</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>evidence-003</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C8" s="25" t="str">
+        <x:v>2025-11-05</x:v>
+      </x:c>
+      <x:c r="D8" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="str">
+        <x:v>ChatGPT for Work seats</x:v>
+      </x:c>
+      <x:c r="F8" s="16"/>
+      <x:c r="G8" s="16" t="str">
+        <x:v>seats</x:v>
+      </x:c>
+      <x:c r="H8" s="16" t="str">
+        <x:v>gate1-openai-com-openai-chatgpt-for-work-seats</x:v>
+      </x:c>
+      <x:c r="I8" s="16" t="str">
+        <x:v>Seats are not active users</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" hidden="0" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>evidence-004</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C9" s="25" t="str">
+        <x:v>2025-09-02</x:v>
+      </x:c>
+      <x:c r="D9" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>business customers</x:v>
+      </x:c>
+      <x:c r="F9" s="16"/>
+      <x:c r="G9" s="16" t="str">
+        <x:v>organizations</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="str">
+        <x:v>gate1-anthropic-com-anthropic-business-customers</x:v>
+      </x:c>
+      <x:c r="I9" s="16" t="str">
+        <x:v>Not consumer subscriptions or seats</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" hidden="0" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>evidence-005</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C10" s="25" t="str">
+        <x:v>2026-03-31</x:v>
+      </x:c>
+      <x:c r="D10" s="16" t="str">
+        <x:v>xAI/X</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="str">
+        <x:v>active paid subscriptions</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="n">
+        <x:v>6300000</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="str">
+        <x:v>subscriptions</x:v>
+      </x:c>
+      <x:c r="H10" s="16" t="str">
+        <x:v>gate1-sec-gov-grok-active-paid-subscriptions-observation</x:v>
+      </x:c>
+      <x:c r="I10" s="16" t="str">
+        <x:v>Includes X subscriptions with Grok access</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" hidden="0" customHeight="1">
+      <x:c r="A11" s="16" t="str">
+        <x:v>evidence-006</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="str">
+        <x:v>2026-03-31</x:v>
+      </x:c>
+      <x:c r="D11" s="16" t="str">
+        <x:v>Grok</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>monthly users of Grok features</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="n">
+        <x:v>117000000</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="str">
+        <x:v>people</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="str">
+        <x:v>gate1-sec-gov-grok-active-paid-subscriptions-observation</x:v>
+      </x:c>
+      <x:c r="I11" s="16" t="str">
+        <x:v>Feature usage is not task delegation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" hidden="0" customHeight="1">
+      <x:c r="A12" s="16" t="str">
+        <x:v>evidence-007</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D12" s="16" t="str">
+        <x:v>OpenClaw</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="str">
+        <x:v>GitHub stars</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="n">
+        <x:v>387590</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="str">
+        <x:v>stars</x:v>
+      </x:c>
+      <x:c r="H12" s="16" t="str">
+        <x:v>gate1-api-github-com-openclaw-github-stars-observation</x:v>
+      </x:c>
+      <x:c r="I12" s="16" t="str">
+        <x:v>Developer-interest proxy; not users</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" hidden="0" customHeight="1">
+      <x:c r="A13" s="16" t="str">
+        <x:v>evidence-008</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="str">
+        <x:v>OpenClaw</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="str">
+        <x:v>GitHub forks</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="n">
+        <x:v>81363</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="str">
+        <x:v>forks</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str">
+        <x:v>gate1-api-github-com-openclaw-github-stars-observation</x:v>
+      </x:c>
+      <x:c r="I13" s="16" t="str">
+        <x:v>Code-copy proxy; not users</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A14" s="16" t="str">
+        <x:v>evidence-009</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="str">
+        <x:v>2026-08-24</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="str">
+        <x:v>OpenClaw</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="str">
+        <x:v>npm downloads previous month</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="n">
+        <x:v>11371521</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="str">
+        <x:v>downloads</x:v>
+      </x:c>
+      <x:c r="H14" s="16" t="str">
+        <x:v>gate1-api-npmjs-org-openclaw-npm-monthly-downloads-observation</x:v>
+      </x:c>
+      <x:c r="I14" s="16" t="str">
+        <x:v>Includes repeated and automated downloads</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A15" s="16" t="str">
+        <x:v>evidence-010</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="str">
+        <x:v>2024-05-13</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>GPT-4o</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>METR 50% time horizon</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="str">
+        <x:v>minutes</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I15" s="16" t="str">
+        <x:v>Clean mostly technical tasks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="54" hidden="0" customHeight="1">
+      <x:c r="A16" s="16" t="str">
+        <x:v>evidence-011</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="str">
+        <x:v>2026-04-07</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="str">
+        <x:v>Claude Mythos Preview</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="str">
+        <x:v>METR 50% time horizon</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="n">
+        <x:v>1044.8</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="str">
+        <x:v>minutes</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I16" s="16" t="str">
+        <x:v>METR warns estimates above 16h are unreliable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A17" s="16" t="str">
+        <x:v>evidence-012</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="str">
+        <x:v>2024-05-13</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="str">
+        <x:v>GPT-4o</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="str">
+        <x:v>METR 80% time horizon</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="n">
+        <x:v>1.3</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="str">
+        <x:v>minutes</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I17" s="16" t="str">
+        <x:v>Clean mostly technical tasks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A18" s="16" t="str">
+        <x:v>evidence-013</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="str">
+        <x:v>Capability</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="str">
+        <x:v>2026-04-07</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="str">
+        <x:v>Claude Mythos Preview</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="str">
+        <x:v>METR 80% time horizon</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="n">
+        <x:v>185.9</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="str">
+        <x:v>minutes</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I18" s="16" t="str">
+        <x:v>Clean mostly technical tasks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A19" s="16" t="str">
+        <x:v>evidence-014</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="str">
+        <x:v>Computer use</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="str">
+        <x:v>OSWorld 2.0 partial-credit score</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="n">
+        <x:v>62.6</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H19" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I19" s="16" t="str">
+        <x:v>Not binary full completion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="54" hidden="0" customHeight="1">
+      <x:c r="A20" s="16" t="str">
+        <x:v>evidence-015</x:v>
+      </x:c>
+      <x:c r="B20" s="16" t="str">
+        <x:v>Computer use</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="str">
+        <x:v>2026-06-25</x:v>
+      </x:c>
+      <x:c r="D20" s="16" t="str">
+        <x:v>Claude Opus 4.8</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="str">
+        <x:v>OSWorld 2.0 binary full completion</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="n">
+        <x:v>20.6</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str">
+        <x:v>gate1-osworld-v2-xlang-ai-osworld-source</x:v>
+      </x:c>
+      <x:c r="I20" s="16" t="str">
+        <x:v>500-step configuration in benchmark paper</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="54" hidden="0" customHeight="1">
+      <x:c r="A21" s="16" t="str">
+        <x:v>evidence-016</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="str">
+        <x:v>Claude Opus 5</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="str">
+        <x:v>Vending-Bench 2 mean profit</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="n">
+        <x:v>11181.87</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str">
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
+      </x:c>
+      <x:c r="I21" s="16" t="str">
+        <x:v>Simulated business; five runs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" hidden="0" customHeight="1">
+      <x:c r="A22" s="16" t="str">
+        <x:v>evidence-017</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D22" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="str">
+        <x:v>Vending-Bench 2 mean profit</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="n">
+        <x:v>9619.37</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str">
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
+      </x:c>
+      <x:c r="I22" s="16" t="str">
+        <x:v>Simulated business; five runs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="54" hidden="0" customHeight="1">
+      <x:c r="A23" s="16" t="str">
+        <x:v>evidence-018</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D23" s="16" t="str">
+        <x:v>Grok 4.6</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="str">
+        <x:v>Vending-Bench 2 mean profit</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="n">
+        <x:v>9047</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str">
+        <x:v>gate1-andonlabs-com-vending-bench-2-benchmark</x:v>
+      </x:c>
+      <x:c r="I23" s="16" t="str">
+        <x:v>Simulated business; five runs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A24" s="16" t="str">
+        <x:v>evidence-019</x:v>
+      </x:c>
+      <x:c r="B24" s="16" t="str">
+        <x:v>Business</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D24" s="16" t="str">
+        <x:v>Qwen 3.8 Max</x:v>
+      </x:c>
+      <x:c r="E24" s="16" t="str">
+        <x:v>tau3 Banking pass rate</x:v>
+      </x:c>
+      <x:c r="F24" s="16" t="n">
+        <x:v>55.2</x:v>
+      </x:c>
+      <x:c r="G24" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H24" s="16" t="str">
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
+      </x:c>
+      <x:c r="I24" s="16" t="str">
+        <x:v>Current top observed; task/policy benchmark</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A25" s="16" t="str">
+        <x:v>evidence-020</x:v>
+      </x:c>
+      <x:c r="B25" s="16" t="str">
+        <x:v>Broad work</x:v>
+      </x:c>
+      <x:c r="C25" s="25" t="str">
+        <x:v>2026-06-26</x:v>
+      </x:c>
+      <x:c r="D25" s="16" t="str">
+        <x:v>best reported broad agent</x:v>
+      </x:c>
+      <x:c r="E25" s="16" t="str">
+        <x:v>Agents' Last Exam CLI</x:v>
+      </x:c>
+      <x:c r="F25" s="16" t="n">
+        <x:v>25.2</x:v>
+      </x:c>
+      <x:c r="G25" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H25" s="16" t="str">
+        <x:v>gate1-rdi-berkeley-edu-best-reported-broad-agent-agents-last-exam-cli</x:v>
+      </x:c>
+      <x:c r="I25" s="16" t="str">
+        <x:v>1500+ tasks across 55 occupations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="54" hidden="0" customHeight="1">
+      <x:c r="A26" s="16" t="str">
+        <x:v>evidence-021</x:v>
+      </x:c>
+      <x:c r="B26" s="16" t="str">
+        <x:v>Harness</x:v>
+      </x:c>
+      <x:c r="C26" s="25" t="str">
+        <x:v>2025-10-28</x:v>
+      </x:c>
+      <x:c r="D26" s="16" t="str">
+        <x:v>o3</x:v>
+      </x:c>
+      <x:c r="E26" s="16" t="str">
+        <x:v>OSWorld baseline at 15 steps</x:v>
+      </x:c>
+      <x:c r="F26" s="16" t="n">
+        <x:v>8.3</x:v>
+      </x:c>
+      <x:c r="G26" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H26" s="16" t="str">
+        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
+      </x:c>
+      <x:c r="I26" s="16" t="str">
+        <x:v>Compare only with same study and step budget</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A27" s="16" t="str">
+        <x:v>evidence-022</x:v>
+      </x:c>
+      <x:c r="B27" s="16" t="str">
+        <x:v>Harness</x:v>
+      </x:c>
+      <x:c r="C27" s="25" t="str">
+        <x:v>2025-10-28</x:v>
+      </x:c>
+      <x:c r="D27" s="16" t="str">
+        <x:v>o3 plus MCP tools</x:v>
+      </x:c>
+      <x:c r="E27" s="16" t="str">
+        <x:v>OSWorld-MCP at 15 steps</x:v>
+      </x:c>
+      <x:c r="F27" s="16" t="n">
+        <x:v>20.4</x:v>
+      </x:c>
+      <x:c r="G27" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H27" s="16" t="str">
+        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
+      </x:c>
+      <x:c r="I27" s="16" t="str">
+        <x:v>Controlled tool/harness uplift</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="54" hidden="0" customHeight="1">
+      <x:c r="A28" s="16" t="str">
+        <x:v>evidence-023</x:v>
+      </x:c>
+      <x:c r="B28" s="16" t="str">
+        <x:v>Harness</x:v>
+      </x:c>
+      <x:c r="C28" s="25" t="str">
+        <x:v>2025-10-28</x:v>
+      </x:c>
+      <x:c r="D28" s="16" t="str">
+        <x:v>Claude 4 Sonnet</x:v>
+      </x:c>
+      <x:c r="E28" s="16" t="str">
+        <x:v>OSWorld baseline at 50 steps</x:v>
+      </x:c>
+      <x:c r="F28" s="16" t="n">
+        <x:v>40.1</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H28" s="16" t="str">
+        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
+      </x:c>
+      <x:c r="I28" s="16" t="str">
+        <x:v>Compare only with same study and step budget</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A29" s="16" t="str">
+        <x:v>evidence-024</x:v>
+      </x:c>
+      <x:c r="B29" s="16" t="str">
+        <x:v>Harness</x:v>
+      </x:c>
+      <x:c r="C29" s="25" t="str">
+        <x:v>2025-10-28</x:v>
+      </x:c>
+      <x:c r="D29" s="16" t="str">
+        <x:v>Claude 4 Sonnet plus MCP tools</x:v>
+      </x:c>
+      <x:c r="E29" s="16" t="str">
+        <x:v>OSWorld-MCP at 50 steps</x:v>
+      </x:c>
+      <x:c r="F29" s="16" t="n">
+        <x:v>43.3</x:v>
+      </x:c>
+      <x:c r="G29" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H29" s="16" t="str">
+        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
+      </x:c>
+      <x:c r="I29" s="16" t="str">
+        <x:v>Controlled tool/harness uplift</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A30" s="16" t="str">
+        <x:v>evidence-025</x:v>
+      </x:c>
+      <x:c r="B30" s="16" t="str">
+        <x:v>Factuality</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="str">
+        <x:v>2026-08-19</x:v>
+      </x:c>
+      <x:c r="D30" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E30" s="16" t="str">
+        <x:v>factual-error reduction vs GPT-5.5 Instant</x:v>
+      </x:c>
+      <x:c r="F30" s="16"/>
+      <x:c r="G30" s="16" t="str">
+        <x:v>percent relative</x:v>
+      </x:c>
+      <x:c r="H30" s="16" t="str">
+        <x:v>gate1-deploymentsafety-openai-com-gpt-5-6-sol-factual-error-reduction-vs-gpt-5</x:v>
+      </x:c>
+      <x:c r="I30" s="16" t="str">
+        <x:v>Three curated sets; not production prevalence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A31" s="16" t="str">
+        <x:v>evidence-026</x:v>
+      </x:c>
+      <x:c r="B31" s="16" t="str">
+        <x:v>Memory</x:v>
+      </x:c>
+      <x:c r="C31" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D31" s="16" t="str">
+        <x:v>hybrid memory system</x:v>
+      </x:c>
+      <x:c r="E31" s="16" t="str">
+        <x:v>LongMemEval task-averaged accuracy</x:v>
+      </x:c>
+      <x:c r="F31" s="16" t="n">
+        <x:v>86.1</x:v>
+      </x:c>
+      <x:c r="G31" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H31" s="16" t="str">
+        <x:v>gate1-redis-github-io-hybrid-memory-system-longmemeval-task-averaged-accuracy</x:v>
+      </x:c>
+      <x:c r="I31" s="16" t="str">
+        <x:v>500-question retrieval benchmark; not continual learning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A32" s="16" t="str">
+        <x:v>evidence-027</x:v>
+      </x:c>
+      <x:c r="B32" s="16" t="str">
+        <x:v>AI R&amp;D</x:v>
+      </x:c>
+      <x:c r="C32" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D32" s="16" t="str">
+        <x:v>GPT-5.5</x:v>
+      </x:c>
+      <x:c r="E32" s="16" t="str">
+        <x:v>OpenAI internal RSI index</x:v>
+      </x:c>
+      <x:c r="F32" s="16" t="n">
+        <x:v>41.7</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="H32" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I32" s="16" t="str">
+        <x:v>Vendor internal evaluation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A33" s="16" t="str">
+        <x:v>evidence-028</x:v>
+      </x:c>
+      <x:c r="B33" s="16" t="str">
+        <x:v>AI R&amp;D</x:v>
+      </x:c>
+      <x:c r="C33" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D33" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E33" s="16" t="str">
+        <x:v>OpenAI internal RSI index</x:v>
+      </x:c>
+      <x:c r="F33" s="16" t="n">
+        <x:v>57.9</x:v>
+      </x:c>
+      <x:c r="G33" s="16" t="str">
+        <x:v>score</x:v>
+      </x:c>
+      <x:c r="H33" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I33" s="16" t="str">
+        <x:v>Vendor internal evaluation; below OpenAI High threshold</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A34" s="16" t="str">
+        <x:v>evidence-029</x:v>
+      </x:c>
+      <x:c r="B34" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C34" s="25" t="str">
+        <x:v>2025-08-07</x:v>
+      </x:c>
+      <x:c r="D34" s="16" t="str">
+        <x:v>GPT-5</x:v>
+      </x:c>
+      <x:c r="E34" s="16" t="str">
+        <x:v>METR 50% time horizon</x:v>
+      </x:c>
+      <x:c r="F34" s="16" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="G34" s="16" t="str">
+        <x:v>minutes</x:v>
+      </x:c>
+      <x:c r="H34" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I34" s="16" t="str">
+        <x:v>Start of 12-month release-frontier window; mostly technical tasks</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A35" s="16" t="str">
+        <x:v>evidence-030</x:v>
+      </x:c>
+      <x:c r="B35" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C35" s="25" t="str">
+        <x:v>2026-04-07</x:v>
+      </x:c>
+      <x:c r="D35" s="16" t="str">
+        <x:v>Claude Mythos Preview</x:v>
+      </x:c>
+      <x:c r="E35" s="16" t="str">
+        <x:v>METR 50% time horizon</x:v>
+      </x:c>
+      <x:c r="F35" s="16" t="n">
+        <x:v>1044.8</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="str">
+        <x:v>minutes</x:v>
+      </x:c>
+      <x:c r="H35" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I35" s="16" t="str">
+        <x:v>5.15x vs GPT-5; METR warns values above 16 hours are unreliable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A36" s="16" t="str">
+        <x:v>evidence-031</x:v>
+      </x:c>
+      <x:c r="B36" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C36" s="25" t="str">
+        <x:v>2025-09-29</x:v>
+      </x:c>
+      <x:c r="D36" s="16" t="str">
+        <x:v>Claude Sonnet 4.5</x:v>
+      </x:c>
+      <x:c r="E36" s="16" t="str">
+        <x:v>OSWorld-Verified success</x:v>
+      </x:c>
+      <x:c r="F36" s="16" t="n">
+        <x:v>61.4</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H36" s="16" t="str">
+        <x:v>gate1-anthropic-com-osworld-observation-source</x:v>
+      </x:c>
+      <x:c r="I36" s="16" t="str">
+        <x:v>Fixed benchmark release-frontier point</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A37" s="16" t="str">
+        <x:v>evidence-032</x:v>
+      </x:c>
+      <x:c r="B37" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C37" s="25" t="str">
+        <x:v>2026-04-23</x:v>
+      </x:c>
+      <x:c r="D37" s="16" t="str">
+        <x:v>GPT-5.5</x:v>
+      </x:c>
+      <x:c r="E37" s="16" t="str">
+        <x:v>OSWorld-Verified success</x:v>
+      </x:c>
+      <x:c r="F37" s="16" t="n">
+        <x:v>78.7</x:v>
+      </x:c>
+      <x:c r="G37" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H37" s="16" t="str">
+        <x:v>gate1-openai-com-osworld-observation-source-2</x:v>
+      </x:c>
+      <x:c r="I37" s="16" t="str">
+        <x:v>17.3pp release-frontier gain; benchmark nearing saturation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A38" s="16" t="str">
+        <x:v>evidence-033</x:v>
+      </x:c>
+      <x:c r="B38" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C38" s="25" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="D38" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E38" s="16" t="str">
+        <x:v>OSWorld 2.0 partial reward</x:v>
+      </x:c>
+      <x:c r="F38" s="16" t="n">
+        <x:v>62.6</x:v>
+      </x:c>
+      <x:c r="G38" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H38" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I38" s="16" t="str">
+        <x:v>Harder benchmark; do not splice to OSWorld-Verified</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A39" s="16" t="str">
+        <x:v>evidence-034</x:v>
+      </x:c>
+      <x:c r="B39" s="16" t="str">
+        <x:v>Consumer benchmark</x:v>
+      </x:c>
+      <x:c r="C39" s="25" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="D39" s="16" t="str">
+        <x:v>Claude Opus 4.6</x:v>
+      </x:c>
+      <x:c r="E39" s="16" t="str">
+        <x:v>MyPCBench perfect completion</x:v>
+      </x:c>
+      <x:c r="F39" s="16" t="n">
+        <x:v>58.2</x:v>
+      </x:c>
+      <x:c r="G39" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H39" s="16" t="str">
+        <x:v>gate1-github-com-mypcbench-source</x:v>
+      </x:c>
+      <x:c r="I39" s="16" t="str">
+        <x:v>Closest canonical consumer reference; not a current frontier because newer agents are unevaluated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A40" s="16" t="str">
+        <x:v>evidence-035</x:v>
+      </x:c>
+      <x:c r="B40" s="16" t="str">
+        <x:v>Consumer benchmark</x:v>
+      </x:c>
+      <x:c r="C40" s="25" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="D40" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E40" s="16" t="str">
+        <x:v>MyPCBench perfect completion</x:v>
+      </x:c>
+      <x:c r="F40" s="16" t="n">
+        <x:v>55.4</x:v>
+      </x:c>
+      <x:c r="G40" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H40" s="16" t="str">
+        <x:v>gate1-github-com-mypcbench-source</x:v>
+      </x:c>
+      <x:c r="I40" s="16" t="str">
+        <x:v>Up 10.3pp from GPT-5.5 in canonical 100-step evaluation; Opus 5 and Fable 5 unevaluated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A41" s="16" t="str">
+        <x:v>evidence-036</x:v>
+      </x:c>
+      <x:c r="B41" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C41" s="25" t="str">
+        <x:v>2026-07-19</x:v>
+      </x:c>
+      <x:c r="D41" s="16" t="str">
+        <x:v>Qwen 3.8 Max</x:v>
+      </x:c>
+      <x:c r="E41" s="16" t="str">
+        <x:v>tau3 Banking pass@1</x:v>
+      </x:c>
+      <x:c r="F41" s="16" t="n">
+        <x:v>55.2</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H41" s="16" t="str">
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
+      </x:c>
+      <x:c r="I41" s="16" t="str">
+        <x:v>System frontier; retrieval and reasoning configuration are part of the result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A42" s="16" t="str">
+        <x:v>evidence-037</x:v>
+      </x:c>
+      <x:c r="B42" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C42" s="25" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="D42" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E42" s="16" t="str">
+        <x:v>Agents Last Exam current comparison</x:v>
+      </x:c>
+      <x:c r="F42" s="16" t="n">
+        <x:v>52.7</x:v>
+      </x:c>
+      <x:c r="G42" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H42" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I42" s="16" t="str">
+        <x:v>Up 5.8pp from GPT-5.5 under OpenAI's current comparison configuration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="54" hidden="0" customHeight="1">
+      <x:c r="A43" s="16" t="str">
+        <x:v>evidence-038</x:v>
+      </x:c>
+      <x:c r="B43" s="16" t="str">
+        <x:v>Capability velocity</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="D43" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="E43" s="16" t="str">
+        <x:v>AutomationBench current comparison</x:v>
+      </x:c>
+      <x:c r="F43" s="16" t="n">
+        <x:v>18.1</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H43" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I43" s="16" t="str">
+        <x:v>Up 5.2pp from GPT-5.5 but low absolute completion</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="108" hidden="0" customHeight="1">
+      <x:c r="A44" s="16" t="str">
+        <x:v>evidence-039</x:v>
+      </x:c>
+      <x:c r="B44" s="16" t="str">
+        <x:v>Professional capability</x:v>
+      </x:c>
+      <x:c r="C44" s="25" t="str">
+        <x:v>2025-08-07</x:v>
+      </x:c>
+      <x:c r="D44" s="16" t="str">
+        <x:v>GPT-5</x:v>
+      </x:c>
+      <x:c r="E44" s="16" t="str">
+        <x:v>Remote Labor Index V1 Automation Rate</x:v>
+      </x:c>
+      <x:c r="F44" s="16" t="n">
+        <x:v>1.67</x:v>
+      </x:c>
+      <x:c r="G44" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H44" s="16" t="str">
+        <x:v>gate1-labs-scale-com-remote-labor-index-source</x:v>
+      </x:c>
+      <x:c r="I44" s="16" t="str">
+        <x:v>Start of retrospective fixed-budget remote-work frontier; not the consumer task distribution</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A45" s="16" t="str">
+        <x:v>evidence-040</x:v>
+      </x:c>
+      <x:c r="B45" s="16" t="str">
+        <x:v>Professional capability</x:v>
+      </x:c>
+      <x:c r="C45" s="25" t="str">
+        <x:v>2026-06-09</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="str">
+        <x:v>Claude Fable 5</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="str">
+        <x:v>Remote Labor Index V1 Automation Rate</x:v>
+      </x:c>
+      <x:c r="F45" s="16" t="n">
+        <x:v>15.8</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H45" s="16" t="str">
+        <x:v>gate1-labs-scale-com-remote-labor-index-source</x:v>
+      </x:c>
+      <x:c r="I45" s="16" t="str">
+        <x:v>Professional-work comparator; 9.46x and +14.13pp versus GPT-5 over 306 release-date days</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A46" s="16" t="str">
+        <x:v>evidence-041</x:v>
+      </x:c>
+      <x:c r="B46" s="16" t="str">
+        <x:v>Consumer benchmark</x:v>
+      </x:c>
+      <x:c r="C46" s="25" t="str">
+        <x:v>2026-08-25</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="str">
+        <x:v>Claude Opus 4.8</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="str">
+        <x:v>MyPCBench perfect completion</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H46" s="16" t="str">
+        <x:v>gate1-mypcbench-pages-dev-mypcbench-source</x:v>
+      </x:c>
+      <x:c r="I46" s="16" t="str">
+        <x:v>Self-reported computer-only run with 200-step budget; not comparable to canonical 100-step series; Opus 5 and Fable 5 absent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="259.20001220703125" hidden="0" customHeight="1">
+      <x:c r="A47" s="16" t="str">
+        <x:v>evidence-042</x:v>
+      </x:c>
+      <x:c r="B47" s="16" t="str">
+        <x:v>Abstract reasoning</x:v>
+      </x:c>
+      <x:c r="C47" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="str">
+        <x:v>GPT-6 Astra · OpenAI Responses API harness</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="str">
+        <x:v>ARC-AGI-3 score</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="n">
+        <x:v>99.9</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H47" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I47" s="16" t="str">
+        <x:v>Maximum-at-any-effort vendor result using persisted reasoning and compaction. It is a striking general-reasoning result, but ARC-AGI-3 is not an economic delegation task and therefore is not promoted into the forecast-driving basket.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="226.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A48" s="16" t="str">
+        <x:v>evidence-043</x:v>
+      </x:c>
+      <x:c r="B48" s="16" t="str">
+        <x:v>Computer use</x:v>
+      </x:c>
+      <x:c r="C48" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="str">
+        <x:v>OSWorld 2.0 offline partial score</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="n">
+        <x:v>72.6</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H48" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I48" s="16" t="str">
+        <x:v>Vendor result on OSWorld 2.0 v2026.08.08 offline tasks, reported as partial score. OpenAI also reports roughly 40 minutes per task versus about 75 minutes for GPT-5.6 Sol; do not splice this series to OSWorld-Verified or strict full-completion scores.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="216" hidden="0" customHeight="1">
+      <x:c r="A49" s="16" t="str">
+        <x:v>evidence-044</x:v>
+      </x:c>
+      <x:c r="B49" s="16" t="str">
+        <x:v>Business workflows</x:v>
+      </x:c>
+      <x:c r="C49" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E49" s="16" t="str">
+        <x:v>AutomationBench vendor evaluation</x:v>
+      </x:c>
+      <x:c r="F49" s="16" t="n">
+        <x:v>41.4</x:v>
+      </x:c>
+      <x:c r="G49" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H49" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I49" s="16" t="str">
+        <x:v>OpenAI's release-table result. It is kept out of the direct basket because the forecast pins the public 600-task table, while benchmark maintainers distinguish that public set from the harder held-out private leaderboard.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A50" s="16" t="str">
+        <x:v>evidence-045</x:v>
+      </x:c>
+      <x:c r="B50" s="16" t="str">
+        <x:v>Broad work</x:v>
+      </x:c>
+      <x:c r="C50" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E50" s="16" t="str">
+        <x:v>Agents' Last Exam</x:v>
+      </x:c>
+      <x:c r="F50" s="16" t="n">
+        <x:v>59.3</x:v>
+      </x:c>
+      <x:c r="G50" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H50" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I50" s="16" t="str">
+        <x:v>Vendor evaluation across broad professional tasks. Retained as supporting evidence because its release configuration is not the pinned CLI series used elsewhere in the ledger.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="205.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A51" s="16" t="str">
+        <x:v>evidence-046</x:v>
+      </x:c>
+      <x:c r="B51" s="16" t="str">
+        <x:v>Alignment</x:v>
+      </x:c>
+      <x:c r="C51" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D51" s="16" t="str">
+        <x:v>GPT-6 Astra without production safeguards</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="str">
+        <x:v>Impossible-task runs that exceeded the authorized target</x:v>
+      </x:c>
+      <x:c r="F51" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G51" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H51" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I51" s="16" t="str">
+        <x:v>OpenAI internal evaluation informed by the Hugging Face incident; the comparison condition reports 48% for GPT-5.6 Sol. This is vendor evidence about scope respect, not a calibrated deployment failure rate.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="226.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A52" s="16" t="str">
+        <x:v>evidence-047</x:v>
+      </x:c>
+      <x:c r="B52" s="16" t="str">
+        <x:v>Business workflows</x:v>
+      </x:c>
+      <x:c r="C52" s="25" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="D52" s="16" t="str">
+        <x:v>Claude Fable 5.1</x:v>
+      </x:c>
+      <x:c r="E52" s="16" t="str">
+        <x:v>AutomationBench vendor evaluation</x:v>
+      </x:c>
+      <x:c r="F52" s="16" t="n">
+        <x:v>31.4</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H52" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="I52" s="16" t="str">
+        <x:v>Anthropic vendor result with production safeguards enabled. Retained as supporting evidence because the forecast pins AutomationBench's public 600-task table, which is distinct from the held-out official leaderboard.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A53" s="16" t="str">
+        <x:v>evidence-048</x:v>
+      </x:c>
+      <x:c r="B53" s="16" t="str">
+        <x:v>Computer use</x:v>
+      </x:c>
+      <x:c r="C53" s="25" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="D53" s="16" t="str">
+        <x:v>Claude Fable 5.1</x:v>
+      </x:c>
+      <x:c r="E53" s="16" t="str">
+        <x:v>OSWorld 2.0 partial score</x:v>
+      </x:c>
+      <x:c r="F53" s="16" t="n">
+        <x:v>77.9</x:v>
+      </x:c>
+      <x:c r="G53" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H53" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="I53" s="16" t="str">
+        <x:v>Anthropic vendor result with production safeguards enabled. Partial scoring is not comparable with strict full completion or the older OSWorld-Verified series.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="183.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A54" s="16" t="str">
+        <x:v>evidence-049</x:v>
+      </x:c>
+      <x:c r="B54" s="16" t="str">
+        <x:v>Computer use</x:v>
+      </x:c>
+      <x:c r="C54" s="25" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="D54" s="16" t="str">
+        <x:v>Claude Fable 5.1</x:v>
+      </x:c>
+      <x:c r="E54" s="16" t="str">
+        <x:v>OSWorld 2.0 strict completion</x:v>
+      </x:c>
+      <x:c r="F54" s="16" t="n">
+        <x:v>41.7</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H54" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="I54" s="16" t="str">
+        <x:v>Anthropic vendor result with production safeguards enabled. Keep separate from the 77.9% partial score and from differently budgeted OSWorld configurations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="194.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A55" s="16" t="str">
+        <x:v>evidence-050</x:v>
+      </x:c>
+      <x:c r="B55" s="16" t="str">
+        <x:v>Professional capability</x:v>
+      </x:c>
+      <x:c r="C55" s="25" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="str">
+        <x:v>Claude Fable 5.1</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="str">
+        <x:v>GDPval-AA v2 Elo</x:v>
+      </x:c>
+      <x:c r="F55" s="16" t="n">
+        <x:v>1853</x:v>
+      </x:c>
+      <x:c r="G55" s="16" t="str">
+        <x:v>Elo</x:v>
+      </x:c>
+      <x:c r="H55" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="I55" s="16" t="str">
+        <x:v>Vendor-reported Elo. It remains ungraded because the forecast contract forbids rescaling a leaderboard without a fixed reference opponent or stable win-rate transformation.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I2"/>
+    <x:mergeCell ref="A3:I3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21276c5d015e4247"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="60" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Model Release and Availability Signals</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="3"/>
+      <x:c r="B2" s="3"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+      <x:c r="E2" s="3"/>
+      <x:c r="F2" s="3"/>
+      <x:c r="G2" s="3"/>
+      <x:c r="H2" s="3"/>
+      <x:c r="I2" s="3"/>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>Dated release metadata used to align observations and distinguish limited, trusted-access, and generally available deployments.</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+    </x:row>
+    <x:row r="4"/>
+    <x:row r="5" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Release ID</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Provider</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>Model</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str">
+        <x:v>Release date</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>Availability stage</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Availability scope</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Parent release</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>openai_gpt5_20250807</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>GPT-5</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="str">
+        <x:v>2025-08-07</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="str">
+        <x:v>ChatGPT API and agent products</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="str"/>
+      <x:c r="H6" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-release</x:v>
+      </x:c>
+      <x:c r="I6" s="16" t="str">
+        <x:v>First GPT-5 release represented in the benchmark data</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>anthropic_sonnet45_20250929</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="str">
+        <x:v>Claude Sonnet 4.5</x:v>
+      </x:c>
+      <x:c r="D7" s="25" t="str">
+        <x:v>2025-09-29</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="str"/>
+      <x:c r="H7" s="16" t="str">
+        <x:v>gate1-anthropic-com-osworld-observation-source</x:v>
+      </x:c>
+      <x:c r="I7" s="16" t="str"/>
+    </x:row>
+    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>anthropic_opus45_20251124</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C8" s="16" t="str">
+        <x:v>Claude Opus 4.5</x:v>
+      </x:c>
+      <x:c r="D8" s="25" t="str">
+        <x:v>2025-11-24</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F8" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G8" s="16" t="str"/>
+      <x:c r="H8" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-5-release</x:v>
+      </x:c>
+      <x:c r="I8" s="16" t="str"/>
+    </x:row>
+    <x:row r="9" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>openai_gpt52_20251211</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>GPT-5.2</x:v>
+      </x:c>
+      <x:c r="D9" s="25" t="str">
+        <x:v>2025-12-11</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F9" s="16" t="str">
+        <x:v>ChatGPT API and agent products</x:v>
+      </x:c>
+      <x:c r="G9" s="16" t="str">
+        <x:v>openai_gpt5_20250807</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-2-release</x:v>
+      </x:c>
+      <x:c r="I9" s="16" t="str">
+        <x:v>Release date verified by benchmark source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>anthropic_opus46_20260205</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="str">
+        <x:v>Claude Opus 4.6</x:v>
+      </x:c>
+      <x:c r="D10" s="25" t="str">
+        <x:v>2026-02-05</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F10" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G10" s="16" t="str">
+        <x:v>anthropic_opus45_20251124</x:v>
+      </x:c>
+      <x:c r="H10" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-6-release</x:v>
+      </x:c>
+      <x:c r="I10" s="16" t="str"/>
+    </x:row>
+    <x:row r="11" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A11" s="16" t="str">
+        <x:v>openai_gpt54_20260305</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>GPT-5.4</x:v>
+      </x:c>
+      <x:c r="D11" s="25" t="str">
+        <x:v>2026-03-05</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F11" s="16" t="str">
+        <x:v>ChatGPT API and Codex</x:v>
+      </x:c>
+      <x:c r="G11" s="16" t="str">
+        <x:v>openai_gpt52_20251211</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="str">
+        <x:v>gate1-openai-com-osworld-observation-source</x:v>
+      </x:c>
+      <x:c r="I11" s="16" t="str"/>
+    </x:row>
+    <x:row r="12" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A12" s="16" t="str">
+        <x:v>openai_gpt54mini_20260317</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="str">
+        <x:v>GPT-5.4 mini</x:v>
+      </x:c>
+      <x:c r="D12" s="25" t="str">
+        <x:v>2026-03-17</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="str">
+        <x:v>ChatGPT API and Codex</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="str">
+        <x:v>openai_gpt54_20260305</x:v>
+      </x:c>
+      <x:c r="H12" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-4-mini-release</x:v>
+      </x:c>
+      <x:c r="I12" s="16" t="str">
+        <x:v>Smaller capability tier rather than direct flagship successor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" hidden="0" customHeight="1">
+      <x:c r="A13" s="16" t="str">
+        <x:v>anthropic_mythos_preview_20260407</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C13" s="16" t="str">
+        <x:v>Claude Mythos Preview</x:v>
+      </x:c>
+      <x:c r="D13" s="25" t="str">
+        <x:v>2026-04-07</x:v>
+      </x:c>
+      <x:c r="E13" s="16" t="str">
+        <x:v>preview</x:v>
+      </x:c>
+      <x:c r="F13" s="16" t="str">
+        <x:v>Limited preview</x:v>
+      </x:c>
+      <x:c r="G13" s="16" t="str">
+        <x:v>anthropic_opus46_20260205</x:v>
+      </x:c>
+      <x:c r="H13" s="16" t="str">
+        <x:v>gate1-metr-org-metr-time-horizon-source</x:v>
+      </x:c>
+      <x:c r="I13" s="16" t="str">
+        <x:v>Release represented through METR evaluation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A14" s="16" t="str">
+        <x:v>anthropic_opus47_20260416</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C14" s="16" t="str">
+        <x:v>Claude Opus 4.7</x:v>
+      </x:c>
+      <x:c r="D14" s="25" t="str">
+        <x:v>2026-04-16</x:v>
+      </x:c>
+      <x:c r="E14" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F14" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G14" s="16" t="str">
+        <x:v>anthropic_opus46_20260205</x:v>
+      </x:c>
+      <x:c r="H14" s="16" t="str">
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
+      </x:c>
+      <x:c r="I14" s="16" t="str">
+        <x:v>Release date verified by benchmark source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A15" s="16" t="str">
+        <x:v>openai_gpt55_20260423</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>GPT-5.5</x:v>
+      </x:c>
+      <x:c r="D15" s="25" t="str">
+        <x:v>2026-04-23</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str">
+        <x:v>ChatGPT API and Codex</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="str">
+        <x:v>openai_gpt54_20260305</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str">
+        <x:v>gate1-openai-com-osworld-observation-source-2</x:v>
+      </x:c>
+      <x:c r="I15" s="16" t="str"/>
+    </x:row>
+    <x:row r="16" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A16" s="16" t="str">
+        <x:v>anthropic_opus48_20260528</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>Claude Opus 4.8</x:v>
+      </x:c>
+      <x:c r="D16" s="25" t="str">
+        <x:v>2026-05-28</x:v>
+      </x:c>
+      <x:c r="E16" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F16" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G16" s="16" t="str">
+        <x:v>anthropic_opus47_20260416</x:v>
+      </x:c>
+      <x:c r="H16" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-8-release</x:v>
+      </x:c>
+      <x:c r="I16" s="16" t="str"/>
+    </x:row>
+    <x:row r="17" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A17" s="16" t="str">
+        <x:v>anthropic_fable5_20260609</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="str">
+        <x:v>Claude Fable 5</x:v>
+      </x:c>
+      <x:c r="D17" s="25" t="str">
+        <x:v>2026-06-09</x:v>
+      </x:c>
+      <x:c r="E17" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F17" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G17" s="16" t="str">
+        <x:v>anthropic_opus48_20260528</x:v>
+      </x:c>
+      <x:c r="H17" s="16" t="str">
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
+      </x:c>
+      <x:c r="I17" s="16" t="str">
+        <x:v>Release date verified by benchmark source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A18" s="16" t="str">
+        <x:v>openai_gpt56sol_20260709</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="str">
+        <x:v>GPT-5.6 Sol</x:v>
+      </x:c>
+      <x:c r="D18" s="25" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="E18" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F18" s="16" t="str">
+        <x:v>ChatGPT API and Codex</x:v>
+      </x:c>
+      <x:c r="G18" s="16" t="str">
+        <x:v>openai_gpt55_20260423</x:v>
+      </x:c>
+      <x:c r="H18" s="16" t="str">
+        <x:v>gate1-openai-com-agents-last-exam-source</x:v>
+      </x:c>
+      <x:c r="I18" s="16" t="str">
+        <x:v>Flagship tier within GPT-5.6 family</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A19" s="16" t="str">
+        <x:v>qwen_qwen38max_20260719</x:v>
+      </x:c>
+      <x:c r="B19" s="16" t="str">
+        <x:v>Qwen</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="str">
+        <x:v>Qwen 3.8 Max</x:v>
+      </x:c>
+      <x:c r="D19" s="25" t="str">
+        <x:v>2026-07-19</x:v>
+      </x:c>
+      <x:c r="E19" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F19" s="16" t="str">
+        <x:v>Provider products and API</x:v>
+      </x:c>
+      <x:c r="G19" s="16" t="str"/>
+      <x:c r="H19" s="16" t="str">
+        <x:v>gate1-taubench-com-tau3-banking-source</x:v>
+      </x:c>
+      <x:c r="I19" s="16" t="str">
+        <x:v>Release date verified by benchmark source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A20" s="16" t="str">
+        <x:v>anthropic_opus5_20260724</x:v>
+      </x:c>
+      <x:c r="B20" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="str">
+        <x:v>Claude Opus 5</x:v>
+      </x:c>
+      <x:c r="D20" s="25" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+      <x:c r="E20" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F20" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G20" s="16" t="str">
+        <x:v>anthropic_opus48_20260528</x:v>
+      </x:c>
+      <x:c r="H20" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-5-release</x:v>
+      </x:c>
+      <x:c r="I20" s="16" t="str"/>
+    </x:row>
+    <x:row r="21" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A21" s="16" t="str">
+        <x:v>openai_gpt6astra_20260903</x:v>
+      </x:c>
+      <x:c r="B21" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C21" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D21" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E21" s="16" t="str">
+        <x:v>limited_rollout</x:v>
+      </x:c>
+      <x:c r="F21" s="16" t="str">
+        <x:v>Trusted Access Program organizations on release day; ChatGPT Plus, Pro, Business, and Enterprise, the OpenAI API, and AWS over the coming days</x:v>
+      </x:c>
+      <x:c r="G21" s="16" t="str">
+        <x:v>openai_gpt56sol_20260709</x:v>
+      </x:c>
+      <x:c r="H21" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I21" s="16" t="str">
+        <x:v>Release-day availability is narrower than the general-access state expected over the following days.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A22" s="16" t="str">
+        <x:v>anthropic_fable51_20260901</x:v>
+      </x:c>
+      <x:c r="B22" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C22" s="16" t="str">
+        <x:v>Claude Fable 5.1</x:v>
+      </x:c>
+      <x:c r="D22" s="25" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E22" s="16" t="str">
+        <x:v>general_availability</x:v>
+      </x:c>
+      <x:c r="F22" s="16" t="str">
+        <x:v>Claude products and API</x:v>
+      </x:c>
+      <x:c r="G22" s="16" t="str">
+        <x:v>anthropic_fable5_20260609</x:v>
+      </x:c>
+      <x:c r="H22" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="I22" s="16" t="str">
+        <x:v>Generally available configuration with production safeguards enabled.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="108" hidden="0" customHeight="1">
+      <x:c r="A23" s="16" t="str">
+        <x:v>anthropic_mythos51_20260901</x:v>
+      </x:c>
+      <x:c r="B23" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C23" s="16" t="str">
+        <x:v>Claude Mythos 5.1</x:v>
+      </x:c>
+      <x:c r="D23" s="25" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E23" s="16" t="str">
+        <x:v>trusted_access</x:v>
+      </x:c>
+      <x:c r="F23" s="16" t="str">
+        <x:v>Anthropic cybersecurity and life-sciences trusted access programs</x:v>
+      </x:c>
+      <x:c r="G23" s="16" t="str">
+        <x:v>anthropic_fable51_20260901</x:v>
+      </x:c>
+      <x:c r="H23" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="I23" s="16" t="str">
+        <x:v>Same underlying model as Fable 5.1 with more permissive domain safeguards for vetted users.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I2"/>
+    <x:mergeCell ref="A3:I3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc5f3d87c9c84734"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4936,7 +7132,7 @@
         <x:v>Finch / FinWorkBench benchmark</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -4957,7 +7153,7 @@
         <x:v>Vending-Bench 2 benchmark</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E7" s="16" t="str">
         <x:v>Business, forecast benchmark, forecast observation, supporting evaluation, supporting evaluation observation</x:v>
@@ -4978,7 +7174,7 @@
         <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E8" s="16" t="str">
         <x:v>Capability velocity, release metadata, supporting evaluation observation</x:v>
@@ -4999,7 +7195,7 @@
         <x:v>EnterpriseOps-Gym-AA benchmark</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E9" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5020,7 +7216,7 @@
         <x:v>Business Arena benchmark</x:v>
       </x:c>
       <x:c r="D10" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E10" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5041,7 +7237,7 @@
         <x:v>EnterpriseArena benchmark</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E11" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5062,7 +7258,7 @@
         <x:v>MerchantBench benchmark</x:v>
       </x:c>
       <x:c r="D12" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E12" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5083,7 +7279,7 @@
         <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E13" s="16" t="str">
         <x:v>supporting evaluation observation</x:v>
@@ -5104,7 +7300,7 @@
         <x:v>pi-Bench benchmark</x:v>
       </x:c>
       <x:c r="D14" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E14" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5125,7 +7321,7 @@
         <x:v>RetailBench benchmark</x:v>
       </x:c>
       <x:c r="D15" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5146,7 +7342,7 @@
         <x:v>TheAgentCompany benchmark</x:v>
       </x:c>
       <x:c r="D16" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5167,7 +7363,7 @@
         <x:v>WeaveBench</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
         <x:v>capability evidence</x:v>
@@ -5188,7 +7384,7 @@
         <x:v>WorkArena++ benchmark</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E18" s="16" t="str">
         <x:v>forecast benchmark</x:v>
@@ -5209,7 +7405,7 @@
         <x:v>YC-Bench benchmark</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E19" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5230,7 +7426,7 @@
         <x:v>CEO-Bench benchmark</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5251,7 +7447,7 @@
         <x:v>Gate 1 · Model–harness capability calculation contract</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E21" s="16" t="str">
         <x:v>methodology, normalization, model configuration</x:v>
@@ -5274,7 +7470,7 @@
         <x:v>AutomationBench benchmark</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E22" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5295,7 +7491,7 @@
         <x:v>Claw-Eval benchmark</x:v>
       </x:c>
       <x:c r="D23" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E23" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5316,7 +7512,7 @@
         <x:v>ClawBench benchmark</x:v>
       </x:c>
       <x:c r="D24" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E24" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5337,7 +7533,7 @@
         <x:v>ClawMark benchmark</x:v>
       </x:c>
       <x:c r="D25" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E25" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5358,7 +7554,7 @@
         <x:v>Commerce Agent Bench benchmark</x:v>
       </x:c>
       <x:c r="D26" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E26" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5379,7 +7575,7 @@
         <x:v>MyPCBench source</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E27" s="16" t="str">
         <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
@@ -5400,7 +7596,7 @@
         <x:v>AssistantBench (HAL) benchmark</x:v>
       </x:c>
       <x:c r="D28" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E28" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5421,7 +7617,7 @@
         <x:v>Remote Labor Index source</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E29" s="16" t="str">
         <x:v>Professional capability, supporting evaluation, supporting evaluation observation</x:v>
@@ -5442,7 +7638,7 @@
         <x:v>METR Time Horizon source</x:v>
       </x:c>
       <x:c r="D30" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E30" s="16" t="str">
         <x:v>Capability, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation, task-horizon observations</x:v>
@@ -5463,7 +7659,7 @@
         <x:v>MyPCBench benchmark</x:v>
       </x:c>
       <x:c r="D31" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E31" s="16" t="str">
         <x:v>capability evidence, forecast benchmark, forecast observation</x:v>
@@ -5484,7 +7680,7 @@
         <x:v>MyPCBench source</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E32" s="16" t="str">
         <x:v>Consumer benchmark, supporting evaluation, supporting evaluation observation</x:v>
@@ -5505,7 +7701,7 @@
         <x:v>OmegaUse-OfficeVal benchmark</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E33" s="16" t="str">
         <x:v>forecast benchmark</x:v>
@@ -5526,7 +7722,7 @@
         <x:v>Agents Last Exam source</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
         <x:v>AI R&amp;D, Capability velocity, Computer use, release metadata, supporting evaluation, supporting evaluation observation</x:v>
@@ -5547,7 +7743,7 @@
         <x:v>GDPval benchmark</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E35" s="16" t="str">
         <x:v>forecast benchmark</x:v>
@@ -5568,7 +7764,7 @@
         <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D36" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
         <x:v>release metadata, supporting evaluation observation</x:v>
@@ -5589,7 +7785,7 @@
         <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
         <x:v>Capability velocity, release metadata, supporting evaluation observation</x:v>
@@ -5610,7 +7806,7 @@
         <x:v>OSWorld source</x:v>
       </x:c>
       <x:c r="D38" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
         <x:v>supporting evaluation</x:v>
@@ -5631,7 +7827,7 @@
         <x:v>OSWorld source</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
         <x:v>Computer use, capability evidence, supporting evaluation</x:v>
@@ -5652,7 +7848,7 @@
         <x:v>Remote Labor Index benchmark</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E40" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5673,7 +7869,7 @@
         <x:v>tau3 Banking benchmark</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
         <x:v>forecast benchmark, forecast observation</x:v>
@@ -5694,7 +7890,7 @@
         <x:v>tau3 Banking source</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
         <x:v>Business, Capability velocity, release metadata, supporting evaluation, supporting evaluation observation</x:v>
@@ -5715,7 +7911,7 @@
         <x:v>TheAgentCompany observation source</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E43" s="16" t="str">
         <x:v>forecast observation</x:v>
@@ -5736,7 +7932,7 @@
         <x:v>OSWorld observation source</x:v>
       </x:c>
       <x:c r="D44" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E44" s="16" t="str">
         <x:v>supporting evaluation observation</x:v>
@@ -5757,7 +7953,7 @@
         <x:v>Task-horizon benchmark results</x:v>
       </x:c>
       <x:c r="D45" s="16" t="str">
-        <x:v>2026-08-26</x:v>
+        <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E45" s="16" t="str">
         <x:v>published trend estimate</x:v>
@@ -5766,6 +7962,745 @@
         <x:v>https://metr.org/assets/benchmark_results_1_1.yaml</x:v>
       </x:c>
       <x:c r="G45" s="16" t="str"/>
+    </x:row>
+    <x:row r="46" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A46" s="16" t="str">
+        <x:v>gate1-anthropic-com-anthropic-business-customers</x:v>
+      </x:c>
+      <x:c r="B46" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C46" s="16" t="str">
+        <x:v>Anthropic: business customers</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/anthropic-raises-series-f-at-usd183b-post-money-valuation</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="str"/>
+    </x:row>
+    <x:row r="47" ht="183.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A47" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
+      </x:c>
+      <x:c r="B47" s="16" t="str">
+        <x:v>Anthropic</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="str">
+        <x:v>Claude Fable 5.1 and Mythos 5.1</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="str">
+        <x:v>release metadata, supporting benchmark evidence, computer-use evidence, professional-work evidence</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="str">
+        <x:v>https://www.anthropic.com/claude-fable-and-mythos-5-1</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="str">
+        <x:v>Anthropic describes Fable 5.1 and Mythos 5.1 as the same underlying model with different safeguards. Fable 5.1 was evaluated with production safeguards enabled.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="54" hidden="0" customHeight="1">
+      <x:c r="A48" s="16" t="str">
+        <x:v>gate1-api-github-com-openclaw-github-stars-observation</x:v>
+      </x:c>
+      <x:c r="B48" s="16" t="str">
+        <x:v>api.github.com</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="str">
+        <x:v>OpenClaw GitHub stars observation</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="str">
+        <x:v>https://api.github.com/repos/openclaw/openclaw</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="str"/>
+    </x:row>
+    <x:row r="49" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A49" s="16" t="str">
+        <x:v>gate1-api-npmjs-org-openclaw-npm-monthly-downloads-observation</x:v>
+      </x:c>
+      <x:c r="B49" s="16" t="str">
+        <x:v>api.npmjs.org</x:v>
+      </x:c>
+      <x:c r="C49" s="16" t="str">
+        <x:v>OpenClaw npm monthly downloads observation</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E49" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F49" s="16" t="str">
+        <x:v>https://api.npmjs.org/downloads/point/last-month/openclaw</x:v>
+      </x:c>
+      <x:c r="G49" s="16" t="str"/>
+    </x:row>
+    <x:row r="50" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A50" s="16" t="str">
+        <x:v>gate1-apnews-com-chatgpt-paid-consumers-observation</x:v>
+      </x:c>
+      <x:c r="B50" s="16" t="str">
+        <x:v>apnews.com</x:v>
+      </x:c>
+      <x:c r="C50" s="16" t="str">
+        <x:v>ChatGPT paid consumers observation</x:v>
+      </x:c>
+      <x:c r="D50" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E50" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F50" s="16" t="str">
+        <x:v>https://apnews.com/article/a0a915c32b85337d799fe2f9525a932a</x:v>
+      </x:c>
+      <x:c r="G50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A51" s="16" t="str">
+        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
+      </x:c>
+      <x:c r="B51" s="16" t="str">
+        <x:v>arxiv.org</x:v>
+      </x:c>
+      <x:c r="C51" s="16" t="str">
+        <x:v>o3: OSWorld baseline at 15 steps</x:v>
+      </x:c>
+      <x:c r="D51" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="str">
+        <x:v>Harness, capability evidence</x:v>
+      </x:c>
+      <x:c r="F51" s="16" t="str">
+        <x:v>https://arxiv.org/abs/2510.24563</x:v>
+      </x:c>
+      <x:c r="G51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A52" s="16" t="str">
+        <x:v>gate1-deploymentsafety-openai-com-gpt-5-6-sol-factual-error-reduction-vs-gpt-5</x:v>
+      </x:c>
+      <x:c r="B52" s="16" t="str">
+        <x:v>deploymentsafety.openai.com</x:v>
+      </x:c>
+      <x:c r="C52" s="16" t="str">
+        <x:v>GPT-5.6 Sol: factual-error reduction vs GPT-5.5 Instant</x:v>
+      </x:c>
+      <x:c r="D52" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E52" s="16" t="str">
+        <x:v>Factuality</x:v>
+      </x:c>
+      <x:c r="F52" s="16" t="str">
+        <x:v>https://deploymentsafety.openai.com/gpt-5-6-august-update/model-safety-training-and-evaluation</x:v>
+      </x:c>
+      <x:c r="G52" s="16" t="str"/>
+    </x:row>
+    <x:row r="53" ht="54" hidden="0" customHeight="1">
+      <x:c r="A53" s="16" t="str">
+        <x:v>gate1-openai-com-codex-reach-observation-3</x:v>
+      </x:c>
+      <x:c r="B53" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C53" s="16" t="str">
+        <x:v>Codex reach observation</x:v>
+      </x:c>
+      <x:c r="D53" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E53" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F53" s="16" t="str">
+        <x:v>https://openai.com/index/codex-for-knowledge-work/</x:v>
+      </x:c>
+      <x:c r="G53" s="16" t="str"/>
+    </x:row>
+    <x:row r="54" ht="270" hidden="0" customHeight="1">
+      <x:c r="A54" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="B54" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C54" s="16" t="str">
+        <x:v>GPT-6 Astra: A new generation of intelligence</x:v>
+      </x:c>
+      <x:c r="D54" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E54" s="16" t="str">
+        <x:v>release metadata, supporting benchmark evidence, computer-use evidence, alignment evidence</x:v>
+      </x:c>
+      <x:c r="F54" s="16" t="str">
+        <x:v>https://openai.com/index/gpt-6-astra/</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="str">
+        <x:v>OpenAI reports maximum-at-any-effort evaluation scores from its research or API environments. ARC-AGI-3 uses OpenAI's general Responses API harness with persisted reasoning and compaction; these settings were not benchmark-specific.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A55" s="16" t="str">
+        <x:v>gate1-openai-com-openai-chatgpt-for-work-seats</x:v>
+      </x:c>
+      <x:c r="B55" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="str">
+        <x:v>OpenAI: ChatGPT for Work seats</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="F55" s="16" t="str">
+        <x:v>https://openai.com/index/1-million-businesses-putting-ai-to-work/</x:v>
+      </x:c>
+      <x:c r="G55" s="16" t="str"/>
+    </x:row>
+    <x:row r="56" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A56" s="16" t="str">
+        <x:v>gate1-rdi-berkeley-edu-best-reported-broad-agent-agents-last-exam-cli</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="str">
+        <x:v>rdi.berkeley.edu</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="str">
+        <x:v>best reported broad agent: Agents' Last Exam CLI</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="str">
+        <x:v>Broad work</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="str">
+        <x:v>https://rdi.berkeley.edu/blog/agents-last-exam/</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="str"/>
+    </x:row>
+    <x:row r="57" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A57" s="16" t="str">
+        <x:v>gate1-redis-github-io-hybrid-memory-system-longmemeval-task-averaged-accuracy</x:v>
+      </x:c>
+      <x:c r="B57" s="16" t="str">
+        <x:v>redis.github.io</x:v>
+      </x:c>
+      <x:c r="C57" s="16" t="str">
+        <x:v>hybrid memory system: LongMemEval task-averaged accuracy</x:v>
+      </x:c>
+      <x:c r="D57" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E57" s="16" t="str">
+        <x:v>Memory</x:v>
+      </x:c>
+      <x:c r="F57" s="16" t="str">
+        <x:v>https://redis.github.io/redis-ai-research-public/longmemeval-agent-memory/</x:v>
+      </x:c>
+      <x:c r="G57" s="16" t="str"/>
+    </x:row>
+    <x:row r="58" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A58" s="16" t="str">
+        <x:v>gate1-sec-gov-grok-active-paid-subscriptions-observation</x:v>
+      </x:c>
+      <x:c r="B58" s="16" t="str">
+        <x:v>sec.gov</x:v>
+      </x:c>
+      <x:c r="C58" s="16" t="str">
+        <x:v>Grok active paid subscriptions observation</x:v>
+      </x:c>
+      <x:c r="D58" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E58" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F58" s="16" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/1181412/000162828026039276/spaceexplorationtechnologi.htm</x:v>
+      </x:c>
+      <x:c r="G58" s="16" t="str"/>
+    </x:row>
+    <x:row r="59" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A59" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-directive-delegation-observation</x:v>
+      </x:c>
+      <x:c r="B59" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="str">
+        <x:v>Claude directive delegation observation</x:v>
+      </x:c>
+      <x:c r="D59" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F59" s="16" t="str">
+        <x:v>https://www.anthropic.com/research/anthropic-economic-index-january-2026-report</x:v>
+      </x:c>
+      <x:c r="G59" s="16" t="str"/>
+    </x:row>
+    <x:row r="60" ht="54" hidden="0" customHeight="1">
+      <x:c r="A60" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-5-release</x:v>
+      </x:c>
+      <x:c r="B60" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="str">
+        <x:v>Claude Opus 4.5 release</x:v>
+      </x:c>
+      <x:c r="D60" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E60" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F60" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-4-5</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="str"/>
+    </x:row>
+    <x:row r="61" ht="54" hidden="0" customHeight="1">
+      <x:c r="A61" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-6-release</x:v>
+      </x:c>
+      <x:c r="B61" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C61" s="16" t="str">
+        <x:v>Claude Opus 4.6 release</x:v>
+      </x:c>
+      <x:c r="D61" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E61" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F61" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-4-6</x:v>
+      </x:c>
+      <x:c r="G61" s="16" t="str"/>
+    </x:row>
+    <x:row r="62" ht="54" hidden="0" customHeight="1">
+      <x:c r="A62" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-8-release</x:v>
+      </x:c>
+      <x:c r="B62" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C62" s="16" t="str">
+        <x:v>Claude Opus 4.8 release</x:v>
+      </x:c>
+      <x:c r="D62" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E62" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F62" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-4-8</x:v>
+      </x:c>
+      <x:c r="G62" s="16" t="str"/>
+    </x:row>
+    <x:row r="63" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A63" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-5-release</x:v>
+      </x:c>
+      <x:c r="B63" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C63" s="16" t="str">
+        <x:v>Claude Opus 5 release</x:v>
+      </x:c>
+      <x:c r="D63" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E63" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F63" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-5</x:v>
+      </x:c>
+      <x:c r="G63" s="16" t="str"/>
+    </x:row>
+    <x:row r="64" ht="108" hidden="0" customHeight="1">
+      <x:c r="A64" s="16" t="str">
+        <x:v>gate1-federalreserve-gov-us-work-genai-any-use-observation</x:v>
+      </x:c>
+      <x:c r="B64" s="16" t="str">
+        <x:v>federalreserve.gov</x:v>
+      </x:c>
+      <x:c r="C64" s="16" t="str">
+        <x:v>US work GenAI any use observation</x:v>
+      </x:c>
+      <x:c r="D64" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E64" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F64" s="16" t="str">
+        <x:v>https://www.federalreserve.gov/econres/notes/feds-notes/monitoring-ai-adoption-in-the-u-s-economy-20260403.html</x:v>
+      </x:c>
+      <x:c r="G64" s="16" t="str"/>
+    </x:row>
+    <x:row r="65" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A65" s="16" t="str">
+        <x:v>gate1-gallup-com-us-employee-ai-use-observation</x:v>
+      </x:c>
+      <x:c r="B65" s="16" t="str">
+        <x:v>gallup.com</x:v>
+      </x:c>
+      <x:c r="C65" s="16" t="str">
+        <x:v>US employee AI use observation</x:v>
+      </x:c>
+      <x:c r="D65" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E65" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F65" s="16" t="str">
+        <x:v>https://www.gallup.com/workplace/704225/rising-adoption-spurs-workforce-changes.aspx</x:v>
+      </x:c>
+      <x:c r="G65" s="16" t="str"/>
+    </x:row>
+    <x:row r="66" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A66" s="16" t="str">
+        <x:v>gate1-gallup-com-us-employee-frequent-ai-use-observation</x:v>
+      </x:c>
+      <x:c r="B66" s="16" t="str">
+        <x:v>gallup.com</x:v>
+      </x:c>
+      <x:c r="C66" s="16" t="str">
+        <x:v>US employee frequent AI use observation</x:v>
+      </x:c>
+      <x:c r="D66" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E66" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F66" s="16" t="str">
+        <x:v>https://www.gallup.com/workplace/701195/frequent-workplace-continued-rise.aspx</x:v>
+      </x:c>
+      <x:c r="G66" s="16" t="str"/>
+    </x:row>
+    <x:row r="67" ht="140.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A67" s="16" t="str">
+        <x:v>gate1-investing-com-chatgpt-paid-consumers-observation</x:v>
+      </x:c>
+      <x:c r="B67" s="16" t="str">
+        <x:v>investing.com</x:v>
+      </x:c>
+      <x:c r="C67" s="16" t="str">
+        <x:v>ChatGPT paid consumers observation</x:v>
+      </x:c>
+      <x:c r="D67" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E67" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F67" s="16" t="str">
+        <x:v>https://www.investing.com/news/stock-market-news/openai-projected-at-least-220-million-people-will-pay-for-chatgpt-by-2030-the-information-reports-4378677</x:v>
+      </x:c>
+      <x:c r="G67" s="16" t="str"/>
+    </x:row>
+    <x:row r="68" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A68" s="16" t="str">
+        <x:v>gate1-microsoft-com-microsoft-365-active-agents-index-observation</x:v>
+      </x:c>
+      <x:c r="B68" s="16" t="str">
+        <x:v>microsoft.com</x:v>
+      </x:c>
+      <x:c r="C68" s="16" t="str">
+        <x:v>Microsoft 365 active agents index observation</x:v>
+      </x:c>
+      <x:c r="D68" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E68" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F68" s="16" t="str">
+        <x:v>https://www.microsoft.com/en-us/worklab/work-trend-index/agents-human-agency-and-the-opportunity-for-every-organization</x:v>
+      </x:c>
+      <x:c r="G68" s="16" t="str"/>
+    </x:row>
+    <x:row r="69" ht="54" hidden="0" customHeight="1">
+      <x:c r="A69" s="16" t="str">
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation</x:v>
+      </x:c>
+      <x:c r="B69" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C69" s="16" t="str">
+        <x:v>ChatGPT reported reach observation</x:v>
+      </x:c>
+      <x:c r="D69" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E69" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F69" s="16" t="str">
+        <x:v>https://openai.com/index/how-people-are-using-chatgpt/</x:v>
+      </x:c>
+      <x:c r="G69" s="16" t="str"/>
+    </x:row>
+    <x:row r="70" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A70" s="16" t="str">
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-2</x:v>
+      </x:c>
+      <x:c r="B70" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C70" s="16" t="str">
+        <x:v>ChatGPT reported reach observation</x:v>
+      </x:c>
+      <x:c r="D70" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E70" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F70" s="16" t="str">
+        <x:v>https://openai.com/index/the-state-of-enterprise-ai-2025-report/</x:v>
+      </x:c>
+      <x:c r="G70" s="16" t="str"/>
+    </x:row>
+    <x:row r="71" ht="54" hidden="0" customHeight="1">
+      <x:c r="A71" s="16" t="str">
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-3</x:v>
+      </x:c>
+      <x:c r="B71" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C71" s="16" t="str">
+        <x:v>ChatGPT reported reach observation</x:v>
+      </x:c>
+      <x:c r="D71" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E71" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F71" s="16" t="str">
+        <x:v>https://openai.com/index/grupo-folha-grupo-uol-partnership/</x:v>
+      </x:c>
+      <x:c r="G71" s="16" t="str"/>
+    </x:row>
+    <x:row r="72" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A72" s="16" t="str">
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-4</x:v>
+      </x:c>
+      <x:c r="B72" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C72" s="16" t="str">
+        <x:v>ChatGPT reported reach observation</x:v>
+      </x:c>
+      <x:c r="D72" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E72" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F72" s="16" t="str">
+        <x:v>https://openai.com/index/how-the-world-is-putting-chatgpt-to-work/</x:v>
+      </x:c>
+      <x:c r="G72" s="16" t="str"/>
+    </x:row>
+    <x:row r="73" ht="54" hidden="0" customHeight="1">
+      <x:c r="A73" s="16" t="str">
+        <x:v>gate1-openai-com-codex-reach-observation</x:v>
+      </x:c>
+      <x:c r="B73" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C73" s="16" t="str">
+        <x:v>Codex reach observation</x:v>
+      </x:c>
+      <x:c r="D73" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E73" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F73" s="16" t="str">
+        <x:v>https://openai.com/index/next-phase-of-enterprise-ai/</x:v>
+      </x:c>
+      <x:c r="G73" s="16" t="str"/>
+    </x:row>
+    <x:row r="74" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A74" s="16" t="str">
+        <x:v>gate1-openai-com-codex-reach-observation-2</x:v>
+      </x:c>
+      <x:c r="B74" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C74" s="16" t="str">
+        <x:v>Codex reach observation</x:v>
+      </x:c>
+      <x:c r="D74" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E74" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F74" s="16" t="str">
+        <x:v>https://openai.com/index/the-next-phase-of-education-for-countries/</x:v>
+      </x:c>
+      <x:c r="G74" s="16" t="str"/>
+    </x:row>
+    <x:row r="75" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A75" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-2-release</x:v>
+      </x:c>
+      <x:c r="B75" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C75" s="16" t="str">
+        <x:v>GPT-5.2 release</x:v>
+      </x:c>
+      <x:c r="D75" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E75" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F75" s="16" t="str">
+        <x:v>https://openai.com/</x:v>
+      </x:c>
+      <x:c r="G75" s="16" t="str"/>
+    </x:row>
+    <x:row r="76" ht="54" hidden="0" customHeight="1">
+      <x:c r="A76" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-4-mini-release</x:v>
+      </x:c>
+      <x:c r="B76" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C76" s="16" t="str">
+        <x:v>GPT-5.4 mini release</x:v>
+      </x:c>
+      <x:c r="D76" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E76" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F76" s="16" t="str">
+        <x:v>https://openai.com/index/introducing-gpt-5-4-mini-and-nano/</x:v>
+      </x:c>
+      <x:c r="G76" s="16" t="str"/>
+    </x:row>
+    <x:row r="77" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A77" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-release</x:v>
+      </x:c>
+      <x:c r="B77" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C77" s="16" t="str">
+        <x:v>GPT-5 release</x:v>
+      </x:c>
+      <x:c r="D77" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E77" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F77" s="16" t="str">
+        <x:v>https://openai.com/index/introducing-gpt-5/</x:v>
+      </x:c>
+      <x:c r="G77" s="16" t="str"/>
+    </x:row>
+    <x:row r="78" ht="54" hidden="0" customHeight="1">
+      <x:c r="A78" s="16" t="str">
+        <x:v>gate1-ramp-com-us-businesses-paying-for-ai-observation</x:v>
+      </x:c>
+      <x:c r="B78" s="16" t="str">
+        <x:v>ramp.com</x:v>
+      </x:c>
+      <x:c r="C78" s="16" t="str">
+        <x:v>US businesses paying for AI observation</x:v>
+      </x:c>
+      <x:c r="D78" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E78" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F78" s="16" t="str">
+        <x:v>https://ramp.com/data/april-2026-ai-index</x:v>
+      </x:c>
+      <x:c r="G78" s="16" t="str"/>
+    </x:row>
+    <x:row r="79" ht="54" hidden="0" customHeight="1">
+      <x:c r="A79" s="16" t="str">
+        <x:v>gate1-ramp-com-us-businesses-paying-for-ai-observation-2</x:v>
+      </x:c>
+      <x:c r="B79" s="16" t="str">
+        <x:v>ramp.com</x:v>
+      </x:c>
+      <x:c r="C79" s="16" t="str">
+        <x:v>US businesses paying for AI observation</x:v>
+      </x:c>
+      <x:c r="D79" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E79" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F79" s="16" t="str">
+        <x:v>https://ramp.com/data/</x:v>
+      </x:c>
+      <x:c r="G79" s="16" t="str"/>
+    </x:row>
+    <x:row r="80" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A80" s="16" t="str">
+        <x:v>gate1-techradar-com-openclaw-github-stars-observation</x:v>
+      </x:c>
+      <x:c r="B80" s="16" t="str">
+        <x:v>techradar.com</x:v>
+      </x:c>
+      <x:c r="C80" s="16" t="str">
+        <x:v>OpenClaw GitHub stars observation</x:v>
+      </x:c>
+      <x:c r="D80" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E80" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F80" s="16" t="str">
+        <x:v>https://www.techradar.com/pro/wild-things-people-are-building-with-openclaw</x:v>
+      </x:c>
+      <x:c r="G80" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5774,7 +8709,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re239c13ea45b4223"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5075f70358e9475c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
+++ b/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9a0940a3125d4bb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R8da8e13224474d8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R1ef87d98bcbd4838"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R697aab421d234433"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R5aab6667b7644f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Evidence" sheetId="6" r:id="R43b117debd5e4831"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Releases" sheetId="7" r:id="R75d07812935a4169"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb8ccdc4d4c1d4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5e220b784f5f455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="Rcc9bca2cbffc486c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R3190523cbaeb436b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R27784fc422134033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="Rc0cd1f46f15f4780"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Evidence" sheetId="6" r:id="Rce850d236b7e40c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Releases" sheetId="7" r:id="R6b2e9d8f177e4470"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re64be198ddcc4157"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -434,7 +434,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf692cba597744bfa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdcdc42325374d4a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -537,7 +537,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilityResearchEvidenceTable" displayName="CapabilityResearchEvidenceTable" ref="A5:I55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilityResearchEvidenceTable" displayName="CapabilityResearchEvidenceTable" ref="A5:I57" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Evidence ID"/>
     <x:tableColumn id="2" name="Category"/>
@@ -1207,7 +1207,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1109f040a14438b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09387638196847e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2538,7 +2538,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67a02012d48a4e8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc34ca3276aee40e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3919,7 +3919,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12261a76a63a4b8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R632a86f1ba8548cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4418,9 +4418,9 @@
     <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R965847d0cb314e76"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3d9885d5bf1475d"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b24a39c91640a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c1e0ddf3454318"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4920,7 +4920,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34da4859e8644913"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd2377f340ec480c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6447,6 +6447,64 @@
         <x:v>Vendor-reported Elo. It remains ungraded because the forecast contract forbids rescaling a leaderboard without a fixed reference opponent or stable win-rate transformation.</x:v>
       </x:c>
     </x:row>
+    <x:row r="56" ht="183.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A56" s="16" t="str">
+        <x:v>evidence-051</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="str">
+        <x:v>Abstract reasoning</x:v>
+      </x:c>
+      <x:c r="C56" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="str">
+        <x:v>FrontierMath Tier 4 score</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="n">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H56" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I56" s="16" t="str">
+        <x:v>Vendor-reported maximum-at-any-effort result on a frontier mathematical-reasoning benchmark. It is important capability evidence but not a direct economic-delegation outcome.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A57" s="16" t="str">
+        <x:v>evidence-052</x:v>
+      </x:c>
+      <x:c r="B57" s="16" t="str">
+        <x:v>Cybersecurity</x:v>
+      </x:c>
+      <x:c r="C57" s="25" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D57" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E57" s="16" t="str">
+        <x:v>ExploitBench score</x:v>
+      </x:c>
+      <x:c r="F57" s="16" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G57" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H57" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="I57" s="16" t="str">
+        <x:v>Vendor-reported maximum-at-any-effort result. OpenAI designates Astra Critical capability in cyber; this is a capability and safety signal, not a Personal-AI delegation measure.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I2"/>
@@ -6454,7 +6512,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21276c5d015e4247"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9395d064228c4adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7048,7 +7106,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc5f3d87c9c84734"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd768d4e6b564a47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8709,7 +8767,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5075f70358e9475c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36c1322c595e4f54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
+++ b/artifacts/report-cards/personal-ai-four-year-capability-report-card.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5e220b784f5f455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="Rcc9bca2cbffc486c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="R3190523cbaeb436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R27784fc422134033"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="Rc0cd1f46f15f4780"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Evidence" sheetId="6" r:id="Rce850d236b7e40c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Releases" sheetId="7" r:id="R6b2e9d8f177e4470"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Re64be198ddcc4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Ra99f7e79e25d4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="2" r:id="R6f2d54414f8e4ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observations" sheetId="3" r:id="Rf8300ad931684b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Path" sheetId="4" r:id="R6ca34dccc7ee4885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="METR Horizon" sheetId="5" r:id="R7d225b5356a4493c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frontier Signals" sheetId="6" r:id="R0416d72998484437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Research Evidence" sheetId="7" r:id="Rde6b5cb4cb284d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Releases" sheetId="8" r:id="R3724baf83d954f79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R038fd8443fff4739"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,12 +21,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="0.0%"/>
-    <x:numFmt numFmtId="201" formatCode="0.000"/>
-    <x:numFmt numFmtId="202" formatCode="0%"/>
-    <x:numFmt numFmtId="203" formatCode="0.0000"/>
-    <x:numFmt numFmtId="204" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="0.0000"/>
+    <x:numFmt numFmtId="202" formatCode="0.000"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
+    <x:numFmt numFmtId="204" formatCode="0%"/>
+    <x:numFmt numFmtId="205" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
   <x:fonts count="5">
     <x:font>
@@ -98,7 +100,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -144,19 +146,22 @@
     <x:xf numFmtId="203" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="204" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="204" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="204" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -434,7 +439,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcdcdc42325374d4a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7ac5b3eeab3c4442"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -444,7 +449,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CapabilitySummaryTable" displayName="CapabilitySummaryTable" ref="A5:K19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CapabilitySummaryTable" displayName="CapabilitySummaryTable" ref="A5:K24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Metric / benchmark family"/>
     <x:tableColumn id="2" name="Score / value"/>
@@ -537,7 +542,25 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilityResearchEvidenceTable" displayName="CapabilityResearchEvidenceTable" ref="A5:I57" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="CapabilityFrontierSignalsTable" displayName="CapabilityFrontierSignalsTable" ref="A5:J12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="Record type"/>
+    <x:tableColumn id="2" name="ID"/>
+    <x:tableColumn id="3" name="Model / series"/>
+    <x:tableColumn id="4" name="Date"/>
+    <x:tableColumn id="5" name="Metric / summary"/>
+    <x:tableColumn id="6" name="Value"/>
+    <x:tableColumn id="7" name="Interval / domains"/>
+    <x:tableColumn id="8" name="Publisher"/>
+    <x:tableColumn id="9" name="Source ID"/>
+    <x:tableColumn id="10" name="Countdown treatment"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="CapabilityResearchEvidenceTable" displayName="CapabilityResearchEvidenceTable" ref="A5:I65" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Evidence ID"/>
     <x:tableColumn id="2" name="Category"/>
@@ -553,8 +576,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="CapabilityModelReleasesTable" displayName="CapabilityModelReleasesTable" ref="A5:I23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="CapabilityModelReleasesTable" displayName="CapabilityModelReleasesTable" ref="A5:I23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Release ID"/>
     <x:tableColumn id="2" name="Provider"/>
@@ -570,8 +593,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G80" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="CapabilitySourcesTable" displayName="CapabilitySourcesTable" ref="A5:G84" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Source ID"/>
     <x:tableColumn id="2" name="Publisher"/>
@@ -891,15 +914,15 @@
       <x:c r="J6" s="16"/>
       <x:c r="K6" s="16"/>
     </x:row>
-    <x:row r="7" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A7" s="16" t="str">
-        <x:v>Current capability</x:v>
+        <x:v>Observed direct-basket capability</x:v>
       </x:c>
       <x:c r="B7" s="17" t="n">
         <x:v>0.46141401843584867</x:v>
       </x:c>
       <x:c r="C7" s="16" t="str">
-        <x:v>Confidence-weighted score</x:v>
+        <x:v>Direct delegation benchmarks only</x:v>
       </x:c>
       <x:c r="D7" s="16"/>
       <x:c r="E7" s="16"/>
@@ -910,15 +933,15 @@
       <x:c r="J7" s="16"/>
       <x:c r="K7" s="16"/>
     </x:row>
-    <x:row r="8" ht="54" hidden="0" customHeight="1">
+    <x:row r="8" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A8" s="16" t="str">
-        <x:v>Letter grade</x:v>
-      </x:c>
-      <x:c r="B8" s="16" t="str">
-        <x:v>F</x:v>
+        <x:v>Frontier-adjusted live capability</x:v>
+      </x:c>
+      <x:c r="B8" s="17" t="n">
+        <x:v>0.4836511835014151</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
-        <x:v>A ≥90%, B ≥80%, C ≥70%, D ≥60%, F &lt;60%</x:v>
+        <x:v>Includes Astra's qualified one-time trajectory lead</x:v>
       </x:c>
       <x:c r="D8" s="16"/>
       <x:c r="E8" s="16"/>
@@ -929,15 +952,15 @@
       <x:c r="J8" s="16"/>
       <x:c r="K8" s="16"/>
     </x:row>
-    <x:row r="9" ht="21.600000381469727" hidden="0" customHeight="1">
+    <x:row r="9" ht="54" hidden="0" customHeight="1">
       <x:c r="A9" s="16" t="str">
-        <x:v>GPA</x:v>
-      </x:c>
-      <x:c r="B9" s="18" t="n">
-        <x:v>0.5601812366737741</x:v>
+        <x:v>Letter grade</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>F</x:v>
       </x:c>
       <x:c r="C9" s="16" t="str">
-        <x:v>0–4</x:v>
+        <x:v>A ≥90%, B ≥80%, C ≥70%, D ≥60%, F &lt;60%</x:v>
       </x:c>
       <x:c r="D9" s="16"/>
       <x:c r="E9" s="16"/>
@@ -950,13 +973,13 @@
     </x:row>
     <x:row r="10" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A10" s="16" t="str">
-        <x:v>Evidence confidence</x:v>
-      </x:c>
-      <x:c r="B10" s="18" t="str">
-        <x:v>Low</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="n">
-        <x:v>0.48611111111111116</x:v>
+        <x:v>GPA</x:v>
+      </x:c>
+      <x:c r="B10" s="18" t="n">
+        <x:v>0.5601812366737741</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="str">
+        <x:v>0–4</x:v>
       </x:c>
       <x:c r="D10" s="16"/>
       <x:c r="E10" s="16"/>
@@ -967,15 +990,15 @@
       <x:c r="J10" s="16"/>
       <x:c r="K10" s="16"/>
     </x:row>
-    <x:row r="11" ht="54" hidden="0" customHeight="1">
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A11" s="16" t="str">
-        <x:v>Pooled economic gap velocity</x:v>
-      </x:c>
-      <x:c r="B11" s="18" t="n">
-        <x:v>0.15706886974084042</x:v>
-      </x:c>
-      <x:c r="C11" s="16" t="str">
-        <x:v>confidence-weighted family gap halvings / quarter</x:v>
+        <x:v>Evidence confidence</x:v>
+      </x:c>
+      <x:c r="B11" s="18" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="n">
+        <x:v>0.48611111111111116</x:v>
       </x:c>
       <x:c r="D11" s="16"/>
       <x:c r="E11" s="16"/>
@@ -986,15 +1009,15 @@
       <x:c r="J11" s="16"/>
       <x:c r="K11" s="16"/>
     </x:row>
-    <x:row r="12" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="12" ht="54" hidden="0" customHeight="1">
       <x:c r="A12" s="16" t="str">
-        <x:v>Cross-family velocity prior</x:v>
+        <x:v>Pooled economic gap velocity</x:v>
       </x:c>
       <x:c r="B12" s="18" t="n">
-        <x:v>0.14986492610341606</x:v>
+        <x:v>0.15706886974084042</x:v>
       </x:c>
       <x:c r="C12" s="16" t="str">
-        <x:v>evidence-weighted prior for sparse families</x:v>
+        <x:v>confidence-weighted family gap halvings / quarter</x:v>
       </x:c>
       <x:c r="D12" s="16"/>
       <x:c r="E12" s="16"/>
@@ -1005,15 +1028,15 @@
       <x:c r="J12" s="16"/>
       <x:c r="K12" s="16"/>
     </x:row>
-    <x:row r="13" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="13" ht="43.20000076293945" hidden="0" customHeight="1">
       <x:c r="A13" s="16" t="str">
-        <x:v>Partial-pooling prior strength</x:v>
+        <x:v>Cross-family velocity prior</x:v>
       </x:c>
       <x:c r="B13" s="18" t="n">
-        <x:v>3</x:v>
+        <x:v>0.14986492610341606</x:v>
       </x:c>
       <x:c r="C13" s="16" t="str">
-        <x:v>history credits</x:v>
+        <x:v>evidence-weighted prior for sparse families</x:v>
       </x:c>
       <x:c r="D13" s="16"/>
       <x:c r="E13" s="16"/>
@@ -1026,13 +1049,13 @@
     </x:row>
     <x:row r="14" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A14" s="16" t="str">
-        <x:v>METR H50 acceleration</x:v>
+        <x:v>Partial-pooling prior strength</x:v>
       </x:c>
       <x:c r="B14" s="18" t="n">
-        <x:v>0.2091206151346937</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C14" s="16" t="str">
-        <x:v>task-horizon doublings / quarter²</x:v>
+        <x:v>history credits</x:v>
       </x:c>
       <x:c r="D14" s="16"/>
       <x:c r="E14" s="16"/>
@@ -1045,10 +1068,10 @@
     </x:row>
     <x:row r="15" ht="32.400001525878906" hidden="0" customHeight="1">
       <x:c r="A15" s="16" t="str">
-        <x:v>METR H80 guardrail</x:v>
+        <x:v>METR H50 acceleration</x:v>
       </x:c>
       <x:c r="B15" s="18" t="n">
-        <x:v>0.3429173634620015</x:v>
+        <x:v>0.2091206151346937</x:v>
       </x:c>
       <x:c r="C15" s="16" t="str">
         <x:v>task-horizon doublings / quarter²</x:v>
@@ -1063,140 +1086,235 @@
       <x:c r="K15" s="16"/>
     </x:row>
     <x:row r="16" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A16" s="21" t="str">
+      <x:c r="A16" s="16" t="str">
+        <x:v>METR H80 guardrail</x:v>
+      </x:c>
+      <x:c r="B16" s="18" t="n">
+        <x:v>0.3429173634620015</x:v>
+      </x:c>
+      <x:c r="C16" s="16" t="str">
+        <x:v>task-horizon doublings / quarter²</x:v>
+      </x:c>
+      <x:c r="D16" s="16"/>
+      <x:c r="E16" s="16"/>
+      <x:c r="F16" s="16"/>
+      <x:c r="G16" s="16"/>
+      <x:c r="H16" s="16"/>
+      <x:c r="I16" s="16"/>
+      <x:c r="J16" s="16"/>
+      <x:c r="K16" s="16"/>
+    </x:row>
+    <x:row r="17" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A17" s="16" t="str">
+        <x:v>Astra broad frontier lead</x:v>
+      </x:c>
+      <x:c r="B17" s="18" t="n">
+        <x:v>1.7142857142857142</x:v>
+      </x:c>
+      <x:c r="C17" s="16" t="str">
+        <x:v>quarters: 6 ECI points ÷ 14 points/year</x:v>
+      </x:c>
+      <x:c r="D17" s="16"/>
+      <x:c r="E17" s="16"/>
+      <x:c r="F17" s="16"/>
+      <x:c r="G17" s="16"/>
+      <x:c r="H17" s="16"/>
+      <x:c r="I17" s="16"/>
+      <x:c r="J17" s="16"/>
+      <x:c r="K17" s="16"/>
+    </x:row>
+    <x:row r="18" ht="54" hidden="0" customHeight="1">
+      <x:c r="A18" s="16" t="str">
+        <x:v>Astra economic-equivalent lead</x:v>
+      </x:c>
+      <x:c r="B18" s="18" t="n">
+        <x:v>0.3796461564826924</x:v>
+      </x:c>
+      <x:c r="C18" s="16" t="str">
+        <x:v>quarters after economic transfer coefficient</x:v>
+      </x:c>
+      <x:c r="D18" s="16"/>
+      <x:c r="E18" s="16"/>
+      <x:c r="F18" s="16"/>
+      <x:c r="G18" s="16"/>
+      <x:c r="H18" s="16"/>
+      <x:c r="I18" s="16"/>
+      <x:c r="J18" s="16"/>
+      <x:c r="K18" s="16"/>
+    </x:row>
+    <x:row r="19" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A19" s="16" t="str">
+        <x:v>Independent corroborating publishers</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C19" s="16" t="str">
+        <x:v>minimum 2</x:v>
+      </x:c>
+      <x:c r="D19" s="16"/>
+      <x:c r="E19" s="16"/>
+      <x:c r="F19" s="16"/>
+      <x:c r="G19" s="16"/>
+      <x:c r="H19" s="16"/>
+      <x:c r="I19" s="16"/>
+      <x:c r="J19" s="16"/>
+      <x:c r="K19" s="16"/>
+    </x:row>
+    <x:row r="20" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A20" s="16" t="str">
+        <x:v>Corroborated capability domains</x:v>
+      </x:c>
+      <x:c r="B20" s="20" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C20" s="16" t="str">
+        <x:v>minimum 3</x:v>
+      </x:c>
+      <x:c r="D20" s="16"/>
+      <x:c r="E20" s="16"/>
+      <x:c r="F20" s="16"/>
+      <x:c r="G20" s="16"/>
+      <x:c r="H20" s="16"/>
+      <x:c r="I20" s="16"/>
+      <x:c r="J20" s="16"/>
+      <x:c r="K20" s="16"/>
+    </x:row>
+    <x:row r="21" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A21" s="22" t="str">
         <x:v>Direct economic stewardship</x:v>
       </x:c>
-      <x:c r="B16" s="22" t="n">
-        <x:v>0.38254856862232545</x:v>
-      </x:c>
-      <x:c r="C16" s="21" t="str">
+      <x:c r="B21" s="23" t="n">
+        <x:v>0.39584909716180033</x:v>
+      </x:c>
+      <x:c r="C21" s="22" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D16" s="23" t="n">
+      <x:c r="D21" s="24" t="n">
         <x:v>0.47619047619047616</x:v>
       </x:c>
-      <x:c r="E16" s="21" t="n">
+      <x:c r="E21" s="22" t="n">
         <x:v>0.7142857142857143</x:v>
       </x:c>
-      <x:c r="F16" s="21" t="n">
+      <x:c r="F21" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G16" s="21" t="n">
+      <x:c r="G21" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H16" s="24" t="n">
+      <x:c r="H21" s="25" t="n">
         <x:v>0.006549844650824387</x:v>
       </x:c>
-      <x:c r="I16" s="21" t="n">
+      <x:c r="I21" s="22" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J16" s="23" t="n">
+      <x:c r="J21" s="24" t="n">
         <x:v>0.5</x:v>
       </x:c>
-      <x:c r="K16" s="24" t="n">
+      <x:c r="K21" s="25" t="n">
         <x:v>0.07820738537712023</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
-      <x:c r="A17" s="21" t="str">
+    <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A22" s="22" t="str">
         <x:v>Operational execution</x:v>
       </x:c>
-      <x:c r="B17" s="22" t="n">
-        <x:v>0.5195</x:v>
-      </x:c>
-      <x:c r="C17" s="21" t="str">
+      <x:c r="B22" s="23" t="n">
+        <x:v>0.5476163788058475</x:v>
+      </x:c>
+      <x:c r="C22" s="22" t="str">
         <x:v>Medium</x:v>
       </x:c>
-      <x:c r="D17" s="23" t="n">
+      <x:c r="D22" s="24" t="n">
         <x:v>0.6296296296296297</x:v>
       </x:c>
-      <x:c r="E17" s="21" t="n">
+      <x:c r="E22" s="22" t="n">
         <x:v>0.375</x:v>
       </x:c>
-      <x:c r="F17" s="21" t="n">
+      <x:c r="F22" s="22" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G17" s="21" t="n">
+      <x:c r="G22" s="22" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H17" s="24" t="n">
+      <x:c r="H22" s="25" t="n">
         <x:v>0.23877625507365563</x:v>
       </x:c>
-      <x:c r="I17" s="21" t="n">
+      <x:c r="I22" s="22" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J17" s="23" t="n">
+      <x:c r="J22" s="24" t="n">
         <x:v>0.75</x:v>
       </x:c>
-      <x:c r="K17" s="24" t="n">
+      <x:c r="K22" s="25" t="n">
         <x:v>0.21654842283109574</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A18" s="21" t="str">
+    <x:row r="23" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A23" s="22" t="str">
         <x:v>Personal stewardship transfer</x:v>
       </x:c>
-      <x:c r="B18" s="22" t="n">
-        <x:v>0.49477499999999996</x:v>
-      </x:c>
-      <x:c r="C18" s="21" t="str">
+      <x:c r="B23" s="23" t="n">
+        <x:v>0.5154237344727879</x:v>
+      </x:c>
+      <x:c r="C23" s="22" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D18" s="23" t="n">
+      <x:c r="D23" s="24" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E18" s="21" t="n">
+      <x:c r="E23" s="22" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="F18" s="21" t="n">
+      <x:c r="F23" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G18" s="21" t="n">
+      <x:c r="G23" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H18" s="24"/>
-      <x:c r="I18" s="21" t="n">
+      <x:c r="H23" s="25"/>
+      <x:c r="I23" s="22" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="23" t="n">
+      <x:c r="J23" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="24" t="n">
+      <x:c r="K23" s="25" t="n">
         <x:v>0.14986492610341606</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="32.400001525878906" hidden="0" customHeight="1">
-      <x:c r="A19" s="21" t="str">
+    <x:row r="24" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A24" s="22" t="str">
         <x:v>Economic value &amp; governance</x:v>
       </x:c>
-      <x:c r="B19" s="22" t="n">
-        <x:v>0.431</x:v>
-      </x:c>
-      <x:c r="C19" s="21" t="str">
+      <x:c r="B24" s="23" t="n">
+        <x:v>0.45648703775762767</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="str">
         <x:v>Low</x:v>
       </x:c>
-      <x:c r="D19" s="23" t="n">
+      <x:c r="D24" s="24" t="n">
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="E19" s="21" t="n">
+      <x:c r="E24" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F19" s="21" t="n">
+      <x:c r="F24" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G19" s="21" t="n">
+      <x:c r="G24" s="22" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H19" s="24" t="n">
+      <x:c r="H24" s="25" t="n">
         <x:v>0.18665713536174536</x:v>
       </x:c>
-      <x:c r="I19" s="21" t="n">
+      <x:c r="I24" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J19" s="23" t="n">
+      <x:c r="J24" s="24" t="n">
         <x:v>0.4</x:v>
       </x:c>
-      <x:c r="K19" s="24" t="n">
+      <x:c r="K24" s="25" t="n">
         <x:v>0.16458180980674778</x:v>
       </x:c>
     </x:row>
@@ -1207,7 +1325,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09387638196847e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd59b28c7a0c8499d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1380,10 +1498,10 @@
       <x:c r="L6" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M6" s="20" t="n">
+      <x:c r="M6" s="18" t="n">
         <x:v>0.006808143514318021</x:v>
       </x:c>
-      <x:c r="N6" s="20" t="n">
+      <x:c r="N6" s="18" t="n">
         <x:v>-0.07189690487427766</x:v>
       </x:c>
       <x:c r="O6" s="16" t="str">
@@ -1430,10 +1548,10 @@
       <x:c r="L7" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M7" s="20" t="n">
+      <x:c r="M7" s="18" t="n">
         <x:v>0.0062915457873307535</x:v>
       </x:c>
-      <x:c r="N7" s="20" t="n">
+      <x:c r="N7" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O7" s="16" t="str">
@@ -1480,10 +1598,10 @@
       <x:c r="L8" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M8" s="20" t="n">
+      <x:c r="M8" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N8" s="20" t="n">
+      <x:c r="N8" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O8" s="16" t="str">
@@ -1530,10 +1648,10 @@
       <x:c r="L9" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M9" s="20" t="n">
+      <x:c r="M9" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N9" s="20" t="n">
+      <x:c r="N9" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O9" s="16" t="str">
@@ -1580,10 +1698,10 @@
       <x:c r="L10" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M10" s="20" t="n">
+      <x:c r="M10" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N10" s="20" t="n">
+      <x:c r="N10" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O10" s="16" t="str">
@@ -1630,10 +1748,10 @@
       <x:c r="L11" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M11" s="20" t="n">
+      <x:c r="M11" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N11" s="20" t="n">
+      <x:c r="N11" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O11" s="16" t="str">
@@ -1680,10 +1798,10 @@
       <x:c r="L12" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M12" s="20" t="n">
+      <x:c r="M12" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N12" s="20" t="n">
+      <x:c r="N12" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O12" s="16" t="str">
@@ -1730,10 +1848,10 @@
       <x:c r="L13" s="16" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M13" s="20" t="n">
+      <x:c r="M13" s="18" t="n">
         <x:v>0.24746910268691757</x:v>
       </x:c>
-      <x:c r="N13" s="20" t="n">
+      <x:c r="N13" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O13" s="16" t="str">
@@ -1780,10 +1898,10 @@
       <x:c r="L14" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M14" s="20" t="n">
+      <x:c r="M14" s="18" t="n">
         <x:v>0.07289706443729066</x:v>
       </x:c>
-      <x:c r="N14" s="20" t="n">
+      <x:c r="N14" s="18" t="n">
         <x:v>-0.060528090139230106</x:v>
       </x:c>
       <x:c r="O14" s="16" t="str">
@@ -1830,10 +1948,10 @@
       <x:c r="L15" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M15" s="20" t="n">
+      <x:c r="M15" s="18" t="n">
         <x:v>0.2794599537469049</x:v>
       </x:c>
-      <x:c r="N15" s="20" t="n">
+      <x:c r="N15" s="18" t="n">
         <x:v>-0.004969950297574373</x:v>
       </x:c>
       <x:c r="O15" s="16" t="str">
@@ -1880,10 +1998,10 @@
       <x:c r="L16" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M16" s="20" t="n">
+      <x:c r="M16" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N16" s="20" t="n">
+      <x:c r="N16" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O16" s="16" t="str">
@@ -1930,10 +2048,10 @@
       <x:c r="L17" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M17" s="20" t="n">
+      <x:c r="M17" s="18" t="n">
         <x:v>0.2876679105055806</x:v>
       </x:c>
-      <x:c r="N17" s="20" t="n">
+      <x:c r="N17" s="18" t="n">
         <x:v>0.15016501951621222</x:v>
       </x:c>
       <x:c r="O17" s="16" t="str">
@@ -1976,10 +2094,10 @@
       <x:c r="L18" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="20" t="n">
+      <x:c r="M18" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18" s="20" t="n">
+      <x:c r="N18" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O18" s="16" t="str">
@@ -2026,10 +2144,10 @@
       <x:c r="L19" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M19" s="20" t="n">
+      <x:c r="M19" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N19" s="20" t="n">
+      <x:c r="N19" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O19" s="16" t="str">
@@ -2076,10 +2194,10 @@
       <x:c r="L20" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M20" s="20" t="n">
+      <x:c r="M20" s="18" t="n">
         <x:v>0.30638724399158446</x:v>
       </x:c>
-      <x:c r="N20" s="20" t="n">
+      <x:c r="N20" s="18" t="n">
         <x:v>0.17695542656782204</x:v>
       </x:c>
       <x:c r="O20" s="16" t="str">
@@ -2126,10 +2244,10 @@
       <x:c r="L21" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M21" s="20" t="n">
+      <x:c r="M21" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N21" s="20" t="n">
+      <x:c r="N21" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O21" s="16" t="str">
@@ -2176,10 +2294,10 @@
       <x:c r="L22" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M22" s="20" t="n">
+      <x:c r="M22" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N22" s="20" t="n">
+      <x:c r="N22" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O22" s="16" t="str">
@@ -2226,10 +2344,10 @@
       <x:c r="L23" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M23" s="20" t="n">
+      <x:c r="M23" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N23" s="20" t="n">
+      <x:c r="N23" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O23" s="16" t="str">
@@ -2276,10 +2394,10 @@
       <x:c r="L24" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M24" s="20" t="n">
+      <x:c r="M24" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N24" s="20" t="n">
+      <x:c r="N24" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O24" s="16" t="str">
@@ -2322,10 +2440,10 @@
       <x:c r="L25" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="20" t="n">
+      <x:c r="M25" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N25" s="20" t="n">
+      <x:c r="N25" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O25" s="16" t="str">
@@ -2372,10 +2490,10 @@
       <x:c r="L26" s="16" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="M26" s="20" t="n">
+      <x:c r="M26" s="18" t="n">
         <x:v>0.18665713536174536</x:v>
       </x:c>
-      <x:c r="N26" s="20" t="n">
+      <x:c r="N26" s="18" t="n">
         <x:v>0.18034796332026065</x:v>
       </x:c>
       <x:c r="O26" s="16" t="str">
@@ -2418,10 +2536,10 @@
       <x:c r="L27" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="20" t="n">
+      <x:c r="M27" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N27" s="20" t="n">
+      <x:c r="N27" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O27" s="16" t="str">
@@ -2468,10 +2586,10 @@
       <x:c r="L28" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M28" s="20" t="n">
+      <x:c r="M28" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N28" s="20" t="n">
+      <x:c r="N28" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O28" s="16" t="str">
@@ -2518,10 +2636,10 @@
       <x:c r="L29" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M29" s="20" t="n">
+      <x:c r="M29" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N29" s="20" t="n">
+      <x:c r="N29" s="18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="O29" s="16" t="str">
@@ -2538,7 +2656,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc34ca3276aee40e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra30f6646b44743ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2639,7 +2757,7 @@
       <x:c r="B6" s="16" t="str">
         <x:v>DES-01</x:v>
       </x:c>
-      <x:c r="C6" s="25" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
@@ -2671,7 +2789,7 @@
       <x:c r="B7" s="16" t="str">
         <x:v>DES-01</x:v>
       </x:c>
-      <x:c r="C7" s="25" t="str">
+      <x:c r="C7" s="26" t="str">
         <x:v>2026-04-16</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
@@ -2703,7 +2821,7 @@
       <x:c r="B8" s="16" t="str">
         <x:v>DES-01</x:v>
       </x:c>
-      <x:c r="C8" s="25" t="str">
+      <x:c r="C8" s="26" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
@@ -2735,7 +2853,7 @@
       <x:c r="B9" s="16" t="str">
         <x:v>DES-02</x:v>
       </x:c>
-      <x:c r="C9" s="25" t="str">
+      <x:c r="C9" s="26" t="str">
         <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
@@ -2767,7 +2885,7 @@
       <x:c r="B10" s="16" t="str">
         <x:v>DES-02</x:v>
       </x:c>
-      <x:c r="C10" s="25" t="str">
+      <x:c r="C10" s="26" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="D10" s="16" t="str">
@@ -2799,7 +2917,7 @@
       <x:c r="B11" s="16" t="str">
         <x:v>DES-03</x:v>
       </x:c>
-      <x:c r="C11" s="25" t="str">
+      <x:c r="C11" s="26" t="str">
         <x:v>2026-04-01</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
@@ -2831,7 +2949,7 @@
       <x:c r="B12" s="16" t="str">
         <x:v>DES-04</x:v>
       </x:c>
-      <x:c r="C12" s="25" t="str">
+      <x:c r="C12" s="26" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
       <x:c r="D12" s="16" t="str">
@@ -2863,7 +2981,7 @@
       <x:c r="B13" s="16" t="str">
         <x:v>DES-05</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="str">
+      <x:c r="C13" s="26" t="str">
         <x:v>2026-03-20</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
@@ -2895,7 +3013,7 @@
       <x:c r="B14" s="16" t="str">
         <x:v>DES-06</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="str">
+      <x:c r="C14" s="26" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="D14" s="16" t="str">
@@ -2927,7 +3045,7 @@
       <x:c r="B15" s="16" t="str">
         <x:v>DES-07</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="str">
+      <x:c r="C15" s="26" t="str">
         <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="D15" s="16" t="str">
@@ -2959,7 +3077,7 @@
       <x:c r="B16" s="16" t="str">
         <x:v>OPS-01</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="str">
+      <x:c r="C16" s="26" t="str">
         <x:v>2026-05-28</x:v>
       </x:c>
       <x:c r="D16" s="16" t="str">
@@ -2991,7 +3109,7 @@
       <x:c r="B17" s="16" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="str">
+      <x:c r="C17" s="26" t="str">
         <x:v>2025-06-17</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
@@ -3023,7 +3141,7 @@
       <x:c r="B18" s="16" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="str">
+      <x:c r="C18" s="26" t="str">
         <x:v>2025-09-29</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
@@ -3055,7 +3173,7 @@
       <x:c r="B19" s="16" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="str">
+      <x:c r="C19" s="26" t="str">
         <x:v>2025-11-24</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
@@ -3087,7 +3205,7 @@
       <x:c r="B20" s="16" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="str">
+      <x:c r="C20" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
@@ -3119,7 +3237,7 @@
       <x:c r="B21" s="16" t="str">
         <x:v>OPS-02</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="str">
+      <x:c r="C21" s="26" t="str">
         <x:v>2026-07-01</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
@@ -3151,7 +3269,7 @@
       <x:c r="B22" s="16" t="str">
         <x:v>OPS-03</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="str">
+      <x:c r="C22" s="26" t="str">
         <x:v>2025-12-17</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
@@ -3183,7 +3301,7 @@
       <x:c r="B23" s="16" t="str">
         <x:v>OPS-03</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="str">
+      <x:c r="C23" s="26" t="str">
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="D23" s="16" t="str">
@@ -3215,7 +3333,7 @@
       <x:c r="B24" s="16" t="str">
         <x:v>OPS-03</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="str">
+      <x:c r="C24" s="26" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="D24" s="16" t="str">
@@ -3247,7 +3365,7 @@
       <x:c r="B25" s="16" t="str">
         <x:v>OPS-04</x:v>
       </x:c>
-      <x:c r="C25" s="25" t="str">
+      <x:c r="C25" s="26" t="str">
         <x:v>2026-03-01</x:v>
       </x:c>
       <x:c r="D25" s="16" t="str">
@@ -3279,7 +3397,7 @@
       <x:c r="B26" s="16" t="str">
         <x:v>OPS-05</x:v>
       </x:c>
-      <x:c r="C26" s="25" t="str">
+      <x:c r="C26" s="26" t="str">
         <x:v>2024-12-19</x:v>
       </x:c>
       <x:c r="D26" s="16" t="str">
@@ -3311,7 +3429,7 @@
       <x:c r="B27" s="16" t="str">
         <x:v>OPS-05</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="str">
+      <x:c r="C27" s="26" t="str">
         <x:v>2025-06-17</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
@@ -3343,7 +3461,7 @@
       <x:c r="B28" s="16" t="str">
         <x:v>OPS-05</x:v>
       </x:c>
-      <x:c r="C28" s="25" t="str">
+      <x:c r="C28" s="26" t="str">
         <x:v>2025-09-01</x:v>
       </x:c>
       <x:c r="D28" s="16" t="str">
@@ -3375,7 +3493,7 @@
       <x:c r="B29" s="16" t="str">
         <x:v>OPS-07</x:v>
       </x:c>
-      <x:c r="C29" s="25" t="str">
+      <x:c r="C29" s="26" t="str">
         <x:v>2025-11-13</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
@@ -3407,7 +3525,7 @@
       <x:c r="B30" s="16" t="str">
         <x:v>OPS-08</x:v>
       </x:c>
-      <x:c r="C30" s="25" t="str">
+      <x:c r="C30" s="26" t="str">
         <x:v>2025-09-29</x:v>
       </x:c>
       <x:c r="D30" s="16" t="str">
@@ -3439,7 +3557,7 @@
       <x:c r="B31" s="16" t="str">
         <x:v>OPS-08</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="str">
+      <x:c r="C31" s="26" t="str">
         <x:v>2025-12-11</x:v>
       </x:c>
       <x:c r="D31" s="16" t="str">
@@ -3471,7 +3589,7 @@
       <x:c r="B32" s="16" t="str">
         <x:v>OPS-08</x:v>
       </x:c>
-      <x:c r="C32" s="25" t="str">
+      <x:c r="C32" s="26" t="str">
         <x:v>2026-03-05</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
@@ -3503,7 +3621,7 @@
       <x:c r="B33" s="16" t="str">
         <x:v>OPS-08</x:v>
       </x:c>
-      <x:c r="C33" s="25" t="str">
+      <x:c r="C33" s="26" t="str">
         <x:v>2026-05-01</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
@@ -3535,7 +3653,7 @@
       <x:c r="B34" s="16" t="str">
         <x:v>OPS-08</x:v>
       </x:c>
-      <x:c r="C34" s="25" t="str">
+      <x:c r="C34" s="26" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
@@ -3567,7 +3685,7 @@
       <x:c r="B35" s="16" t="str">
         <x:v>PER-01</x:v>
       </x:c>
-      <x:c r="C35" s="25" t="str">
+      <x:c r="C35" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
@@ -3599,7 +3717,7 @@
       <x:c r="B36" s="16" t="str">
         <x:v>PER-02</x:v>
       </x:c>
-      <x:c r="C36" s="25" t="str">
+      <x:c r="C36" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="D36" s="16" t="str">
@@ -3631,7 +3749,7 @@
       <x:c r="B37" s="16" t="str">
         <x:v>PER-03</x:v>
       </x:c>
-      <x:c r="C37" s="25" t="str">
+      <x:c r="C37" s="26" t="str">
         <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
@@ -3663,7 +3781,7 @@
       <x:c r="B38" s="16" t="str">
         <x:v>PER-04</x:v>
       </x:c>
-      <x:c r="C38" s="25" t="str">
+      <x:c r="C38" s="26" t="str">
         <x:v>2025-04-16</x:v>
       </x:c>
       <x:c r="D38" s="16" t="str">
@@ -3695,7 +3813,7 @@
       <x:c r="B39" s="16" t="str">
         <x:v>VAL-02</x:v>
       </x:c>
-      <x:c r="C39" s="25" t="str">
+      <x:c r="C39" s="26" t="str">
         <x:v>2025-09-29</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
@@ -3727,7 +3845,7 @@
       <x:c r="B40" s="16" t="str">
         <x:v>VAL-02</x:v>
       </x:c>
-      <x:c r="C40" s="25" t="str">
+      <x:c r="C40" s="26" t="str">
         <x:v>2025-11-24</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
@@ -3759,7 +3877,7 @@
       <x:c r="B41" s="16" t="str">
         <x:v>VAL-02</x:v>
       </x:c>
-      <x:c r="C41" s="25" t="str">
+      <x:c r="C41" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
@@ -3791,7 +3909,7 @@
       <x:c r="B42" s="16" t="str">
         <x:v>VAL-02</x:v>
       </x:c>
-      <x:c r="C42" s="25" t="str">
+      <x:c r="C42" s="26" t="str">
         <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
@@ -3823,7 +3941,7 @@
       <x:c r="B43" s="16" t="str">
         <x:v>VAL-04</x:v>
       </x:c>
-      <x:c r="C43" s="25" t="str">
+      <x:c r="C43" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
@@ -3855,7 +3973,7 @@
       <x:c r="B44" s="16" t="str">
         <x:v>OPS-09</x:v>
       </x:c>
-      <x:c r="C44" s="25" t="str">
+      <x:c r="C44" s="26" t="str">
         <x:v>2026-04-16</x:v>
       </x:c>
       <x:c r="D44" s="16" t="str">
@@ -3887,7 +4005,7 @@
       <x:c r="B45" s="16" t="str">
         <x:v>OPS-01</x:v>
       </x:c>
-      <x:c r="C45" s="25" t="str">
+      <x:c r="C45" s="26" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="D45" s="16" t="str">
@@ -3919,7 +4037,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R632a86f1ba8548cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05559de72d3146bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4006,7 +4124,7 @@
       <x:c r="A6" s="16" t="str">
         <x:v>2024-Q1</x:v>
       </x:c>
-      <x:c r="B6" s="25" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>2024-03-31</x:v>
       </x:c>
       <x:c r="C6" s="17"/>
@@ -4019,7 +4137,7 @@
       <x:c r="A7" s="16" t="str">
         <x:v>2024-Q2</x:v>
       </x:c>
-      <x:c r="B7" s="25" t="str">
+      <x:c r="B7" s="26" t="str">
         <x:v>2024-06-30</x:v>
       </x:c>
       <x:c r="C7" s="17"/>
@@ -4032,7 +4150,7 @@
       <x:c r="A8" s="16" t="str">
         <x:v>2024-Q3</x:v>
       </x:c>
-      <x:c r="B8" s="25" t="str">
+      <x:c r="B8" s="26" t="str">
         <x:v>2024-09-30</x:v>
       </x:c>
       <x:c r="C8" s="17"/>
@@ -4045,7 +4163,7 @@
       <x:c r="A9" s="16" t="str">
         <x:v>2024-Q4</x:v>
       </x:c>
-      <x:c r="B9" s="25" t="str">
+      <x:c r="B9" s="26" t="str">
         <x:v>2024-12-31</x:v>
       </x:c>
       <x:c r="C9" s="17" t="n">
@@ -4062,7 +4180,7 @@
       <x:c r="A10" s="16" t="str">
         <x:v>2025-Q1</x:v>
       </x:c>
-      <x:c r="B10" s="25" t="str">
+      <x:c r="B10" s="26" t="str">
         <x:v>2025-03-31</x:v>
       </x:c>
       <x:c r="C10" s="17" t="n">
@@ -4079,7 +4197,7 @@
       <x:c r="A11" s="16" t="str">
         <x:v>2025-Q2</x:v>
       </x:c>
-      <x:c r="B11" s="25" t="str">
+      <x:c r="B11" s="26" t="str">
         <x:v>2025-06-30</x:v>
       </x:c>
       <x:c r="C11" s="17" t="n">
@@ -4098,7 +4216,7 @@
       <x:c r="A12" s="16" t="str">
         <x:v>2025-Q3</x:v>
       </x:c>
-      <x:c r="B12" s="25" t="str">
+      <x:c r="B12" s="26" t="str">
         <x:v>2025-09-30</x:v>
       </x:c>
       <x:c r="C12" s="17" t="n">
@@ -4119,7 +4237,7 @@
       <x:c r="A13" s="16" t="str">
         <x:v>2025-Q4</x:v>
       </x:c>
-      <x:c r="B13" s="25" t="str">
+      <x:c r="B13" s="26" t="str">
         <x:v>2025-12-31</x:v>
       </x:c>
       <x:c r="C13" s="17" t="n">
@@ -4140,7 +4258,7 @@
       <x:c r="A14" s="16" t="str">
         <x:v>2026-Q1</x:v>
       </x:c>
-      <x:c r="B14" s="25" t="str">
+      <x:c r="B14" s="26" t="str">
         <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="C14" s="17" t="n">
@@ -4163,7 +4281,7 @@
       <x:c r="A15" s="16" t="str">
         <x:v>2026-Q2</x:v>
       </x:c>
-      <x:c r="B15" s="25" t="str">
+      <x:c r="B15" s="26" t="str">
         <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="C15" s="17" t="n">
@@ -4186,230 +4304,230 @@
       <x:c r="A16" s="16" t="str">
         <x:v>2026-Q3</x:v>
       </x:c>
-      <x:c r="B16" s="25" t="str">
+      <x:c r="B16" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="C16" s="17" t="n">
-        <x:v>0.46141401843584867</x:v>
+        <x:v>0.4836511835014151</x:v>
       </x:c>
       <x:c r="D16" s="17" t="n">
-        <x:v>0.38254856862232545</x:v>
+        <x:v>0.39584909716180033</x:v>
       </x:c>
       <x:c r="E16" s="17" t="n">
-        <x:v>0.5195</x:v>
+        <x:v>0.5476163788058475</x:v>
       </x:c>
       <x:c r="F16" s="17" t="n">
-        <x:v>0.49477499999999996</x:v>
+        <x:v>0.5154237344727879</x:v>
       </x:c>
       <x:c r="G16" s="17" t="n">
-        <x:v>0.431</x:v>
+        <x:v>0.45648703775762767</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A17" s="16" t="str">
         <x:v>2026-Q4</x:v>
       </x:c>
-      <x:c r="B17" s="25" t="str">
+      <x:c r="B17" s="26" t="str">
         <x:v>2026-12-31</x:v>
       </x:c>
       <x:c r="C17" s="17" t="n">
-        <x:v>0.5229995627802766</x:v>
+        <x:v>0.548819841416865</x:v>
       </x:c>
       <x:c r="D17" s="17" t="n">
-        <x:v>0.4202758375398714</x:v>
+        <x:v>0.4369838560641441</x:v>
       </x:c>
       <x:c r="E17" s="17" t="n">
-        <x:v>0.5964688772542405</x:v>
+        <x:v>0.6278564695617517</x:v>
       </x:c>
       <x:c r="F17" s="17" t="n">
-        <x:v>0.552271008992256</x:v>
+        <x:v>0.5766712382271815</x:v>
       </x:c>
       <x:c r="G17" s="17" t="n">
-        <x:v>0.5017009236990078</x:v>
+        <x:v>0.5314427292494595</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A18" s="16" t="str">
         <x:v>2027-Q1</x:v>
       </x:c>
-      <x:c r="B18" s="25" t="str">
+      <x:c r="B18" s="26" t="str">
         <x:v>2027-03-31</x:v>
       </x:c>
       <x:c r="C18" s="17" t="n">
-        <x:v>0.5935051470655859</x:v>
+        <x:v>0.6221094789334313</x:v>
       </x:c>
       <x:c r="D18" s="17" t="n">
-        <x:v>0.4673398551270709</x:v>
+        <x:v>0.48785339675199246</x:v>
       </x:c>
       <x:c r="E18" s="17" t="n">
-        <x:v>0.6808011881770635</x:v>
+        <x:v>0.7136908887887266</x:v>
       </x:c>
       <x:c r="F18" s="17" t="n">
-        <x:v>0.6193267190642807</x:v>
+        <x:v>0.6469233399366259</x:v>
       </x:c>
       <x:c r="G18" s="17" t="n">
-        <x:v>0.5830271843081689</x:v>
+        <x:v>0.6161029135421308</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A19" s="16" t="str">
         <x:v>2027-Q2</x:v>
       </x:c>
-      <x:c r="B19" s="25" t="str">
+      <x:c r="B19" s="26" t="str">
         <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="C19" s="17" t="n">
-        <x:v>0.6702136448373787</x:v>
+        <x:v>0.7000389755923849</x:v>
       </x:c>
       <x:c r="D19" s="17" t="n">
-        <x:v>0.5245890317621351</x:v>
+        <x:v>0.5490126355724585</x:v>
       </x:c>
       <x:c r="E19" s="17" t="n">
-        <x:v>0.7670137971277526</x:v>
+        <x:v>0.7986697461894741</x:v>
       </x:c>
       <x:c r="F19" s="17" t="n">
-        <x:v>0.6938558057039086</x:v>
+        <x:v>0.7232837561717131</x:v>
       </x:c>
       <x:c r="G19" s="17" t="n">
-        <x:v>0.6717619134028711</x:v>
+        <x:v>0.7062435426438467</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A20" s="16" t="str">
         <x:v>2027-Q3</x:v>
       </x:c>
-      <x:c r="B20" s="25" t="str">
+      <x:c r="B20" s="26" t="str">
         <x:v>2027-09-30</x:v>
       </x:c>
       <x:c r="C20" s="17" t="n">
-        <x:v>0.7484056019235392</x:v>
+        <x:v>0.7772105650159628</x:v>
       </x:c>
       <x:c r="D20" s="17" t="n">
-        <x:v>0.5919116923360023</x:v>
+        <x:v>0.6198152736997502</x:v>
       </x:c>
       <x:c r="E20" s="17" t="n">
-        <x:v>0.847345194629627</x:v>
+        <x:v>0.874529814377945</x:v>
       </x:c>
       <x:c r="F20" s="17" t="n">
-        <x:v>0.771519152001999</x:v>
+        <x:v>0.8005165242137949</x:v>
       </x:c>
       <x:c r="G20" s="17" t="n">
-        <x:v>0.7619688824935531</x:v>
+        <x:v>0.794929773189293</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A21" s="16" t="str">
         <x:v>2027-Q4</x:v>
       </x:c>
-      <x:c r="B21" s="25" t="str">
+      <x:c r="B21" s="26" t="str">
         <x:v>2027-12-31</x:v>
       </x:c>
       <x:c r="C21" s="17" t="n">
-        <x:v>0.8218754308129803</x:v>
+        <x:v>0.847201887016517</x:v>
       </x:c>
       <x:c r="D21" s="17" t="n">
-        <x:v>0.6675717363225923</x:v>
+        <x:v>0.6977333577675674</x:v>
       </x:c>
       <x:c r="E21" s="17" t="n">
-        <x:v>0.9134787578279036</x:v>
+        <x:v>0.9335116118602027</x:v>
       </x:c>
       <x:c r="F21" s="17" t="n">
-        <x:v>0.8457604280448145</x:v>
+        <x:v>0.8714595307433102</x:v>
       </x:c>
       <x:c r="G21" s="17" t="n">
-        <x:v>0.845395776269385</x:v>
+        <x:v>0.8734412333850708</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A22" s="16" t="str">
         <x:v>2028-Q1</x:v>
       </x:c>
-      <x:c r="B22" s="25" t="str">
+      <x:c r="B22" s="26" t="str">
         <x:v>2028-03-31</x:v>
       </x:c>
       <x:c r="C22" s="17" t="n">
-        <x:v>0.8844520818471866</x:v>
+        <x:v>0.9044087192507758</x:v>
       </x:c>
       <x:c r="D22" s="17" t="n">
-        <x:v>0.7475926341041975</x:v>
+        <x:v>0.777858957062808</x:v>
       </x:c>
       <x:c r="E22" s="17" t="n">
-        <x:v>0.9596379122408556</x:v>
+        <x:v>0.9716616973968089</x:v>
       </x:c>
       <x:c r="F22" s="17" t="n">
-        <x:v>0.909004461475341</x:v>
+        <x:v>0.928760718850436</x:v>
       </x:c>
       <x:c r="G22" s="17" t="n">
-        <x:v>0.9133955193622444</x:v>
+        <x:v>0.933808691040626</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A23" s="16" t="str">
         <x:v>2028-Q2</x:v>
       </x:c>
-      <x:c r="B23" s="25" t="str">
+      <x:c r="B23" s="26" t="str">
         <x:v>2028-06-30</x:v>
       </x:c>
       <x:c r="C23" s="17" t="n">
-        <x:v>0.9320987866474012</x:v>
+        <x:v>0.9460566809508101</x:v>
       </x:c>
       <x:c r="D23" s="17" t="n">
-        <x:v>0.8256212592531782</x:v>
+        <x:v>0.8531083530008593</x:v>
       </x:c>
       <x:c r="E23" s="17" t="n">
-        <x:v>0.9855034454242547</x:v>
+        <x:v>0.9909844626445938</x:v>
       </x:c>
       <x:c r="F23" s="17" t="n">
-        <x:v>0.9552024733547424</x:v>
+        <x:v>0.9677521907198676</x:v>
       </x:c>
       <x:c r="G23" s="17" t="n">
-        <x:v>0.9602303867818771</x:v>
+        <x:v>0.972280909180725</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A24" s="16" t="str">
         <x:v>2028-Q3</x:v>
       </x:c>
-      <x:c r="B24" s="25" t="str">
+      <x:c r="B24" s="26" t="str">
         <x:v>2028-09-30</x:v>
       </x:c>
       <x:c r="C24" s="17" t="n">
-        <x:v>0.9643049231635812</x:v>
+        <x:v>0.9729560568281789</x:v>
       </x:c>
       <x:c r="D24" s="17" t="n">
-        <x:v>0.8938773235175859</x:v>
+        <x:v>0.9157121493692403</x:v>
       </x:c>
       <x:c r="E24" s="17" t="n">
-        <x:v>0.9963351713992433</x:v>
+        <x:v>0.9980633817617315</x:v>
       </x:c>
       <x:c r="F24" s="17" t="n">
-        <x:v>0.9827039499618946</x:v>
+        <x:v>0.9888765606508462</x:v>
       </x:c>
       <x:c r="G24" s="17" t="n">
-        <x:v>0.986015173001708</x:v>
+        <x:v>0.9913876165644271</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A25" s="16" t="str">
         <x:v>2028-Q4</x:v>
       </x:c>
-      <x:c r="B25" s="25" t="str">
+      <x:c r="B25" s="26" t="str">
         <x:v>2028-12-31</x:v>
       </x:c>
       <x:c r="C25" s="17" t="n">
-        <x:v>0.9836084379542608</x:v>
+        <x:v>0.9883348220856817</x:v>
       </x:c>
       <x:c r="D25" s="17" t="n">
-        <x:v>0.9455298336524652</x:v>
+        <x:v>0.9600231980524645</x:v>
       </x:c>
       <x:c r="E25" s="17" t="n">
-        <x:v>0.9994218464309694</x:v>
+        <x:v>0.9997545066687251</x:v>
       </x:c>
       <x:c r="F25" s="17" t="n">
-        <x:v>0.9951815650138214</x:v>
+        <x:v>0.9973364765557599</x:v>
       </x:c>
       <x:c r="G25" s="17" t="n">
-        <x:v>0.996563545473006</x:v>
+        <x:v>0.998207829482387</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4418,9 +4536,9 @@
     <x:mergeCell ref="A3:G3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3d9885d5bf1475d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf45dd3b021f34d98"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c1e0ddf3454318"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a7127194c2b4985"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4520,7 +4638,7 @@
       <x:c r="D6" s="16" t="str">
         <x:v>GPT-5</x:v>
       </x:c>
-      <x:c r="E6" s="25" t="str">
+      <x:c r="E6" s="26" t="str">
         <x:v>2025-08-07</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
@@ -4549,7 +4667,7 @@
       <x:c r="D7" s="16" t="str">
         <x:v>Claude Opus 4.5</x:v>
       </x:c>
-      <x:c r="E7" s="25" t="str">
+      <x:c r="E7" s="26" t="str">
         <x:v>2025-11-24</x:v>
       </x:c>
       <x:c r="F7" s="16" t="n">
@@ -4578,7 +4696,7 @@
       <x:c r="D8" s="16" t="str">
         <x:v>GPT-5.2</x:v>
       </x:c>
-      <x:c r="E8" s="25" t="str">
+      <x:c r="E8" s="26" t="str">
         <x:v>2025-12-11</x:v>
       </x:c>
       <x:c r="F8" s="16" t="n">
@@ -4607,7 +4725,7 @@
       <x:c r="D9" s="16" t="str">
         <x:v>Claude Opus 4.6</x:v>
       </x:c>
-      <x:c r="E9" s="25" t="str">
+      <x:c r="E9" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="F9" s="16" t="n">
@@ -4636,7 +4754,7 @@
       <x:c r="D10" s="16" t="str">
         <x:v>Claude Mythos Preview</x:v>
       </x:c>
-      <x:c r="E10" s="25" t="str">
+      <x:c r="E10" s="26" t="str">
         <x:v>2026-04-07</x:v>
       </x:c>
       <x:c r="F10" s="16" t="n">
@@ -4665,7 +4783,7 @@
       <x:c r="D11" s="16" t="str">
         <x:v>GPT-5</x:v>
       </x:c>
-      <x:c r="E11" s="25" t="str">
+      <x:c r="E11" s="26" t="str">
         <x:v>2025-08-07</x:v>
       </x:c>
       <x:c r="F11" s="16" t="n">
@@ -4694,7 +4812,7 @@
       <x:c r="D12" s="16" t="str">
         <x:v>Claude Opus 4.5</x:v>
       </x:c>
-      <x:c r="E12" s="25" t="str">
+      <x:c r="E12" s="26" t="str">
         <x:v>2025-11-24</x:v>
       </x:c>
       <x:c r="F12" s="16" t="n">
@@ -4723,7 +4841,7 @@
       <x:c r="D13" s="16" t="str">
         <x:v>GPT-5.2</x:v>
       </x:c>
-      <x:c r="E13" s="25" t="str">
+      <x:c r="E13" s="26" t="str">
         <x:v>2025-12-11</x:v>
       </x:c>
       <x:c r="F13" s="16" t="n">
@@ -4752,7 +4870,7 @@
       <x:c r="D14" s="16" t="str">
         <x:v>Claude Opus 4.6</x:v>
       </x:c>
-      <x:c r="E14" s="25" t="str">
+      <x:c r="E14" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="F14" s="16" t="n">
@@ -4781,7 +4899,7 @@
       <x:c r="D15" s="16" t="str">
         <x:v>Claude Mythos Preview</x:v>
       </x:c>
-      <x:c r="E15" s="25" t="str">
+      <x:c r="E15" s="26" t="str">
         <x:v>2026-04-07</x:v>
       </x:c>
       <x:c r="F15" s="16" t="n">
@@ -4810,7 +4928,7 @@
       <x:c r="D16" s="16" t="str">
         <x:v>doubling_time</x:v>
       </x:c>
-      <x:c r="E16" s="25" t="str">
+      <x:c r="E16" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
@@ -4839,7 +4957,7 @@
       <x:c r="D17" s="16" t="str">
         <x:v>doubling_time</x:v>
       </x:c>
-      <x:c r="E17" s="25" t="str">
+      <x:c r="E17" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F17" s="16" t="n">
@@ -4868,7 +4986,7 @@
       <x:c r="D18" s="16" t="str">
         <x:v>doubling_time</x:v>
       </x:c>
-      <x:c r="E18" s="25" t="str">
+      <x:c r="E18" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F18" s="16" t="n">
@@ -4897,7 +5015,7 @@
       <x:c r="D19" s="16" t="str">
         <x:v>h80_doubling_time</x:v>
       </x:c>
-      <x:c r="E19" s="25" t="str">
+      <x:c r="E19" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="F19" s="16" t="n">
@@ -4920,12 +5038,329 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd2377f340ec480c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7558aff35a174b37"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="74" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="60" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="3" t="str">
+        <x:v>Independently Corroborated Frontier-Capability Shock</x:v>
+      </x:c>
+      <x:c r="B1" s="3"/>
+      <x:c r="C1" s="3"/>
+      <x:c r="D1" s="3"/>
+      <x:c r="E1" s="3"/>
+      <x:c r="F1" s="3"/>
+      <x:c r="G1" s="3"/>
+      <x:c r="H1" s="3"/>
+      <x:c r="I1" s="3"/>
+      <x:c r="J1" s="3"/>
+    </x:row>
+    <x:row r="2" ht="26" customHeight="1">
+      <x:c r="A2" s="3"/>
+      <x:c r="B2" s="3"/>
+      <x:c r="C2" s="3"/>
+      <x:c r="D2" s="3"/>
+      <x:c r="E2" s="3"/>
+      <x:c r="F2" s="3"/>
+      <x:c r="G2" s="3"/>
+      <x:c r="H2" s="3"/>
+      <x:c r="I2" s="3"/>
+      <x:c r="J2" s="3"/>
+    </x:row>
+    <x:row r="3" ht="24" hidden="0" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>Astra's overall capability portfolio changes the trajectory through an explicit trend-and-transfer bridge; ARC-AGI-3 and ECI are not treated as delegation percentages.</x:v>
+      </x:c>
+      <x:c r="B3" s="6"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="6"/>
+      <x:c r="F3" s="6"/>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="6"/>
+      <x:c r="I3" s="6"/>
+      <x:c r="J3" s="6"/>
+    </x:row>
+    <x:row r="4"/>
+    <x:row r="5" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Record type</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="C5" s="12" t="str">
+        <x:v>Model / series</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="str">
+        <x:v>Date</x:v>
+      </x:c>
+      <x:c r="E5" s="12" t="str">
+        <x:v>Metric / summary</x:v>
+      </x:c>
+      <x:c r="F5" s="12" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="G5" s="12" t="str">
+        <x:v>Interval / domains</x:v>
+      </x:c>
+      <x:c r="H5" s="12" t="str">
+        <x:v>Publisher</x:v>
+      </x:c>
+      <x:c r="I5" s="12" t="str">
+        <x:v>Source ID</x:v>
+      </x:c>
+      <x:c r="J5" s="12" t="str">
+        <x:v>Countdown treatment</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" hidden="0" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>Aggregate observation</x:v>
+      </x:c>
+      <x:c r="B6" s="16" t="str">
+        <x:v>frontier_astra_eci_20260903</x:v>
+      </x:c>
+      <x:c r="C6" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D6" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E6" s="16" t="str">
+        <x:v>Epoch Capabilities Index</x:v>
+      </x:c>
+      <x:c r="F6" s="16" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G6" s="16" t="str">
+        <x:v>165–174</x:v>
+      </x:c>
+      <x:c r="H6" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="I6" s="16" t="str">
+        <x:v>gate1-epoch-ai-gpt-6-astra-model</x:v>
+      </x:c>
+      <x:c r="J6" s="16" t="str">
+        <x:v>Sets shock magnitude; not a delegation percentage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" hidden="0" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>Trend</x:v>
+      </x:c>
+      <x:c r="B7" s="16" t="str">
+        <x:v>eci_reasoning_frontier_trend_20260901</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="str">
+        <x:v>Reasoning SOTA</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="str">
+        <x:v>linear frontier trend</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G7" s="16" t="str">
+        <x:v>ECI points per year</x:v>
+      </x:c>
+      <x:c r="H7" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="I7" s="16" t="str">
+        <x:v>gate1-epoch-ai-eci-frontier-trend</x:v>
+      </x:c>
+      <x:c r="J7" s="16" t="str">
+        <x:v>Converts ECI gain to broad frontier-progress time</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>Corroboration</x:v>
+      </x:c>
+      <x:c r="B8" s="16" t="str">
+        <x:v>corroboration_openai_release_portfolio_astra</x:v>
+      </x:c>
+      <x:c r="C8" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E8" s="16" t="str">
+        <x:v>OpenAI reports large release-day gains across reasoning, mathematics, cyber, computer use, workflow automation, broad work, and authorization-boundary evaluations.</x:v>
+      </x:c>
+      <x:c r="F8" s="16"/>
+      <x:c r="G8" s="16" t="str">
+        <x:v>abstract reasoning, mathematics, cybersecurity, computer use, business workflows, broad professional work, scope adherence</x:v>
+      </x:c>
+      <x:c r="H8" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="I8" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="J8" s="16" t="str">
+        <x:v>Portfolio evidence; not an independent publisher</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>Corroboration</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
+        <x:v>corroboration_epoch_eci_astra</x:v>
+      </x:c>
+      <x:c r="C9" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E9" s="16" t="str">
+        <x:v>Astra set a new ECI record at 169, six points above the rounded prior best.</x:v>
+      </x:c>
+      <x:c r="F9" s="16"/>
+      <x:c r="G9" s="16" t="str">
+        <x:v>broad aggregate capability</x:v>
+      </x:c>
+      <x:c r="H9" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="I9" s="16" t="str">
+        <x:v>gate1-epoch-ai-gpt-6-astra-model</x:v>
+      </x:c>
+      <x:c r="J9" s="16" t="str">
+        <x:v>Independent qualification evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="151.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>Corroboration</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
+        <x:v>corroboration_epoch_domain_records_astra</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D10" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E10" s="16" t="str">
+        <x:v>Epoch reports records on its math, continual-learning, and game-puzzle benchmarks; Astra's MirrorCode result lies between Opus 4.7 and Fable 5.</x:v>
+      </x:c>
+      <x:c r="F10" s="16"/>
+      <x:c r="G10" s="16" t="str">
+        <x:v>mathematics, continual learning, game puzzles, long-horizon coding</x:v>
+      </x:c>
+      <x:c r="H10" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="I10" s="16" t="str">
+        <x:v>gate1-x-com-epoch-ai-gpt-6-astra-assessment</x:v>
+      </x:c>
+      <x:c r="J10" s="16" t="str">
+        <x:v>Independent qualification evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="162" hidden="0" customHeight="1">
+      <x:c r="A11" s="16" t="str">
+        <x:v>Corroboration</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="str">
+        <x:v>corroboration_arcprize_astra</x:v>
+      </x:c>
+      <x:c r="C11" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D11" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E11" s="16" t="str">
+        <x:v>Astra scored 62.7% on ARC Prize's standard harness and 99.9% with the provider adapter, while using fewer actions than the median human on 96.0% of levels.</x:v>
+      </x:c>
+      <x:c r="F11" s="16"/>
+      <x:c r="G11" s="16" t="str">
+        <x:v>interactive abstract reasoning, exploration, world-model formation, planning, action efficiency</x:v>
+      </x:c>
+      <x:c r="H11" s="16" t="str">
+        <x:v>ARC Prize Foundation</x:v>
+      </x:c>
+      <x:c r="I11" s="16" t="str">
+        <x:v>gate1-arcprize-org-gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="J11" s="16" t="str">
+        <x:v>Independent qualification evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A12" s="16" t="str">
+        <x:v>Forecast policy</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="str">
+        <x:v>frontier_astra_eci_20260903</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="str">
+        <x:v>eci_reasoning_frontier_trend_20260901</x:v>
+      </x:c>
+      <x:c r="D12" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E12" s="16" t="str">
+        <x:v>eciTimeLeadTimesEconomicToH50TransferCoefficient</x:v>
+      </x:c>
+      <x:c r="F12" s="16" t="n">
+        <x:v>0.3796461564826924</x:v>
+      </x:c>
+      <x:c r="G12" s="16" t="str">
+        <x:v>2 independent publishers; 3 domains</x:v>
+      </x:c>
+      <x:c r="H12" s="16" t="str">
+        <x:v>Diffuse Personal AI</x:v>
+      </x:c>
+      <x:c r="I12" s="16" t="str">
+        <x:v>gate1-diffuse-personal-ai-gate-1-model-harness-capability-calculation-contract</x:v>
+      </x:c>
+      <x:c r="J12" s="16" t="str">
+        <x:v>One-time economic-equivalent lead; direct benchmark observations unchanged</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J2"/>
+    <x:mergeCell ref="A3:J3"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R154b8694c8a947cf"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5014,7 +5449,7 @@
       <x:c r="B6" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C6" s="25" t="str">
+      <x:c r="C6" s="26" t="str">
         <x:v>2026-02-27</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
@@ -5041,7 +5476,7 @@
       <x:c r="B7" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C7" s="25" t="str">
+      <x:c r="C7" s="26" t="str">
         <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
@@ -5068,7 +5503,7 @@
       <x:c r="B8" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C8" s="25" t="str">
+      <x:c r="C8" s="26" t="str">
         <x:v>2025-11-05</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
@@ -5095,7 +5530,7 @@
       <x:c r="B9" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C9" s="25" t="str">
+      <x:c r="C9" s="26" t="str">
         <x:v>2025-09-02</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
@@ -5122,7 +5557,7 @@
       <x:c r="B10" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C10" s="25" t="str">
+      <x:c r="C10" s="26" t="str">
         <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="D10" s="16" t="str">
@@ -5151,7 +5586,7 @@
       <x:c r="B11" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C11" s="25" t="str">
+      <x:c r="C11" s="26" t="str">
         <x:v>2026-03-31</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
@@ -5180,7 +5615,7 @@
       <x:c r="B12" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C12" s="25" t="str">
+      <x:c r="C12" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D12" s="16" t="str">
@@ -5209,7 +5644,7 @@
       <x:c r="B13" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="str">
+      <x:c r="C13" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
@@ -5238,7 +5673,7 @@
       <x:c r="B14" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="str">
+      <x:c r="C14" s="26" t="str">
         <x:v>2026-08-24</x:v>
       </x:c>
       <x:c r="D14" s="16" t="str">
@@ -5267,7 +5702,7 @@
       <x:c r="B15" s="16" t="str">
         <x:v>Capability</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="str">
+      <x:c r="C15" s="26" t="str">
         <x:v>2024-05-13</x:v>
       </x:c>
       <x:c r="D15" s="16" t="str">
@@ -5296,7 +5731,7 @@
       <x:c r="B16" s="16" t="str">
         <x:v>Capability</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="str">
+      <x:c r="C16" s="26" t="str">
         <x:v>2026-04-07</x:v>
       </x:c>
       <x:c r="D16" s="16" t="str">
@@ -5325,7 +5760,7 @@
       <x:c r="B17" s="16" t="str">
         <x:v>Capability</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="str">
+      <x:c r="C17" s="26" t="str">
         <x:v>2024-05-13</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
@@ -5354,7 +5789,7 @@
       <x:c r="B18" s="16" t="str">
         <x:v>Capability</x:v>
       </x:c>
-      <x:c r="C18" s="25" t="str">
+      <x:c r="C18" s="26" t="str">
         <x:v>2026-04-07</x:v>
       </x:c>
       <x:c r="D18" s="16" t="str">
@@ -5383,7 +5818,7 @@
       <x:c r="B19" s="16" t="str">
         <x:v>Computer use</x:v>
       </x:c>
-      <x:c r="C19" s="25" t="str">
+      <x:c r="C19" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D19" s="16" t="str">
@@ -5412,7 +5847,7 @@
       <x:c r="B20" s="16" t="str">
         <x:v>Computer use</x:v>
       </x:c>
-      <x:c r="C20" s="25" t="str">
+      <x:c r="C20" s="26" t="str">
         <x:v>2026-06-25</x:v>
       </x:c>
       <x:c r="D20" s="16" t="str">
@@ -5441,7 +5876,7 @@
       <x:c r="B21" s="16" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="C21" s="25" t="str">
+      <x:c r="C21" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D21" s="16" t="str">
@@ -5470,7 +5905,7 @@
       <x:c r="B22" s="16" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="str">
+      <x:c r="C22" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D22" s="16" t="str">
@@ -5499,7 +5934,7 @@
       <x:c r="B23" s="16" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="str">
+      <x:c r="C23" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D23" s="16" t="str">
@@ -5528,7 +5963,7 @@
       <x:c r="B24" s="16" t="str">
         <x:v>Business</x:v>
       </x:c>
-      <x:c r="C24" s="25" t="str">
+      <x:c r="C24" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D24" s="16" t="str">
@@ -5557,7 +5992,7 @@
       <x:c r="B25" s="16" t="str">
         <x:v>Broad work</x:v>
       </x:c>
-      <x:c r="C25" s="25" t="str">
+      <x:c r="C25" s="26" t="str">
         <x:v>2026-06-26</x:v>
       </x:c>
       <x:c r="D25" s="16" t="str">
@@ -5586,7 +6021,7 @@
       <x:c r="B26" s="16" t="str">
         <x:v>Harness</x:v>
       </x:c>
-      <x:c r="C26" s="25" t="str">
+      <x:c r="C26" s="26" t="str">
         <x:v>2025-10-28</x:v>
       </x:c>
       <x:c r="D26" s="16" t="str">
@@ -5615,7 +6050,7 @@
       <x:c r="B27" s="16" t="str">
         <x:v>Harness</x:v>
       </x:c>
-      <x:c r="C27" s="25" t="str">
+      <x:c r="C27" s="26" t="str">
         <x:v>2025-10-28</x:v>
       </x:c>
       <x:c r="D27" s="16" t="str">
@@ -5644,7 +6079,7 @@
       <x:c r="B28" s="16" t="str">
         <x:v>Harness</x:v>
       </x:c>
-      <x:c r="C28" s="25" t="str">
+      <x:c r="C28" s="26" t="str">
         <x:v>2025-10-28</x:v>
       </x:c>
       <x:c r="D28" s="16" t="str">
@@ -5673,7 +6108,7 @@
       <x:c r="B29" s="16" t="str">
         <x:v>Harness</x:v>
       </x:c>
-      <x:c r="C29" s="25" t="str">
+      <x:c r="C29" s="26" t="str">
         <x:v>2025-10-28</x:v>
       </x:c>
       <x:c r="D29" s="16" t="str">
@@ -5702,7 +6137,7 @@
       <x:c r="B30" s="16" t="str">
         <x:v>Factuality</x:v>
       </x:c>
-      <x:c r="C30" s="25" t="str">
+      <x:c r="C30" s="26" t="str">
         <x:v>2026-08-19</x:v>
       </x:c>
       <x:c r="D30" s="16" t="str">
@@ -5729,7 +6164,7 @@
       <x:c r="B31" s="16" t="str">
         <x:v>Memory</x:v>
       </x:c>
-      <x:c r="C31" s="25" t="str">
+      <x:c r="C31" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D31" s="16" t="str">
@@ -5758,7 +6193,7 @@
       <x:c r="B32" s="16" t="str">
         <x:v>AI R&amp;D</x:v>
       </x:c>
-      <x:c r="C32" s="25" t="str">
+      <x:c r="C32" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
@@ -5787,7 +6222,7 @@
       <x:c r="B33" s="16" t="str">
         <x:v>AI R&amp;D</x:v>
       </x:c>
-      <x:c r="C33" s="25" t="str">
+      <x:c r="C33" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
@@ -5816,7 +6251,7 @@
       <x:c r="B34" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C34" s="25" t="str">
+      <x:c r="C34" s="26" t="str">
         <x:v>2025-08-07</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
@@ -5845,7 +6280,7 @@
       <x:c r="B35" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C35" s="25" t="str">
+      <x:c r="C35" s="26" t="str">
         <x:v>2026-04-07</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
@@ -5874,7 +6309,7 @@
       <x:c r="B36" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C36" s="25" t="str">
+      <x:c r="C36" s="26" t="str">
         <x:v>2025-09-29</x:v>
       </x:c>
       <x:c r="D36" s="16" t="str">
@@ -5903,7 +6338,7 @@
       <x:c r="B37" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C37" s="25" t="str">
+      <x:c r="C37" s="26" t="str">
         <x:v>2026-04-23</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
@@ -5932,7 +6367,7 @@
       <x:c r="B38" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C38" s="25" t="str">
+      <x:c r="C38" s="26" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="D38" s="16" t="str">
@@ -5961,7 +6396,7 @@
       <x:c r="B39" s="16" t="str">
         <x:v>Consumer benchmark</x:v>
       </x:c>
-      <x:c r="C39" s="25" t="str">
+      <x:c r="C39" s="26" t="str">
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
@@ -5990,7 +6425,7 @@
       <x:c r="B40" s="16" t="str">
         <x:v>Consumer benchmark</x:v>
       </x:c>
-      <x:c r="C40" s="25" t="str">
+      <x:c r="C40" s="26" t="str">
         <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
@@ -6019,7 +6454,7 @@
       <x:c r="B41" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C41" s="25" t="str">
+      <x:c r="C41" s="26" t="str">
         <x:v>2026-07-19</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
@@ -6048,7 +6483,7 @@
       <x:c r="B42" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C42" s="25" t="str">
+      <x:c r="C42" s="26" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
@@ -6077,7 +6512,7 @@
       <x:c r="B43" s="16" t="str">
         <x:v>Capability velocity</x:v>
       </x:c>
-      <x:c r="C43" s="25" t="str">
+      <x:c r="C43" s="26" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
@@ -6106,7 +6541,7 @@
       <x:c r="B44" s="16" t="str">
         <x:v>Professional capability</x:v>
       </x:c>
-      <x:c r="C44" s="25" t="str">
+      <x:c r="C44" s="26" t="str">
         <x:v>2025-08-07</x:v>
       </x:c>
       <x:c r="D44" s="16" t="str">
@@ -6135,7 +6570,7 @@
       <x:c r="B45" s="16" t="str">
         <x:v>Professional capability</x:v>
       </x:c>
-      <x:c r="C45" s="25" t="str">
+      <x:c r="C45" s="26" t="str">
         <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="D45" s="16" t="str">
@@ -6164,7 +6599,7 @@
       <x:c r="B46" s="16" t="str">
         <x:v>Consumer benchmark</x:v>
       </x:c>
-      <x:c r="C46" s="25" t="str">
+      <x:c r="C46" s="26" t="str">
         <x:v>2026-08-25</x:v>
       </x:c>
       <x:c r="D46" s="16" t="str">
@@ -6193,7 +6628,7 @@
       <x:c r="B47" s="16" t="str">
         <x:v>Abstract reasoning</x:v>
       </x:c>
-      <x:c r="C47" s="25" t="str">
+      <x:c r="C47" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D47" s="16" t="str">
@@ -6222,7 +6657,7 @@
       <x:c r="B48" s="16" t="str">
         <x:v>Computer use</x:v>
       </x:c>
-      <x:c r="C48" s="25" t="str">
+      <x:c r="C48" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D48" s="16" t="str">
@@ -6251,7 +6686,7 @@
       <x:c r="B49" s="16" t="str">
         <x:v>Business workflows</x:v>
       </x:c>
-      <x:c r="C49" s="25" t="str">
+      <x:c r="C49" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D49" s="16" t="str">
@@ -6280,7 +6715,7 @@
       <x:c r="B50" s="16" t="str">
         <x:v>Broad work</x:v>
       </x:c>
-      <x:c r="C50" s="25" t="str">
+      <x:c r="C50" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D50" s="16" t="str">
@@ -6309,7 +6744,7 @@
       <x:c r="B51" s="16" t="str">
         <x:v>Alignment</x:v>
       </x:c>
-      <x:c r="C51" s="25" t="str">
+      <x:c r="C51" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D51" s="16" t="str">
@@ -6338,7 +6773,7 @@
       <x:c r="B52" s="16" t="str">
         <x:v>Business workflows</x:v>
       </x:c>
-      <x:c r="C52" s="25" t="str">
+      <x:c r="C52" s="26" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="D52" s="16" t="str">
@@ -6367,7 +6802,7 @@
       <x:c r="B53" s="16" t="str">
         <x:v>Computer use</x:v>
       </x:c>
-      <x:c r="C53" s="25" t="str">
+      <x:c r="C53" s="26" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="D53" s="16" t="str">
@@ -6396,7 +6831,7 @@
       <x:c r="B54" s="16" t="str">
         <x:v>Computer use</x:v>
       </x:c>
-      <x:c r="C54" s="25" t="str">
+      <x:c r="C54" s="26" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="D54" s="16" t="str">
@@ -6425,7 +6860,7 @@
       <x:c r="B55" s="16" t="str">
         <x:v>Professional capability</x:v>
       </x:c>
-      <x:c r="C55" s="25" t="str">
+      <x:c r="C55" s="26" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="D55" s="16" t="str">
@@ -6454,7 +6889,7 @@
       <x:c r="B56" s="16" t="str">
         <x:v>Abstract reasoning</x:v>
       </x:c>
-      <x:c r="C56" s="25" t="str">
+      <x:c r="C56" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D56" s="16" t="str">
@@ -6483,7 +6918,7 @@
       <x:c r="B57" s="16" t="str">
         <x:v>Cybersecurity</x:v>
       </x:c>
-      <x:c r="C57" s="25" t="str">
+      <x:c r="C57" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="D57" s="16" t="str">
@@ -6503,6 +6938,238 @@
       </x:c>
       <x:c r="I57" s="16" t="str">
         <x:v>Vendor-reported maximum-at-any-effort result. OpenAI designates Astra Critical capability in cyber; this is a capability and safety signal, not a Personal-AI delegation measure.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="151.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A58" s="16" t="str">
+        <x:v>evidence-053</x:v>
+      </x:c>
+      <x:c r="B58" s="16" t="str">
+        <x:v>Broad model capability</x:v>
+      </x:c>
+      <x:c r="C58" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D58" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E58" s="16" t="str">
+        <x:v>Epoch Capabilities Index</x:v>
+      </x:c>
+      <x:c r="F58" s="16" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="G58" s="16" t="str">
+        <x:v>index points</x:v>
+      </x:c>
+      <x:c r="H58" s="16" t="str">
+        <x:v>gate1-epoch-ai-gpt-6-astra-model</x:v>
+      </x:c>
+      <x:c r="I58" s="16" t="str">
+        <x:v>Independent point estimate; Epoch reports a 90% interval of 165–174. ECI is a broad capability aggregate, not a direct delegation task.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="205.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A59" s="16" t="str">
+        <x:v>evidence-054</x:v>
+      </x:c>
+      <x:c r="B59" s="16" t="str">
+        <x:v>Broad model capability</x:v>
+      </x:c>
+      <x:c r="C59" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D59" s="16" t="str">
+        <x:v>GPT-6 Astra versus prior ECI frontier</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="str">
+        <x:v>ECI point gain</x:v>
+      </x:c>
+      <x:c r="F59" s="16" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G59" s="16" t="str">
+        <x:v>index points</x:v>
+      </x:c>
+      <x:c r="H59" s="16" t="str">
+        <x:v>gate1-epoch-ai-gpt-6-astra-model</x:v>
+      </x:c>
+      <x:c r="I59" s="16" t="str">
+        <x:v>Uses Epoch's rounded comparison of 169 versus the prior best of 163. The live model translates the gain through a trend and transfer bridge rather than treating 169 as a delegation percentage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="162" hidden="0" customHeight="1">
+      <x:c r="A60" s="16" t="str">
+        <x:v>evidence-055</x:v>
+      </x:c>
+      <x:c r="B60" s="16" t="str">
+        <x:v>Cross-domain model capability</x:v>
+      </x:c>
+      <x:c r="C60" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D60" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E60" s="16" t="str">
+        <x:v>Epoch benchmark suites with new records</x:v>
+      </x:c>
+      <x:c r="F60" s="16" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="str">
+        <x:v>benchmark suites</x:v>
+      </x:c>
+      <x:c r="H60" s="16" t="str">
+        <x:v>gate1-x-com-epoch-ai-gpt-6-astra-assessment</x:v>
+      </x:c>
+      <x:c r="I60" s="16" t="str">
+        <x:v>Epoch identifies math, continual learning, and game puzzles. This is an independent cross-domain release signal, not a normalized delegation score.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="162" hidden="0" customHeight="1">
+      <x:c r="A61" s="16" t="str">
+        <x:v>evidence-056</x:v>
+      </x:c>
+      <x:c r="B61" s="16" t="str">
+        <x:v>Long-horizon coding</x:v>
+      </x:c>
+      <x:c r="C61" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D61" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="E61" s="16" t="str">
+        <x:v>MirrorCode ordinal position</x:v>
+      </x:c>
+      <x:c r="F61" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G61" s="16" t="str">
+        <x:v>reported comparison</x:v>
+      </x:c>
+      <x:c r="H61" s="16" t="str">
+        <x:v>gate1-x-com-epoch-ai-gpt-6-astra-assessment</x:v>
+      </x:c>
+      <x:c r="I61" s="16" t="str">
+        <x:v>Epoch places Astra between Opus 4.7 and Fable 5. The value marks one reported ordinal comparison and is not a benchmark score used in the equation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="151.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A62" s="16" t="str">
+        <x:v>evidence-057</x:v>
+      </x:c>
+      <x:c r="B62" s="16" t="str">
+        <x:v>Interactive abstract reasoning</x:v>
+      </x:c>
+      <x:c r="C62" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D62" s="16" t="str">
+        <x:v>GPT-6 Astra · ARC Prize standard harness</x:v>
+      </x:c>
+      <x:c r="E62" s="16" t="str">
+        <x:v>ARC-AGI-3 score</x:v>
+      </x:c>
+      <x:c r="F62" s="16" t="n">
+        <x:v>62.7</x:v>
+      </x:c>
+      <x:c r="G62" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H62" s="16" t="str">
+        <x:v>gate1-arcprize-org-gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="I62" s="16" t="str">
+        <x:v>Independent standard-harness result at maximum effort; reported evaluation cost was $26,098. Kept separate from the provider-adapter result.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="205.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A63" s="16" t="str">
+        <x:v>evidence-058</x:v>
+      </x:c>
+      <x:c r="B63" s="16" t="str">
+        <x:v>Interactive abstract reasoning</x:v>
+      </x:c>
+      <x:c r="C63" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D63" s="16" t="str">
+        <x:v>GPT-6 Astra · OpenAI provider adapter</x:v>
+      </x:c>
+      <x:c r="E63" s="16" t="str">
+        <x:v>ARC-AGI-3 score</x:v>
+      </x:c>
+      <x:c r="F63" s="16" t="n">
+        <x:v>99.9</x:v>
+      </x:c>
+      <x:c r="G63" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H63" s="16" t="str">
+        <x:v>gate1-arcprize-org-gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="I63" s="16" t="str">
+        <x:v>Independent benchmark-operator result using OpenAI's provider adapter with persisted opaque reasoning and compaction; reported evaluation cost was $18,817. Not a direct delegation percentage.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A64" s="16" t="str">
+        <x:v>evidence-059</x:v>
+      </x:c>
+      <x:c r="B64" s="16" t="str">
+        <x:v>Agentic efficiency</x:v>
+      </x:c>
+      <x:c r="C64" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D64" s="16" t="str">
+        <x:v>GPT-6 Astra · OpenAI provider adapter</x:v>
+      </x:c>
+      <x:c r="E64" s="16" t="str">
+        <x:v>ARC-AGI-3 levels using fewer actions than median human</x:v>
+      </x:c>
+      <x:c r="F64" s="16" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="G64" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H64" s="16" t="str">
+        <x:v>gate1-arcprize-org-gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="I64" s="16" t="str">
+        <x:v>ARC Prize's action-efficiency comparison across evaluated levels; it supports model-level planning efficiency but does not measure household delegation directly.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="140.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A65" s="16" t="str">
+        <x:v>evidence-060</x:v>
+      </x:c>
+      <x:c r="B65" s="16" t="str">
+        <x:v>Agentic efficiency</x:v>
+      </x:c>
+      <x:c r="C65" s="26" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="D65" s="16" t="str">
+        <x:v>GPT-6 Astra · OpenAI provider adapter</x:v>
+      </x:c>
+      <x:c r="E65" s="16" t="str">
+        <x:v>Mean action reduction versus median human</x:v>
+      </x:c>
+      <x:c r="F65" s="16" t="n">
+        <x:v>51.7</x:v>
+      </x:c>
+      <x:c r="G65" s="16" t="str">
+        <x:v>percent</x:v>
+      </x:c>
+      <x:c r="H65" s="16" t="str">
+        <x:v>gate1-arcprize-org-gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="I65" s="16" t="str">
+        <x:v>Average action reduction reported by ARC Prize. It is a mechanistic efficiency signal, not a direct economic completion score.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6512,12 +7179,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9395d064228c4adf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra262785dfe1f4cb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -6609,7 +7276,7 @@
       <x:c r="C6" s="16" t="str">
         <x:v>GPT-5</x:v>
       </x:c>
-      <x:c r="D6" s="25" t="str">
+      <x:c r="D6" s="26" t="str">
         <x:v>2025-08-07</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
@@ -6636,7 +7303,7 @@
       <x:c r="C7" s="16" t="str">
         <x:v>Claude Sonnet 4.5</x:v>
       </x:c>
-      <x:c r="D7" s="25" t="str">
+      <x:c r="D7" s="26" t="str">
         <x:v>2025-09-29</x:v>
       </x:c>
       <x:c r="E7" s="16" t="str">
@@ -6661,7 +7328,7 @@
       <x:c r="C8" s="16" t="str">
         <x:v>Claude Opus 4.5</x:v>
       </x:c>
-      <x:c r="D8" s="25" t="str">
+      <x:c r="D8" s="26" t="str">
         <x:v>2025-11-24</x:v>
       </x:c>
       <x:c r="E8" s="16" t="str">
@@ -6686,7 +7353,7 @@
       <x:c r="C9" s="16" t="str">
         <x:v>GPT-5.2</x:v>
       </x:c>
-      <x:c r="D9" s="25" t="str">
+      <x:c r="D9" s="26" t="str">
         <x:v>2025-12-11</x:v>
       </x:c>
       <x:c r="E9" s="16" t="str">
@@ -6715,7 +7382,7 @@
       <x:c r="C10" s="16" t="str">
         <x:v>Claude Opus 4.6</x:v>
       </x:c>
-      <x:c r="D10" s="25" t="str">
+      <x:c r="D10" s="26" t="str">
         <x:v>2026-02-05</x:v>
       </x:c>
       <x:c r="E10" s="16" t="str">
@@ -6742,7 +7409,7 @@
       <x:c r="C11" s="16" t="str">
         <x:v>GPT-5.4</x:v>
       </x:c>
-      <x:c r="D11" s="25" t="str">
+      <x:c r="D11" s="26" t="str">
         <x:v>2026-03-05</x:v>
       </x:c>
       <x:c r="E11" s="16" t="str">
@@ -6769,7 +7436,7 @@
       <x:c r="C12" s="16" t="str">
         <x:v>GPT-5.4 mini</x:v>
       </x:c>
-      <x:c r="D12" s="25" t="str">
+      <x:c r="D12" s="26" t="str">
         <x:v>2026-03-17</x:v>
       </x:c>
       <x:c r="E12" s="16" t="str">
@@ -6798,7 +7465,7 @@
       <x:c r="C13" s="16" t="str">
         <x:v>Claude Mythos Preview</x:v>
       </x:c>
-      <x:c r="D13" s="25" t="str">
+      <x:c r="D13" s="26" t="str">
         <x:v>2026-04-07</x:v>
       </x:c>
       <x:c r="E13" s="16" t="str">
@@ -6827,7 +7494,7 @@
       <x:c r="C14" s="16" t="str">
         <x:v>Claude Opus 4.7</x:v>
       </x:c>
-      <x:c r="D14" s="25" t="str">
+      <x:c r="D14" s="26" t="str">
         <x:v>2026-04-16</x:v>
       </x:c>
       <x:c r="E14" s="16" t="str">
@@ -6856,7 +7523,7 @@
       <x:c r="C15" s="16" t="str">
         <x:v>GPT-5.5</x:v>
       </x:c>
-      <x:c r="D15" s="25" t="str">
+      <x:c r="D15" s="26" t="str">
         <x:v>2026-04-23</x:v>
       </x:c>
       <x:c r="E15" s="16" t="str">
@@ -6883,7 +7550,7 @@
       <x:c r="C16" s="16" t="str">
         <x:v>Claude Opus 4.8</x:v>
       </x:c>
-      <x:c r="D16" s="25" t="str">
+      <x:c r="D16" s="26" t="str">
         <x:v>2026-05-28</x:v>
       </x:c>
       <x:c r="E16" s="16" t="str">
@@ -6910,7 +7577,7 @@
       <x:c r="C17" s="16" t="str">
         <x:v>Claude Fable 5</x:v>
       </x:c>
-      <x:c r="D17" s="25" t="str">
+      <x:c r="D17" s="26" t="str">
         <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="E17" s="16" t="str">
@@ -6939,7 +7606,7 @@
       <x:c r="C18" s="16" t="str">
         <x:v>GPT-5.6 Sol</x:v>
       </x:c>
-      <x:c r="D18" s="25" t="str">
+      <x:c r="D18" s="26" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="E18" s="16" t="str">
@@ -6968,7 +7635,7 @@
       <x:c r="C19" s="16" t="str">
         <x:v>Qwen 3.8 Max</x:v>
       </x:c>
-      <x:c r="D19" s="25" t="str">
+      <x:c r="D19" s="26" t="str">
         <x:v>2026-07-19</x:v>
       </x:c>
       <x:c r="E19" s="16" t="str">
@@ -6995,7 +7662,7 @@
       <x:c r="C20" s="16" t="str">
         <x:v>Claude Opus 5</x:v>
       </x:c>
-      <x:c r="D20" s="25" t="str">
+      <x:c r="D20" s="26" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="E20" s="16" t="str">
@@ -7022,7 +7689,7 @@
       <x:c r="C21" s="16" t="str">
         <x:v>GPT-6 Astra</x:v>
       </x:c>
-      <x:c r="D21" s="25" t="str">
+      <x:c r="D21" s="26" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E21" s="16" t="str">
@@ -7051,7 +7718,7 @@
       <x:c r="C22" s="16" t="str">
         <x:v>Claude Fable 5.1</x:v>
       </x:c>
-      <x:c r="D22" s="25" t="str">
+      <x:c r="D22" s="26" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E22" s="16" t="str">
@@ -7080,7 +7747,7 @@
       <x:c r="C23" s="16" t="str">
         <x:v>Claude Mythos 5.1</x:v>
       </x:c>
-      <x:c r="D23" s="25" t="str">
+      <x:c r="D23" s="26" t="str">
         <x:v>2026-09-01</x:v>
       </x:c>
       <x:c r="E23" s="16" t="str">
@@ -7106,12 +7773,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd768d4e6b564a47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86bffca52b1f4ed1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -8000,185 +8667,195 @@
       </x:c>
       <x:c r="G44" s="16" t="str"/>
     </x:row>
-    <x:row r="45" ht="54" hidden="0" customHeight="1">
+    <x:row r="45" ht="129.60000610351562" hidden="0" customHeight="1">
       <x:c r="A45" s="16" t="str">
+        <x:v>gate1-arcprize-org-gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="B45" s="16" t="str">
+        <x:v>ARC Prize Foundation</x:v>
+      </x:c>
+      <x:c r="C45" s="16" t="str">
+        <x:v>GPT-6 Astra on ARC-AGI-3</x:v>
+      </x:c>
+      <x:c r="D45" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E45" s="16" t="str">
+        <x:v>independent benchmark evaluation, agentic reasoning evidence, cross-domain corroboration</x:v>
+      </x:c>
+      <x:c r="F45" s="16" t="str">
+        <x:v>https://arcprize.org/blog/astra</x:v>
+      </x:c>
+      <x:c r="G45" s="16" t="str">
+        <x:v>ARC Prize separately reports a standard harness and OpenAI's provider adapter, plus human-normalized action efficiency.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="129.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A46" s="16" t="str">
+        <x:v>gate1-epoch-ai-eci-frontier-trend</x:v>
+      </x:c>
+      <x:c r="B46" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="C46" s="16" t="str">
+        <x:v>The ECI frontier has advanced by 14 points per year since the introduction of reasoning models</x:v>
+      </x:c>
+      <x:c r="D46" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E46" s="16" t="str">
+        <x:v>frontier trend estimate, capability shock normalization</x:v>
+      </x:c>
+      <x:c r="F46" s="16" t="str">
+        <x:v>https://epoch.ai/data-insights/eci-frontier-trend</x:v>
+      </x:c>
+      <x:c r="G46" s="16" t="str">
+        <x:v>Epoch estimates a linear 14 ECI-point annual frontier trend after reasoning models appeared in September 2024.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="172.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A47" s="16" t="str">
+        <x:v>gate1-epoch-ai-gpt-6-astra-model</x:v>
+      </x:c>
+      <x:c r="B47" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="C47" s="16" t="str">
+        <x:v>GPT-6 Astra</x:v>
+      </x:c>
+      <x:c r="D47" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E47" s="16" t="str">
+        <x:v>independent model evaluation, frontier capability signal</x:v>
+      </x:c>
+      <x:c r="F47" s="16" t="str">
+        <x:v>https://epoch.ai/models/gpt-6-astra</x:v>
+      </x:c>
+      <x:c r="G47" s="16" t="str">
+        <x:v>Epoch reports an ECI point estimate of 169 with a 90% interval of 165–174 and rank 1 of 267 evaluated models. OpenAI provided Epoch pre-release access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="270" hidden="0" customHeight="1">
+      <x:c r="A48" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+      </x:c>
+      <x:c r="B48" s="16" t="str">
+        <x:v>OpenAI</x:v>
+      </x:c>
+      <x:c r="C48" s="16" t="str">
+        <x:v>GPT-6 Astra: A new generation of intelligence</x:v>
+      </x:c>
+      <x:c r="D48" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E48" s="16" t="str">
+        <x:v>release metadata, supporting benchmark evidence, computer-use evidence, alignment evidence</x:v>
+      </x:c>
+      <x:c r="F48" s="16" t="str">
+        <x:v>https://openai.com/index/gpt-6-astra/</x:v>
+      </x:c>
+      <x:c r="G48" s="16" t="str">
+        <x:v>OpenAI reports maximum-at-any-effort evaluation scores from its research or API environments. ARC-AGI-3 uses OpenAI's general Responses API harness with persisted reasoning and compaction; these settings were not benchmark-specific.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="108" hidden="0" customHeight="1">
+      <x:c r="A49" s="16" t="str">
+        <x:v>gate1-x-com-epoch-ai-gpt-6-astra-assessment</x:v>
+      </x:c>
+      <x:c r="B49" s="16" t="str">
+        <x:v>Epoch AI</x:v>
+      </x:c>
+      <x:c r="C49" s="16" t="str">
+        <x:v>GPT-6 Astra ECI and benchmark assessment</x:v>
+      </x:c>
+      <x:c r="D49" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E49" s="16" t="str">
+        <x:v>independent benchmark summary, cross-domain corroboration</x:v>
+      </x:c>
+      <x:c r="F49" s="16" t="str">
+        <x:v>https://x.com/EpochAIResearch/status/2095602754282783108</x:v>
+      </x:c>
+      <x:c r="G49" s="16" t="str">
+        <x:v>Epoch says Astra set ECI and domain-benchmark records after OpenAI supplied pre-release access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="54" hidden="0" customHeight="1">
+      <x:c r="A50" s="16" t="str">
         <x:v>gate1-metr-task-horizon-benchmark-results</x:v>
       </x:c>
-      <x:c r="B45" s="16" t="str">
+      <x:c r="B50" s="16" t="str">
         <x:v>METR</x:v>
       </x:c>
-      <x:c r="C45" s="16" t="str">
+      <x:c r="C50" s="16" t="str">
         <x:v>Task-horizon benchmark results</x:v>
       </x:c>
-      <x:c r="D45" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E45" s="16" t="str">
+      <x:c r="D50" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E50" s="16" t="str">
         <x:v>published trend estimate</x:v>
       </x:c>
-      <x:c r="F45" s="16" t="str">
+      <x:c r="F50" s="16" t="str">
         <x:v>https://metr.org/assets/benchmark_results_1_1.yaml</x:v>
       </x:c>
-      <x:c r="G45" s="16" t="str"/>
-    </x:row>
-    <x:row r="46" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A46" s="16" t="str">
+      <x:c r="G50" s="16" t="str"/>
+    </x:row>
+    <x:row r="51" ht="86.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A51" s="16" t="str">
         <x:v>gate1-anthropic-com-anthropic-business-customers</x:v>
       </x:c>
-      <x:c r="B46" s="16" t="str">
+      <x:c r="B51" s="16" t="str">
         <x:v>anthropic.com</x:v>
       </x:c>
-      <x:c r="C46" s="16" t="str">
+      <x:c r="C51" s="16" t="str">
         <x:v>Anthropic: business customers</x:v>
       </x:c>
-      <x:c r="D46" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E46" s="16" t="str">
+      <x:c r="D51" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E51" s="16" t="str">
         <x:v>Distribution</x:v>
       </x:c>
-      <x:c r="F46" s="16" t="str">
+      <x:c r="F51" s="16" t="str">
         <x:v>https://www.anthropic.com/news/anthropic-raises-series-f-at-usd183b-post-money-valuation</x:v>
       </x:c>
-      <x:c r="G46" s="16" t="str"/>
-    </x:row>
-    <x:row r="47" ht="183.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A47" s="16" t="str">
+      <x:c r="G51" s="16" t="str"/>
+    </x:row>
+    <x:row r="52" ht="183.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A52" s="16" t="str">
         <x:v>gate1-anthropic-com-claude-fable-and-mythos-5-1-release</x:v>
       </x:c>
-      <x:c r="B47" s="16" t="str">
+      <x:c r="B52" s="16" t="str">
         <x:v>Anthropic</x:v>
       </x:c>
-      <x:c r="C47" s="16" t="str">
+      <x:c r="C52" s="16" t="str">
         <x:v>Claude Fable 5.1 and Mythos 5.1</x:v>
       </x:c>
-      <x:c r="D47" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E47" s="16" t="str">
+      <x:c r="D52" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E52" s="16" t="str">
         <x:v>release metadata, supporting benchmark evidence, computer-use evidence, professional-work evidence</x:v>
       </x:c>
-      <x:c r="F47" s="16" t="str">
+      <x:c r="F52" s="16" t="str">
         <x:v>https://www.anthropic.com/claude-fable-and-mythos-5-1</x:v>
       </x:c>
-      <x:c r="G47" s="16" t="str">
+      <x:c r="G52" s="16" t="str">
         <x:v>Anthropic describes Fable 5.1 and Mythos 5.1 as the same underlying model with different safeguards. Fable 5.1 was evaluated with production safeguards enabled.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48" ht="54" hidden="0" customHeight="1">
-      <x:c r="A48" s="16" t="str">
-        <x:v>gate1-api-github-com-openclaw-github-stars-observation</x:v>
-      </x:c>
-      <x:c r="B48" s="16" t="str">
-        <x:v>api.github.com</x:v>
-      </x:c>
-      <x:c r="C48" s="16" t="str">
-        <x:v>OpenClaw GitHub stars observation</x:v>
-      </x:c>
-      <x:c r="D48" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E48" s="16" t="str">
-        <x:v>Distribution, adoption observation</x:v>
-      </x:c>
-      <x:c r="F48" s="16" t="str">
-        <x:v>https://api.github.com/repos/openclaw/openclaw</x:v>
-      </x:c>
-      <x:c r="G48" s="16" t="str"/>
-    </x:row>
-    <x:row r="49" ht="64.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A49" s="16" t="str">
-        <x:v>gate1-api-npmjs-org-openclaw-npm-monthly-downloads-observation</x:v>
-      </x:c>
-      <x:c r="B49" s="16" t="str">
-        <x:v>api.npmjs.org</x:v>
-      </x:c>
-      <x:c r="C49" s="16" t="str">
-        <x:v>OpenClaw npm monthly downloads observation</x:v>
-      </x:c>
-      <x:c r="D49" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E49" s="16" t="str">
-        <x:v>Distribution, adoption observation</x:v>
-      </x:c>
-      <x:c r="F49" s="16" t="str">
-        <x:v>https://api.npmjs.org/downloads/point/last-month/openclaw</x:v>
-      </x:c>
-      <x:c r="G49" s="16" t="str"/>
-    </x:row>
-    <x:row r="50" ht="64.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A50" s="16" t="str">
-        <x:v>gate1-apnews-com-chatgpt-paid-consumers-observation</x:v>
-      </x:c>
-      <x:c r="B50" s="16" t="str">
-        <x:v>apnews.com</x:v>
-      </x:c>
-      <x:c r="C50" s="16" t="str">
-        <x:v>ChatGPT paid consumers observation</x:v>
-      </x:c>
-      <x:c r="D50" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E50" s="16" t="str">
-        <x:v>Distribution, adoption observation</x:v>
-      </x:c>
-      <x:c r="F50" s="16" t="str">
-        <x:v>https://apnews.com/article/a0a915c32b85337d799fe2f9525a932a</x:v>
-      </x:c>
-      <x:c r="G50" s="16" t="str"/>
-    </x:row>
-    <x:row r="51" ht="43.20000076293945" hidden="0" customHeight="1">
-      <x:c r="A51" s="16" t="str">
-        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
-      </x:c>
-      <x:c r="B51" s="16" t="str">
-        <x:v>arxiv.org</x:v>
-      </x:c>
-      <x:c r="C51" s="16" t="str">
-        <x:v>o3: OSWorld baseline at 15 steps</x:v>
-      </x:c>
-      <x:c r="D51" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E51" s="16" t="str">
-        <x:v>Harness, capability evidence</x:v>
-      </x:c>
-      <x:c r="F51" s="16" t="str">
-        <x:v>https://arxiv.org/abs/2510.24563</x:v>
-      </x:c>
-      <x:c r="G51" s="16" t="str"/>
-    </x:row>
-    <x:row r="52" ht="97.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A52" s="16" t="str">
-        <x:v>gate1-deploymentsafety-openai-com-gpt-5-6-sol-factual-error-reduction-vs-gpt-5</x:v>
-      </x:c>
-      <x:c r="B52" s="16" t="str">
-        <x:v>deploymentsafety.openai.com</x:v>
-      </x:c>
-      <x:c r="C52" s="16" t="str">
-        <x:v>GPT-5.6 Sol: factual-error reduction vs GPT-5.5 Instant</x:v>
-      </x:c>
-      <x:c r="D52" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E52" s="16" t="str">
-        <x:v>Factuality</x:v>
-      </x:c>
-      <x:c r="F52" s="16" t="str">
-        <x:v>https://deploymentsafety.openai.com/gpt-5-6-august-update/model-safety-training-and-evaluation</x:v>
-      </x:c>
-      <x:c r="G52" s="16" t="str"/>
     </x:row>
     <x:row r="53" ht="54" hidden="0" customHeight="1">
       <x:c r="A53" s="16" t="str">
-        <x:v>gate1-openai-com-codex-reach-observation-3</x:v>
+        <x:v>gate1-api-github-com-openclaw-github-stars-observation</x:v>
       </x:c>
       <x:c r="B53" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>api.github.com</x:v>
       </x:c>
       <x:c r="C53" s="16" t="str">
-        <x:v>Codex reach observation</x:v>
+        <x:v>OpenClaw GitHub stars observation</x:v>
       </x:c>
       <x:c r="D53" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8187,105 +8864,103 @@
         <x:v>Distribution, adoption observation</x:v>
       </x:c>
       <x:c r="F53" s="16" t="str">
-        <x:v>https://openai.com/index/codex-for-knowledge-work/</x:v>
+        <x:v>https://api.github.com/repos/openclaw/openclaw</x:v>
       </x:c>
       <x:c r="G53" s="16" t="str"/>
     </x:row>
-    <x:row r="54" ht="270" hidden="0" customHeight="1">
+    <x:row r="54" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A54" s="16" t="str">
-        <x:v>gate1-openai-com-gpt-6-astra-release</x:v>
+        <x:v>gate1-api-npmjs-org-openclaw-npm-monthly-downloads-observation</x:v>
       </x:c>
       <x:c r="B54" s="16" t="str">
-        <x:v>OpenAI</x:v>
+        <x:v>api.npmjs.org</x:v>
       </x:c>
       <x:c r="C54" s="16" t="str">
-        <x:v>GPT-6 Astra: A new generation of intelligence</x:v>
+        <x:v>OpenClaw npm monthly downloads observation</x:v>
       </x:c>
       <x:c r="D54" s="16" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E54" s="16" t="str">
-        <x:v>release metadata, supporting benchmark evidence, computer-use evidence, alignment evidence</x:v>
+        <x:v>Distribution, adoption observation</x:v>
       </x:c>
       <x:c r="F54" s="16" t="str">
-        <x:v>https://openai.com/index/gpt-6-astra/</x:v>
-      </x:c>
-      <x:c r="G54" s="16" t="str">
-        <x:v>OpenAI reports maximum-at-any-effort evaluation scores from its research or API environments. ARC-AGI-3 uses OpenAI's general Responses API harness with persisted reasoning and compaction; these settings were not benchmark-specific.</x:v>
-      </x:c>
+        <x:v>https://api.npmjs.org/downloads/point/last-month/openclaw</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="str"/>
     </x:row>
     <x:row r="55" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A55" s="16" t="str">
-        <x:v>gate1-openai-com-openai-chatgpt-for-work-seats</x:v>
+        <x:v>gate1-apnews-com-chatgpt-paid-consumers-observation</x:v>
       </x:c>
       <x:c r="B55" s="16" t="str">
+        <x:v>apnews.com</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="str">
+        <x:v>ChatGPT paid consumers observation</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F55" s="16" t="str">
+        <x:v>https://apnews.com/article/a0a915c32b85337d799fe2f9525a932a</x:v>
+      </x:c>
+      <x:c r="G55" s="16" t="str"/>
+    </x:row>
+    <x:row r="56" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A56" s="16" t="str">
+        <x:v>gate1-arxiv-org-o3-osworld-baseline-at-15-steps</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="str">
+        <x:v>arxiv.org</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="str">
+        <x:v>o3: OSWorld baseline at 15 steps</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="str">
+        <x:v>Harness, capability evidence</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="str">
+        <x:v>https://arxiv.org/abs/2510.24563</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="str"/>
+    </x:row>
+    <x:row r="57" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A57" s="16" t="str">
+        <x:v>gate1-deploymentsafety-openai-com-gpt-5-6-sol-factual-error-reduction-vs-gpt-5</x:v>
+      </x:c>
+      <x:c r="B57" s="16" t="str">
+        <x:v>deploymentsafety.openai.com</x:v>
+      </x:c>
+      <x:c r="C57" s="16" t="str">
+        <x:v>GPT-5.6 Sol: factual-error reduction vs GPT-5.5 Instant</x:v>
+      </x:c>
+      <x:c r="D57" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E57" s="16" t="str">
+        <x:v>Factuality</x:v>
+      </x:c>
+      <x:c r="F57" s="16" t="str">
+        <x:v>https://deploymentsafety.openai.com/gpt-5-6-august-update/model-safety-training-and-evaluation</x:v>
+      </x:c>
+      <x:c r="G57" s="16" t="str"/>
+    </x:row>
+    <x:row r="58" ht="54" hidden="0" customHeight="1">
+      <x:c r="A58" s="16" t="str">
+        <x:v>gate1-openai-com-codex-reach-observation-3</x:v>
+      </x:c>
+      <x:c r="B58" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
-      <x:c r="C55" s="16" t="str">
-        <x:v>OpenAI: ChatGPT for Work seats</x:v>
-      </x:c>
-      <x:c r="D55" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E55" s="16" t="str">
-        <x:v>Distribution</x:v>
-      </x:c>
-      <x:c r="F55" s="16" t="str">
-        <x:v>https://openai.com/index/1-million-businesses-putting-ai-to-work/</x:v>
-      </x:c>
-      <x:c r="G55" s="16" t="str"/>
-    </x:row>
-    <x:row r="56" ht="64.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A56" s="16" t="str">
-        <x:v>gate1-rdi-berkeley-edu-best-reported-broad-agent-agents-last-exam-cli</x:v>
-      </x:c>
-      <x:c r="B56" s="16" t="str">
-        <x:v>rdi.berkeley.edu</x:v>
-      </x:c>
-      <x:c r="C56" s="16" t="str">
-        <x:v>best reported broad agent: Agents' Last Exam CLI</x:v>
-      </x:c>
-      <x:c r="D56" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E56" s="16" t="str">
-        <x:v>Broad work</x:v>
-      </x:c>
-      <x:c r="F56" s="16" t="str">
-        <x:v>https://rdi.berkeley.edu/blog/agents-last-exam/</x:v>
-      </x:c>
-      <x:c r="G56" s="16" t="str"/>
-    </x:row>
-    <x:row r="57" ht="75.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A57" s="16" t="str">
-        <x:v>gate1-redis-github-io-hybrid-memory-system-longmemeval-task-averaged-accuracy</x:v>
-      </x:c>
-      <x:c r="B57" s="16" t="str">
-        <x:v>redis.github.io</x:v>
-      </x:c>
-      <x:c r="C57" s="16" t="str">
-        <x:v>hybrid memory system: LongMemEval task-averaged accuracy</x:v>
-      </x:c>
-      <x:c r="D57" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E57" s="16" t="str">
-        <x:v>Memory</x:v>
-      </x:c>
-      <x:c r="F57" s="16" t="str">
-        <x:v>https://redis.github.io/redis-ai-research-public/longmemeval-agent-memory/</x:v>
-      </x:c>
-      <x:c r="G57" s="16" t="str"/>
-    </x:row>
-    <x:row r="58" ht="97.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A58" s="16" t="str">
-        <x:v>gate1-sec-gov-grok-active-paid-subscriptions-observation</x:v>
-      </x:c>
-      <x:c r="B58" s="16" t="str">
-        <x:v>sec.gov</x:v>
-      </x:c>
       <x:c r="C58" s="16" t="str">
-        <x:v>Grok active paid subscriptions observation</x:v>
+        <x:v>Codex reach observation</x:v>
       </x:c>
       <x:c r="D58" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8294,208 +8969,208 @@
         <x:v>Distribution, adoption observation</x:v>
       </x:c>
       <x:c r="F58" s="16" t="str">
+        <x:v>https://openai.com/index/codex-for-knowledge-work/</x:v>
+      </x:c>
+      <x:c r="G58" s="16" t="str"/>
+    </x:row>
+    <x:row r="59" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A59" s="16" t="str">
+        <x:v>gate1-openai-com-openai-chatgpt-for-work-seats</x:v>
+      </x:c>
+      <x:c r="B59" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="str">
+        <x:v>OpenAI: ChatGPT for Work seats</x:v>
+      </x:c>
+      <x:c r="D59" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="str">
+        <x:v>Distribution</x:v>
+      </x:c>
+      <x:c r="F59" s="16" t="str">
+        <x:v>https://openai.com/index/1-million-businesses-putting-ai-to-work/</x:v>
+      </x:c>
+      <x:c r="G59" s="16" t="str"/>
+    </x:row>
+    <x:row r="60" ht="64.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A60" s="16" t="str">
+        <x:v>gate1-rdi-berkeley-edu-best-reported-broad-agent-agents-last-exam-cli</x:v>
+      </x:c>
+      <x:c r="B60" s="16" t="str">
+        <x:v>rdi.berkeley.edu</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="str">
+        <x:v>best reported broad agent: Agents' Last Exam CLI</x:v>
+      </x:c>
+      <x:c r="D60" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E60" s="16" t="str">
+        <x:v>Broad work</x:v>
+      </x:c>
+      <x:c r="F60" s="16" t="str">
+        <x:v>https://rdi.berkeley.edu/blog/agents-last-exam/</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="str"/>
+    </x:row>
+    <x:row r="61" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A61" s="16" t="str">
+        <x:v>gate1-redis-github-io-hybrid-memory-system-longmemeval-task-averaged-accuracy</x:v>
+      </x:c>
+      <x:c r="B61" s="16" t="str">
+        <x:v>redis.github.io</x:v>
+      </x:c>
+      <x:c r="C61" s="16" t="str">
+        <x:v>hybrid memory system: LongMemEval task-averaged accuracy</x:v>
+      </x:c>
+      <x:c r="D61" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E61" s="16" t="str">
+        <x:v>Memory</x:v>
+      </x:c>
+      <x:c r="F61" s="16" t="str">
+        <x:v>https://redis.github.io/redis-ai-research-public/longmemeval-agent-memory/</x:v>
+      </x:c>
+      <x:c r="G61" s="16" t="str"/>
+    </x:row>
+    <x:row r="62" ht="97.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A62" s="16" t="str">
+        <x:v>gate1-sec-gov-grok-active-paid-subscriptions-observation</x:v>
+      </x:c>
+      <x:c r="B62" s="16" t="str">
+        <x:v>sec.gov</x:v>
+      </x:c>
+      <x:c r="C62" s="16" t="str">
+        <x:v>Grok active paid subscriptions observation</x:v>
+      </x:c>
+      <x:c r="D62" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E62" s="16" t="str">
+        <x:v>Distribution, adoption observation</x:v>
+      </x:c>
+      <x:c r="F62" s="16" t="str">
         <x:v>https://www.sec.gov/Archives/edgar/data/1181412/000162828026039276/spaceexplorationtechnologi.htm</x:v>
       </x:c>
-      <x:c r="G58" s="16" t="str"/>
-    </x:row>
-    <x:row r="59" ht="75.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A59" s="16" t="str">
+      <x:c r="G62" s="16" t="str"/>
+    </x:row>
+    <x:row r="63" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A63" s="16" t="str">
         <x:v>gate1-anthropic-com-claude-directive-delegation-observation</x:v>
-      </x:c>
-      <x:c r="B59" s="16" t="str">
-        <x:v>anthropic.com</x:v>
-      </x:c>
-      <x:c r="C59" s="16" t="str">
-        <x:v>Claude directive delegation observation</x:v>
-      </x:c>
-      <x:c r="D59" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E59" s="16" t="str">
-        <x:v>adoption observation</x:v>
-      </x:c>
-      <x:c r="F59" s="16" t="str">
-        <x:v>https://www.anthropic.com/research/anthropic-economic-index-january-2026-report</x:v>
-      </x:c>
-      <x:c r="G59" s="16" t="str"/>
-    </x:row>
-    <x:row r="60" ht="54" hidden="0" customHeight="1">
-      <x:c r="A60" s="16" t="str">
-        <x:v>gate1-anthropic-com-claude-opus-4-5-release</x:v>
-      </x:c>
-      <x:c r="B60" s="16" t="str">
-        <x:v>anthropic.com</x:v>
-      </x:c>
-      <x:c r="C60" s="16" t="str">
-        <x:v>Claude Opus 4.5 release</x:v>
-      </x:c>
-      <x:c r="D60" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E60" s="16" t="str">
-        <x:v>release metadata</x:v>
-      </x:c>
-      <x:c r="F60" s="16" t="str">
-        <x:v>https://www.anthropic.com/news/claude-opus-4-5</x:v>
-      </x:c>
-      <x:c r="G60" s="16" t="str"/>
-    </x:row>
-    <x:row r="61" ht="54" hidden="0" customHeight="1">
-      <x:c r="A61" s="16" t="str">
-        <x:v>gate1-anthropic-com-claude-opus-4-6-release</x:v>
-      </x:c>
-      <x:c r="B61" s="16" t="str">
-        <x:v>anthropic.com</x:v>
-      </x:c>
-      <x:c r="C61" s="16" t="str">
-        <x:v>Claude Opus 4.6 release</x:v>
-      </x:c>
-      <x:c r="D61" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E61" s="16" t="str">
-        <x:v>release metadata</x:v>
-      </x:c>
-      <x:c r="F61" s="16" t="str">
-        <x:v>https://www.anthropic.com/news/claude-opus-4-6</x:v>
-      </x:c>
-      <x:c r="G61" s="16" t="str"/>
-    </x:row>
-    <x:row r="62" ht="54" hidden="0" customHeight="1">
-      <x:c r="A62" s="16" t="str">
-        <x:v>gate1-anthropic-com-claude-opus-4-8-release</x:v>
-      </x:c>
-      <x:c r="B62" s="16" t="str">
-        <x:v>anthropic.com</x:v>
-      </x:c>
-      <x:c r="C62" s="16" t="str">
-        <x:v>Claude Opus 4.8 release</x:v>
-      </x:c>
-      <x:c r="D62" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E62" s="16" t="str">
-        <x:v>release metadata</x:v>
-      </x:c>
-      <x:c r="F62" s="16" t="str">
-        <x:v>https://www.anthropic.com/news/claude-opus-4-8</x:v>
-      </x:c>
-      <x:c r="G62" s="16" t="str"/>
-    </x:row>
-    <x:row r="63" ht="43.20000076293945" hidden="0" customHeight="1">
-      <x:c r="A63" s="16" t="str">
-        <x:v>gate1-anthropic-com-claude-opus-5-release</x:v>
       </x:c>
       <x:c r="B63" s="16" t="str">
         <x:v>anthropic.com</x:v>
       </x:c>
       <x:c r="C63" s="16" t="str">
+        <x:v>Claude directive delegation observation</x:v>
+      </x:c>
+      <x:c r="D63" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E63" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F63" s="16" t="str">
+        <x:v>https://www.anthropic.com/research/anthropic-economic-index-january-2026-report</x:v>
+      </x:c>
+      <x:c r="G63" s="16" t="str"/>
+    </x:row>
+    <x:row r="64" ht="54" hidden="0" customHeight="1">
+      <x:c r="A64" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-5-release</x:v>
+      </x:c>
+      <x:c r="B64" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C64" s="16" t="str">
+        <x:v>Claude Opus 4.5 release</x:v>
+      </x:c>
+      <x:c r="D64" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E64" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F64" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-4-5</x:v>
+      </x:c>
+      <x:c r="G64" s="16" t="str"/>
+    </x:row>
+    <x:row r="65" ht="54" hidden="0" customHeight="1">
+      <x:c r="A65" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-6-release</x:v>
+      </x:c>
+      <x:c r="B65" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C65" s="16" t="str">
+        <x:v>Claude Opus 4.6 release</x:v>
+      </x:c>
+      <x:c r="D65" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E65" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F65" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-4-6</x:v>
+      </x:c>
+      <x:c r="G65" s="16" t="str"/>
+    </x:row>
+    <x:row r="66" ht="54" hidden="0" customHeight="1">
+      <x:c r="A66" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-4-8-release</x:v>
+      </x:c>
+      <x:c r="B66" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C66" s="16" t="str">
+        <x:v>Claude Opus 4.8 release</x:v>
+      </x:c>
+      <x:c r="D66" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E66" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F66" s="16" t="str">
+        <x:v>https://www.anthropic.com/news/claude-opus-4-8</x:v>
+      </x:c>
+      <x:c r="G66" s="16" t="str"/>
+    </x:row>
+    <x:row r="67" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A67" s="16" t="str">
+        <x:v>gate1-anthropic-com-claude-opus-5-release</x:v>
+      </x:c>
+      <x:c r="B67" s="16" t="str">
+        <x:v>anthropic.com</x:v>
+      </x:c>
+      <x:c r="C67" s="16" t="str">
         <x:v>Claude Opus 5 release</x:v>
       </x:c>
-      <x:c r="D63" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E63" s="16" t="str">
+      <x:c r="D67" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E67" s="16" t="str">
         <x:v>release metadata</x:v>
       </x:c>
-      <x:c r="F63" s="16" t="str">
+      <x:c r="F67" s="16" t="str">
         <x:v>https://www.anthropic.com/news/claude-opus-5</x:v>
       </x:c>
-      <x:c r="G63" s="16" t="str"/>
-    </x:row>
-    <x:row r="64" ht="108" hidden="0" customHeight="1">
-      <x:c r="A64" s="16" t="str">
+      <x:c r="G67" s="16" t="str"/>
+    </x:row>
+    <x:row r="68" ht="108" hidden="0" customHeight="1">
+      <x:c r="A68" s="16" t="str">
         <x:v>gate1-federalreserve-gov-us-work-genai-any-use-observation</x:v>
       </x:c>
-      <x:c r="B64" s="16" t="str">
+      <x:c r="B68" s="16" t="str">
         <x:v>federalreserve.gov</x:v>
       </x:c>
-      <x:c r="C64" s="16" t="str">
+      <x:c r="C68" s="16" t="str">
         <x:v>US work GenAI any use observation</x:v>
-      </x:c>
-      <x:c r="D64" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E64" s="16" t="str">
-        <x:v>adoption observation</x:v>
-      </x:c>
-      <x:c r="F64" s="16" t="str">
-        <x:v>https://www.federalreserve.gov/econres/notes/feds-notes/monitoring-ai-adoption-in-the-u-s-economy-20260403.html</x:v>
-      </x:c>
-      <x:c r="G64" s="16" t="str"/>
-    </x:row>
-    <x:row r="65" ht="86.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A65" s="16" t="str">
-        <x:v>gate1-gallup-com-us-employee-ai-use-observation</x:v>
-      </x:c>
-      <x:c r="B65" s="16" t="str">
-        <x:v>gallup.com</x:v>
-      </x:c>
-      <x:c r="C65" s="16" t="str">
-        <x:v>US employee AI use observation</x:v>
-      </x:c>
-      <x:c r="D65" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E65" s="16" t="str">
-        <x:v>adoption observation</x:v>
-      </x:c>
-      <x:c r="F65" s="16" t="str">
-        <x:v>https://www.gallup.com/workplace/704225/rising-adoption-spurs-workforce-changes.aspx</x:v>
-      </x:c>
-      <x:c r="G65" s="16" t="str"/>
-    </x:row>
-    <x:row r="66" ht="75.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A66" s="16" t="str">
-        <x:v>gate1-gallup-com-us-employee-frequent-ai-use-observation</x:v>
-      </x:c>
-      <x:c r="B66" s="16" t="str">
-        <x:v>gallup.com</x:v>
-      </x:c>
-      <x:c r="C66" s="16" t="str">
-        <x:v>US employee frequent AI use observation</x:v>
-      </x:c>
-      <x:c r="D66" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E66" s="16" t="str">
-        <x:v>adoption observation</x:v>
-      </x:c>
-      <x:c r="F66" s="16" t="str">
-        <x:v>https://www.gallup.com/workplace/701195/frequent-workplace-continued-rise.aspx</x:v>
-      </x:c>
-      <x:c r="G66" s="16" t="str"/>
-    </x:row>
-    <x:row r="67" ht="140.39999389648438" hidden="0" customHeight="1">
-      <x:c r="A67" s="16" t="str">
-        <x:v>gate1-investing-com-chatgpt-paid-consumers-observation</x:v>
-      </x:c>
-      <x:c r="B67" s="16" t="str">
-        <x:v>investing.com</x:v>
-      </x:c>
-      <x:c r="C67" s="16" t="str">
-        <x:v>ChatGPT paid consumers observation</x:v>
-      </x:c>
-      <x:c r="D67" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E67" s="16" t="str">
-        <x:v>adoption observation</x:v>
-      </x:c>
-      <x:c r="F67" s="16" t="str">
-        <x:v>https://www.investing.com/news/stock-market-news/openai-projected-at-least-220-million-people-will-pay-for-chatgpt-by-2030-the-information-reports-4378677</x:v>
-      </x:c>
-      <x:c r="G67" s="16" t="str"/>
-    </x:row>
-    <x:row r="68" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A68" s="16" t="str">
-        <x:v>gate1-microsoft-com-microsoft-365-active-agents-index-observation</x:v>
-      </x:c>
-      <x:c r="B68" s="16" t="str">
-        <x:v>microsoft.com</x:v>
-      </x:c>
-      <x:c r="C68" s="16" t="str">
-        <x:v>Microsoft 365 active agents index observation</x:v>
       </x:c>
       <x:c r="D68" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8504,19 +9179,19 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F68" s="16" t="str">
-        <x:v>https://www.microsoft.com/en-us/worklab/work-trend-index/agents-human-agency-and-the-opportunity-for-every-organization</x:v>
+        <x:v>https://www.federalreserve.gov/econres/notes/feds-notes/monitoring-ai-adoption-in-the-u-s-economy-20260403.html</x:v>
       </x:c>
       <x:c r="G68" s="16" t="str"/>
     </x:row>
-    <x:row r="69" ht="54" hidden="0" customHeight="1">
+    <x:row r="69" ht="86.4000015258789" hidden="0" customHeight="1">
       <x:c r="A69" s="16" t="str">
-        <x:v>gate1-openai-com-chatgpt-reported-reach-observation</x:v>
+        <x:v>gate1-gallup-com-us-employee-ai-use-observation</x:v>
       </x:c>
       <x:c r="B69" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>gallup.com</x:v>
       </x:c>
       <x:c r="C69" s="16" t="str">
-        <x:v>ChatGPT reported reach observation</x:v>
+        <x:v>US employee AI use observation</x:v>
       </x:c>
       <x:c r="D69" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8525,19 +9200,19 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F69" s="16" t="str">
-        <x:v>https://openai.com/index/how-people-are-using-chatgpt/</x:v>
+        <x:v>https://www.gallup.com/workplace/704225/rising-adoption-spurs-workforce-changes.aspx</x:v>
       </x:c>
       <x:c r="G69" s="16" t="str"/>
     </x:row>
-    <x:row r="70" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="70" ht="75.5999984741211" hidden="0" customHeight="1">
       <x:c r="A70" s="16" t="str">
-        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-2</x:v>
+        <x:v>gate1-gallup-com-us-employee-frequent-ai-use-observation</x:v>
       </x:c>
       <x:c r="B70" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>gallup.com</x:v>
       </x:c>
       <x:c r="C70" s="16" t="str">
-        <x:v>ChatGPT reported reach observation</x:v>
+        <x:v>US employee frequent AI use observation</x:v>
       </x:c>
       <x:c r="D70" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8546,19 +9221,19 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F70" s="16" t="str">
-        <x:v>https://openai.com/index/the-state-of-enterprise-ai-2025-report/</x:v>
+        <x:v>https://www.gallup.com/workplace/701195/frequent-workplace-continued-rise.aspx</x:v>
       </x:c>
       <x:c r="G70" s="16" t="str"/>
     </x:row>
-    <x:row r="71" ht="54" hidden="0" customHeight="1">
+    <x:row r="71" ht="140.39999389648438" hidden="0" customHeight="1">
       <x:c r="A71" s="16" t="str">
-        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-3</x:v>
+        <x:v>gate1-investing-com-chatgpt-paid-consumers-observation</x:v>
       </x:c>
       <x:c r="B71" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>investing.com</x:v>
       </x:c>
       <x:c r="C71" s="16" t="str">
-        <x:v>ChatGPT reported reach observation</x:v>
+        <x:v>ChatGPT paid consumers observation</x:v>
       </x:c>
       <x:c r="D71" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8567,19 +9242,19 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F71" s="16" t="str">
-        <x:v>https://openai.com/index/grupo-folha-grupo-uol-partnership/</x:v>
+        <x:v>https://www.investing.com/news/stock-market-news/openai-projected-at-least-220-million-people-will-pay-for-chatgpt-by-2030-the-information-reports-4378677</x:v>
       </x:c>
       <x:c r="G71" s="16" t="str"/>
     </x:row>
-    <x:row r="72" ht="64.80000305175781" hidden="0" customHeight="1">
+    <x:row r="72" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A72" s="16" t="str">
-        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-4</x:v>
+        <x:v>gate1-microsoft-com-microsoft-365-active-agents-index-observation</x:v>
       </x:c>
       <x:c r="B72" s="16" t="str">
-        <x:v>openai.com</x:v>
+        <x:v>microsoft.com</x:v>
       </x:c>
       <x:c r="C72" s="16" t="str">
-        <x:v>ChatGPT reported reach observation</x:v>
+        <x:v>Microsoft 365 active agents index observation</x:v>
       </x:c>
       <x:c r="D72" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8588,19 +9263,19 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F72" s="16" t="str">
-        <x:v>https://openai.com/index/how-the-world-is-putting-chatgpt-to-work/</x:v>
+        <x:v>https://www.microsoft.com/en-us/worklab/work-trend-index/agents-human-agency-and-the-opportunity-for-every-organization</x:v>
       </x:c>
       <x:c r="G72" s="16" t="str"/>
     </x:row>
     <x:row r="73" ht="54" hidden="0" customHeight="1">
       <x:c r="A73" s="16" t="str">
-        <x:v>gate1-openai-com-codex-reach-observation</x:v>
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation</x:v>
       </x:c>
       <x:c r="B73" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C73" s="16" t="str">
-        <x:v>Codex reach observation</x:v>
+        <x:v>ChatGPT reported reach observation</x:v>
       </x:c>
       <x:c r="D73" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8609,19 +9284,19 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F73" s="16" t="str">
-        <x:v>https://openai.com/index/next-phase-of-enterprise-ai/</x:v>
+        <x:v>https://openai.com/index/how-people-are-using-chatgpt/</x:v>
       </x:c>
       <x:c r="G73" s="16" t="str"/>
     </x:row>
     <x:row r="74" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A74" s="16" t="str">
-        <x:v>gate1-openai-com-codex-reach-observation-2</x:v>
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-2</x:v>
       </x:c>
       <x:c r="B74" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C74" s="16" t="str">
-        <x:v>Codex reach observation</x:v>
+        <x:v>ChatGPT reported reach observation</x:v>
       </x:c>
       <x:c r="D74" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8630,82 +9305,82 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F74" s="16" t="str">
-        <x:v>https://openai.com/index/the-next-phase-of-education-for-countries/</x:v>
+        <x:v>https://openai.com/index/the-state-of-enterprise-ai-2025-report/</x:v>
       </x:c>
       <x:c r="G74" s="16" t="str"/>
     </x:row>
-    <x:row r="75" ht="32.400001525878906" hidden="0" customHeight="1">
+    <x:row r="75" ht="54" hidden="0" customHeight="1">
       <x:c r="A75" s="16" t="str">
-        <x:v>gate1-openai-com-gpt-5-2-release</x:v>
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-3</x:v>
       </x:c>
       <x:c r="B75" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C75" s="16" t="str">
-        <x:v>GPT-5.2 release</x:v>
+        <x:v>ChatGPT reported reach observation</x:v>
       </x:c>
       <x:c r="D75" s="16" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E75" s="16" t="str">
-        <x:v>release metadata</x:v>
+        <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F75" s="16" t="str">
-        <x:v>https://openai.com/</x:v>
+        <x:v>https://openai.com/index/grupo-folha-grupo-uol-partnership/</x:v>
       </x:c>
       <x:c r="G75" s="16" t="str"/>
     </x:row>
-    <x:row r="76" ht="54" hidden="0" customHeight="1">
+    <x:row r="76" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A76" s="16" t="str">
-        <x:v>gate1-openai-com-gpt-5-4-mini-release</x:v>
+        <x:v>gate1-openai-com-chatgpt-reported-reach-observation-4</x:v>
       </x:c>
       <x:c r="B76" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C76" s="16" t="str">
-        <x:v>GPT-5.4 mini release</x:v>
+        <x:v>ChatGPT reported reach observation</x:v>
       </x:c>
       <x:c r="D76" s="16" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E76" s="16" t="str">
-        <x:v>release metadata</x:v>
+        <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F76" s="16" t="str">
-        <x:v>https://openai.com/index/introducing-gpt-5-4-mini-and-nano/</x:v>
+        <x:v>https://openai.com/index/how-the-world-is-putting-chatgpt-to-work/</x:v>
       </x:c>
       <x:c r="G76" s="16" t="str"/>
     </x:row>
-    <x:row r="77" ht="43.20000076293945" hidden="0" customHeight="1">
+    <x:row r="77" ht="54" hidden="0" customHeight="1">
       <x:c r="A77" s="16" t="str">
-        <x:v>gate1-openai-com-gpt-5-release</x:v>
+        <x:v>gate1-openai-com-codex-reach-observation</x:v>
       </x:c>
       <x:c r="B77" s="16" t="str">
         <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C77" s="16" t="str">
-        <x:v>GPT-5 release</x:v>
+        <x:v>Codex reach observation</x:v>
       </x:c>
       <x:c r="D77" s="16" t="str">
         <x:v>2026-09-03</x:v>
       </x:c>
       <x:c r="E77" s="16" t="str">
-        <x:v>release metadata</x:v>
+        <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F77" s="16" t="str">
-        <x:v>https://openai.com/index/introducing-gpt-5/</x:v>
+        <x:v>https://openai.com/index/next-phase-of-enterprise-ai/</x:v>
       </x:c>
       <x:c r="G77" s="16" t="str"/>
     </x:row>
-    <x:row r="78" ht="54" hidden="0" customHeight="1">
+    <x:row r="78" ht="64.80000305175781" hidden="0" customHeight="1">
       <x:c r="A78" s="16" t="str">
-        <x:v>gate1-ramp-com-us-businesses-paying-for-ai-observation</x:v>
+        <x:v>gate1-openai-com-codex-reach-observation-2</x:v>
       </x:c>
       <x:c r="B78" s="16" t="str">
-        <x:v>ramp.com</x:v>
+        <x:v>openai.com</x:v>
       </x:c>
       <x:c r="C78" s="16" t="str">
-        <x:v>US businesses paying for AI observation</x:v>
+        <x:v>Codex reach observation</x:v>
       </x:c>
       <x:c r="D78" s="16" t="str">
         <x:v>2026-09-03</x:v>
@@ -8714,51 +9389,135 @@
         <x:v>adoption observation</x:v>
       </x:c>
       <x:c r="F78" s="16" t="str">
+        <x:v>https://openai.com/index/the-next-phase-of-education-for-countries/</x:v>
+      </x:c>
+      <x:c r="G78" s="16" t="str"/>
+    </x:row>
+    <x:row r="79" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A79" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-2-release</x:v>
+      </x:c>
+      <x:c r="B79" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C79" s="16" t="str">
+        <x:v>GPT-5.2 release</x:v>
+      </x:c>
+      <x:c r="D79" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E79" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F79" s="16" t="str">
+        <x:v>https://openai.com/</x:v>
+      </x:c>
+      <x:c r="G79" s="16" t="str"/>
+    </x:row>
+    <x:row r="80" ht="54" hidden="0" customHeight="1">
+      <x:c r="A80" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-4-mini-release</x:v>
+      </x:c>
+      <x:c r="B80" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C80" s="16" t="str">
+        <x:v>GPT-5.4 mini release</x:v>
+      </x:c>
+      <x:c r="D80" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E80" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F80" s="16" t="str">
+        <x:v>https://openai.com/index/introducing-gpt-5-4-mini-and-nano/</x:v>
+      </x:c>
+      <x:c r="G80" s="16" t="str"/>
+    </x:row>
+    <x:row r="81" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A81" s="16" t="str">
+        <x:v>gate1-openai-com-gpt-5-release</x:v>
+      </x:c>
+      <x:c r="B81" s="16" t="str">
+        <x:v>openai.com</x:v>
+      </x:c>
+      <x:c r="C81" s="16" t="str">
+        <x:v>GPT-5 release</x:v>
+      </x:c>
+      <x:c r="D81" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E81" s="16" t="str">
+        <x:v>release metadata</x:v>
+      </x:c>
+      <x:c r="F81" s="16" t="str">
+        <x:v>https://openai.com/index/introducing-gpt-5/</x:v>
+      </x:c>
+      <x:c r="G81" s="16" t="str"/>
+    </x:row>
+    <x:row r="82" ht="54" hidden="0" customHeight="1">
+      <x:c r="A82" s="16" t="str">
+        <x:v>gate1-ramp-com-us-businesses-paying-for-ai-observation</x:v>
+      </x:c>
+      <x:c r="B82" s="16" t="str">
+        <x:v>ramp.com</x:v>
+      </x:c>
+      <x:c r="C82" s="16" t="str">
+        <x:v>US businesses paying for AI observation</x:v>
+      </x:c>
+      <x:c r="D82" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E82" s="16" t="str">
+        <x:v>adoption observation</x:v>
+      </x:c>
+      <x:c r="F82" s="16" t="str">
         <x:v>https://ramp.com/data/april-2026-ai-index</x:v>
       </x:c>
-      <x:c r="G78" s="16" t="str"/>
-    </x:row>
-    <x:row r="79" ht="54" hidden="0" customHeight="1">
-      <x:c r="A79" s="16" t="str">
+      <x:c r="G82" s="16" t="str"/>
+    </x:row>
+    <x:row r="83" ht="54" hidden="0" customHeight="1">
+      <x:c r="A83" s="16" t="str">
         <x:v>gate1-ramp-com-us-businesses-paying-for-ai-observation-2</x:v>
       </x:c>
-      <x:c r="B79" s="16" t="str">
+      <x:c r="B83" s="16" t="str">
         <x:v>ramp.com</x:v>
       </x:c>
-      <x:c r="C79" s="16" t="str">
+      <x:c r="C83" s="16" t="str">
         <x:v>US businesses paying for AI observation</x:v>
       </x:c>
-      <x:c r="D79" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E79" s="16" t="str">
+      <x:c r="D83" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E83" s="16" t="str">
         <x:v>adoption observation</x:v>
       </x:c>
-      <x:c r="F79" s="16" t="str">
+      <x:c r="F83" s="16" t="str">
         <x:v>https://ramp.com/data/</x:v>
       </x:c>
-      <x:c r="G79" s="16" t="str"/>
-    </x:row>
-    <x:row r="80" ht="75.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A80" s="16" t="str">
+      <x:c r="G83" s="16" t="str"/>
+    </x:row>
+    <x:row r="84" ht="75.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A84" s="16" t="str">
         <x:v>gate1-techradar-com-openclaw-github-stars-observation</x:v>
       </x:c>
-      <x:c r="B80" s="16" t="str">
+      <x:c r="B84" s="16" t="str">
         <x:v>techradar.com</x:v>
       </x:c>
-      <x:c r="C80" s="16" t="str">
+      <x:c r="C84" s="16" t="str">
         <x:v>OpenClaw GitHub stars observation</x:v>
       </x:c>
-      <x:c r="D80" s="16" t="str">
-        <x:v>2026-09-03</x:v>
-      </x:c>
-      <x:c r="E80" s="16" t="str">
+      <x:c r="D84" s="16" t="str">
+        <x:v>2026-09-03</x:v>
+      </x:c>
+      <x:c r="E84" s="16" t="str">
         <x:v>adoption observation</x:v>
       </x:c>
-      <x:c r="F80" s="16" t="str">
+      <x:c r="F84" s="16" t="str">
         <x:v>https://www.techradar.com/pro/wild-things-people-are-building-with-openclaw</x:v>
       </x:c>
-      <x:c r="G80" s="16" t="str"/>
+      <x:c r="G84" s="16" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8767,7 +9526,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36c1322c595e4f54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bb4ca11bf014534"/>
   </x:tableParts>
 </x:worksheet>
 </file>